--- a/docs/design/ACSMS-SCR-017/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_販売店情報登録画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-017/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_販売店情報登録画面_V1.0.xlsx
@@ -1701,7 +1701,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/16</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2127,7 +2127,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/16</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2626,7 +2626,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>HANBAITEN_NOT_FOUND</t>
+          <t>NOT_FOUND</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -2942,7 +2942,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/16</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3279,7 +3279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK99"/>
+  <dimension ref="A1:AK100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3440,7 +3440,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/16</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3794,7 +3794,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -4581,7 +4581,7 @@
       <c r="X33" s="11" t="n"/>
       <c r="Y33" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z33" s="10" t="n"/>
@@ -4701,7 +4701,7 @@
       <c r="X35" s="11" t="n"/>
       <c r="Y35" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z35" s="10" t="n"/>
@@ -4761,7 +4761,7 @@
       <c r="X36" s="11" t="n"/>
       <c r="Y36" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z36" s="10" t="n"/>
@@ -4821,7 +4821,7 @@
       <c r="X37" s="11" t="n"/>
       <c r="Y37" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z37" s="10" t="n"/>
@@ -4881,7 +4881,7 @@
       <c r="X38" s="11" t="n"/>
       <c r="Y38" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z38" s="10" t="n"/>
@@ -5303,7 +5303,7 @@
       <c r="X45" s="11" t="n"/>
       <c r="Y45" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z45" s="10" t="n"/>
@@ -5363,7 +5363,7 @@
       <c r="X46" s="11" t="n"/>
       <c r="Y46" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z46" s="10" t="n"/>
@@ -5690,7 +5690,7 @@
       <c r="C52" s="38" t="n"/>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>biko</t>
+          <t>haiten_flg</t>
         </is>
       </c>
       <c r="E52" s="10" t="n"/>
@@ -5703,7 +5703,7 @@
       <c r="L52" s="11" t="n"/>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N52" s="10" t="n"/>
@@ -5723,7 +5723,7 @@
       <c r="X52" s="11" t="n"/>
       <c r="Y52" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z52" s="10" t="n"/>
@@ -5734,7 +5734,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>廃店フラグ（true:廃店, false:営業中）</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -5750,7 +5750,7 @@
       <c r="C53" s="38" t="n"/>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>biko</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
@@ -5776,11 +5776,7 @@
       </c>
       <c r="R53" s="10" t="n"/>
       <c r="S53" s="11" t="n"/>
-      <c r="T53" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T53" s="17" t="inlineStr"/>
       <c r="U53" s="10" t="n"/>
       <c r="V53" s="10" t="n"/>
       <c r="W53" s="10" t="n"/>
@@ -5798,7 +5794,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -5811,10 +5807,10 @@
       <c r="B54" s="31" t="n">
         <v>27</v>
       </c>
-      <c r="C54" s="39" t="n"/>
+      <c r="C54" s="38" t="n"/>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E54" s="10" t="n"/>
@@ -5851,7 +5847,7 @@
       <c r="X54" s="11" t="n"/>
       <c r="Y54" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z54" s="10" t="n"/>
@@ -5862,7 +5858,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -5871,64 +5867,128 @@
       <c r="AJ54" s="10" t="n"/>
       <c r="AK54" s="11" t="n"/>
     </row>
-    <row r="55" ht="19.5" customHeight="1"/>
-    <row r="56" ht="19.5" customHeight="1">
-      <c r="B56" s="40" t="inlineStr">
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="31" t="n">
+        <v>28</v>
+      </c>
+      <c r="C55" s="39" t="n"/>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="10" t="n"/>
+      <c r="K55" s="10" t="n"/>
+      <c r="L55" s="11" t="n"/>
+      <c r="M55" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="n"/>
+      <c r="P55" s="11" t="n"/>
+      <c r="Q55" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="11" t="n"/>
+      <c r="T55" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U55" s="10" t="n"/>
+      <c r="V55" s="10" t="n"/>
+      <c r="W55" s="10" t="n"/>
+      <c r="X55" s="11" t="n"/>
+      <c r="Y55" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z55" s="10" t="n"/>
+      <c r="AA55" s="10" t="n"/>
+      <c r="AB55" s="10" t="n"/>
+      <c r="AC55" s="10" t="n"/>
+      <c r="AD55" s="10" t="n"/>
+      <c r="AE55" s="11" t="n"/>
+      <c r="AF55" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AG55" s="10" t="n"/>
+      <c r="AH55" s="10" t="n"/>
+      <c r="AI55" s="10" t="n"/>
+      <c r="AJ55" s="10" t="n"/>
+      <c r="AK55" s="11" t="n"/>
+    </row>
+    <row r="56" ht="19.5" customHeight="1"/>
+    <row r="57" ht="19.5" customHeight="1">
+      <c r="B57" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="C57" s="19" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>GET /api/v1/hanbaiten/1</t>
         </is>
       </c>
-      <c r="D57" s="10" t="n"/>
-      <c r="E57" s="10" t="n"/>
-      <c r="F57" s="10" t="n"/>
-      <c r="G57" s="10" t="n"/>
-      <c r="H57" s="10" t="n"/>
-      <c r="I57" s="10" t="n"/>
-      <c r="J57" s="10" t="n"/>
-      <c r="K57" s="10" t="n"/>
-      <c r="L57" s="10" t="n"/>
-      <c r="M57" s="10" t="n"/>
-      <c r="N57" s="10" t="n"/>
-      <c r="O57" s="10" t="n"/>
-      <c r="P57" s="10" t="n"/>
-      <c r="Q57" s="10" t="n"/>
-      <c r="R57" s="10" t="n"/>
-      <c r="S57" s="10" t="n"/>
-      <c r="T57" s="10" t="n"/>
-      <c r="U57" s="10" t="n"/>
-      <c r="V57" s="10" t="n"/>
-      <c r="W57" s="10" t="n"/>
-      <c r="X57" s="10" t="n"/>
-      <c r="Y57" s="10" t="n"/>
-      <c r="Z57" s="10" t="n"/>
-      <c r="AA57" s="10" t="n"/>
-      <c r="AB57" s="10" t="n"/>
-      <c r="AC57" s="10" t="n"/>
-      <c r="AD57" s="10" t="n"/>
-      <c r="AE57" s="10" t="n"/>
-      <c r="AF57" s="10" t="n"/>
-      <c r="AG57" s="10" t="n"/>
-      <c r="AH57" s="10" t="n"/>
-      <c r="AI57" s="10" t="n"/>
-      <c r="AJ57" s="10" t="n"/>
-      <c r="AK57" s="11" t="n"/>
-    </row>
-    <row r="59" ht="19.5" customHeight="1">
-      <c r="B59" s="40" t="inlineStr">
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="10" t="n"/>
+      <c r="J58" s="10" t="n"/>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="10" t="n"/>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="10" t="n"/>
+      <c r="X58" s="10" t="n"/>
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="10" t="n"/>
+      <c r="AE58" s="10" t="n"/>
+      <c r="AF58" s="10" t="n"/>
+      <c r="AG58" s="10" t="n"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="10" t="n"/>
+      <c r="AJ58" s="10" t="n"/>
+      <c r="AK58" s="11" t="n"/>
+    </row>
+    <row r="60" ht="19.5" customHeight="1">
+      <c r="B60" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="409" customHeight="1">
-      <c r="C60" s="19" t="inlineStr">
+    <row r="61" ht="409" customHeight="1">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
@@ -5955,6 +6015,7 @@
     "yokin_shubetsu": 1,
     "koza_no": "1234567",
     "koza_meigi": "販売店A代表",
+    "haiten_flg": false,
     "biko": "特別な対応なし",
     "created_at": "2026-01-15T10:00:00Z",
     "updated_at": "2026-03-10T14:30:00Z"
@@ -5962,50 +6023,50 @@
 }</t>
         </is>
       </c>
-      <c r="D60" s="10" t="n"/>
-      <c r="E60" s="10" t="n"/>
-      <c r="F60" s="10" t="n"/>
-      <c r="G60" s="10" t="n"/>
-      <c r="H60" s="10" t="n"/>
-      <c r="I60" s="10" t="n"/>
-      <c r="J60" s="10" t="n"/>
-      <c r="K60" s="10" t="n"/>
-      <c r="L60" s="10" t="n"/>
-      <c r="M60" s="10" t="n"/>
-      <c r="N60" s="10" t="n"/>
-      <c r="O60" s="10" t="n"/>
-      <c r="P60" s="10" t="n"/>
-      <c r="Q60" s="10" t="n"/>
-      <c r="R60" s="10" t="n"/>
-      <c r="S60" s="10" t="n"/>
-      <c r="T60" s="10" t="n"/>
-      <c r="U60" s="10" t="n"/>
-      <c r="V60" s="10" t="n"/>
-      <c r="W60" s="10" t="n"/>
-      <c r="X60" s="10" t="n"/>
-      <c r="Y60" s="10" t="n"/>
-      <c r="Z60" s="10" t="n"/>
-      <c r="AA60" s="10" t="n"/>
-      <c r="AB60" s="10" t="n"/>
-      <c r="AC60" s="10" t="n"/>
-      <c r="AD60" s="10" t="n"/>
-      <c r="AE60" s="10" t="n"/>
-      <c r="AF60" s="10" t="n"/>
-      <c r="AG60" s="10" t="n"/>
-      <c r="AH60" s="10" t="n"/>
-      <c r="AI60" s="10" t="n"/>
-      <c r="AJ60" s="10" t="n"/>
-      <c r="AK60" s="11" t="n"/>
-    </row>
-    <row r="62" ht="19.5" customHeight="1">
-      <c r="B62" s="40" t="inlineStr">
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="10" t="n"/>
+      <c r="J61" s="10" t="n"/>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="10" t="n"/>
+      <c r="Q61" s="10" t="n"/>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="10" t="n"/>
+      <c r="X61" s="10" t="n"/>
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="10" t="n"/>
+      <c r="AE61" s="10" t="n"/>
+      <c r="AF61" s="10" t="n"/>
+      <c r="AG61" s="10" t="n"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="10" t="n"/>
+      <c r="AJ61" s="10" t="n"/>
+      <c r="AK61" s="11" t="n"/>
+    </row>
+    <row r="63" ht="19.5" customHeight="1">
+      <c r="B63" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="72" customHeight="1">
-      <c r="C63" s="19" t="inlineStr">
+    <row r="64" ht="72" customHeight="1">
+      <c r="C64" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -6013,50 +6074,50 @@
 }</t>
         </is>
       </c>
-      <c r="D63" s="10" t="n"/>
-      <c r="E63" s="10" t="n"/>
-      <c r="F63" s="10" t="n"/>
-      <c r="G63" s="10" t="n"/>
-      <c r="H63" s="10" t="n"/>
-      <c r="I63" s="10" t="n"/>
-      <c r="J63" s="10" t="n"/>
-      <c r="K63" s="10" t="n"/>
-      <c r="L63" s="10" t="n"/>
-      <c r="M63" s="10" t="n"/>
-      <c r="N63" s="10" t="n"/>
-      <c r="O63" s="10" t="n"/>
-      <c r="P63" s="10" t="n"/>
-      <c r="Q63" s="10" t="n"/>
-      <c r="R63" s="10" t="n"/>
-      <c r="S63" s="10" t="n"/>
-      <c r="T63" s="10" t="n"/>
-      <c r="U63" s="10" t="n"/>
-      <c r="V63" s="10" t="n"/>
-      <c r="W63" s="10" t="n"/>
-      <c r="X63" s="10" t="n"/>
-      <c r="Y63" s="10" t="n"/>
-      <c r="Z63" s="10" t="n"/>
-      <c r="AA63" s="10" t="n"/>
-      <c r="AB63" s="10" t="n"/>
-      <c r="AC63" s="10" t="n"/>
-      <c r="AD63" s="10" t="n"/>
-      <c r="AE63" s="10" t="n"/>
-      <c r="AF63" s="10" t="n"/>
-      <c r="AG63" s="10" t="n"/>
-      <c r="AH63" s="10" t="n"/>
-      <c r="AI63" s="10" t="n"/>
-      <c r="AJ63" s="10" t="n"/>
-      <c r="AK63" s="11" t="n"/>
-    </row>
-    <row r="65" ht="19.5" customHeight="1">
-      <c r="B65" s="40" t="inlineStr">
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="10" t="n"/>
+      <c r="J64" s="10" t="n"/>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="10" t="n"/>
+      <c r="Q64" s="10" t="n"/>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="10" t="n"/>
+      <c r="X64" s="10" t="n"/>
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="10" t="n"/>
+      <c r="AD64" s="10" t="n"/>
+      <c r="AE64" s="10" t="n"/>
+      <c r="AF64" s="10" t="n"/>
+      <c r="AG64" s="10" t="n"/>
+      <c r="AH64" s="10" t="n"/>
+      <c r="AI64" s="10" t="n"/>
+      <c r="AJ64" s="10" t="n"/>
+      <c r="AK64" s="11" t="n"/>
+    </row>
+    <row r="66" ht="19.5" customHeight="1">
+      <c r="B66" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="72" customHeight="1">
-      <c r="C66" s="19" t="inlineStr">
+    <row r="67" ht="72" customHeight="1">
+      <c r="C67" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -6064,50 +6125,50 @@
 }</t>
         </is>
       </c>
-      <c r="D66" s="10" t="n"/>
-      <c r="E66" s="10" t="n"/>
-      <c r="F66" s="10" t="n"/>
-      <c r="G66" s="10" t="n"/>
-      <c r="H66" s="10" t="n"/>
-      <c r="I66" s="10" t="n"/>
-      <c r="J66" s="10" t="n"/>
-      <c r="K66" s="10" t="n"/>
-      <c r="L66" s="10" t="n"/>
-      <c r="M66" s="10" t="n"/>
-      <c r="N66" s="10" t="n"/>
-      <c r="O66" s="10" t="n"/>
-      <c r="P66" s="10" t="n"/>
-      <c r="Q66" s="10" t="n"/>
-      <c r="R66" s="10" t="n"/>
-      <c r="S66" s="10" t="n"/>
-      <c r="T66" s="10" t="n"/>
-      <c r="U66" s="10" t="n"/>
-      <c r="V66" s="10" t="n"/>
-      <c r="W66" s="10" t="n"/>
-      <c r="X66" s="10" t="n"/>
-      <c r="Y66" s="10" t="n"/>
-      <c r="Z66" s="10" t="n"/>
-      <c r="AA66" s="10" t="n"/>
-      <c r="AB66" s="10" t="n"/>
-      <c r="AC66" s="10" t="n"/>
-      <c r="AD66" s="10" t="n"/>
-      <c r="AE66" s="10" t="n"/>
-      <c r="AF66" s="10" t="n"/>
-      <c r="AG66" s="10" t="n"/>
-      <c r="AH66" s="10" t="n"/>
-      <c r="AI66" s="10" t="n"/>
-      <c r="AJ66" s="10" t="n"/>
-      <c r="AK66" s="11" t="n"/>
-    </row>
-    <row r="68" ht="19.5" customHeight="1">
-      <c r="B68" s="40" t="inlineStr">
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="10" t="n"/>
+      <c r="J67" s="10" t="n"/>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="10" t="n"/>
+      <c r="Q67" s="10" t="n"/>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
+      <c r="U67" s="10" t="n"/>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" s="10" t="n"/>
+      <c r="X67" s="10" t="n"/>
+      <c r="Y67" s="10" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
+      <c r="AB67" s="10" t="n"/>
+      <c r="AC67" s="10" t="n"/>
+      <c r="AD67" s="10" t="n"/>
+      <c r="AE67" s="10" t="n"/>
+      <c r="AF67" s="10" t="n"/>
+      <c r="AG67" s="10" t="n"/>
+      <c r="AH67" s="10" t="n"/>
+      <c r="AI67" s="10" t="n"/>
+      <c r="AJ67" s="10" t="n"/>
+      <c r="AK67" s="11" t="n"/>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="B69" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Data Scope Violation）</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="72" customHeight="1">
-      <c r="C69" s="19" t="inlineStr">
+    <row r="70" ht="72" customHeight="1">
+      <c r="C70" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "DATA_SCOPE_VIOLATION",
@@ -6115,101 +6176,101 @@
 }</t>
         </is>
       </c>
-      <c r="D69" s="10" t="n"/>
-      <c r="E69" s="10" t="n"/>
-      <c r="F69" s="10" t="n"/>
-      <c r="G69" s="10" t="n"/>
-      <c r="H69" s="10" t="n"/>
-      <c r="I69" s="10" t="n"/>
-      <c r="J69" s="10" t="n"/>
-      <c r="K69" s="10" t="n"/>
-      <c r="L69" s="10" t="n"/>
-      <c r="M69" s="10" t="n"/>
-      <c r="N69" s="10" t="n"/>
-      <c r="O69" s="10" t="n"/>
-      <c r="P69" s="10" t="n"/>
-      <c r="Q69" s="10" t="n"/>
-      <c r="R69" s="10" t="n"/>
-      <c r="S69" s="10" t="n"/>
-      <c r="T69" s="10" t="n"/>
-      <c r="U69" s="10" t="n"/>
-      <c r="V69" s="10" t="n"/>
-      <c r="W69" s="10" t="n"/>
-      <c r="X69" s="10" t="n"/>
-      <c r="Y69" s="10" t="n"/>
-      <c r="Z69" s="10" t="n"/>
-      <c r="AA69" s="10" t="n"/>
-      <c r="AB69" s="10" t="n"/>
-      <c r="AC69" s="10" t="n"/>
-      <c r="AD69" s="10" t="n"/>
-      <c r="AE69" s="10" t="n"/>
-      <c r="AF69" s="10" t="n"/>
-      <c r="AG69" s="10" t="n"/>
-      <c r="AH69" s="10" t="n"/>
-      <c r="AI69" s="10" t="n"/>
-      <c r="AJ69" s="10" t="n"/>
-      <c r="AK69" s="11" t="n"/>
-    </row>
-    <row r="71" ht="19.5" customHeight="1">
-      <c r="B71" s="40" t="inlineStr">
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="10" t="n"/>
+      <c r="J70" s="10" t="n"/>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="10" t="n"/>
+      <c r="Q70" s="10" t="n"/>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
+      <c r="U70" s="10" t="n"/>
+      <c r="V70" s="10" t="n"/>
+      <c r="W70" s="10" t="n"/>
+      <c r="X70" s="10" t="n"/>
+      <c r="Y70" s="10" t="n"/>
+      <c r="Z70" s="10" t="n"/>
+      <c r="AA70" s="10" t="n"/>
+      <c r="AB70" s="10" t="n"/>
+      <c r="AC70" s="10" t="n"/>
+      <c r="AD70" s="10" t="n"/>
+      <c r="AE70" s="10" t="n"/>
+      <c r="AF70" s="10" t="n"/>
+      <c r="AG70" s="10" t="n"/>
+      <c r="AH70" s="10" t="n"/>
+      <c r="AI70" s="10" t="n"/>
+      <c r="AJ70" s="10" t="n"/>
+      <c r="AK70" s="11" t="n"/>
+    </row>
+    <row r="72" ht="19.5" customHeight="1">
+      <c r="B72" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 404 Not Found）</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="72" customHeight="1">
-      <c r="C72" s="19" t="inlineStr">
+    <row r="73" ht="72" customHeight="1">
+      <c r="C73" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "HANBAITEN_NOT_FOUND",
+  "error_code": "NOT_FOUND",
   "message": "指定された販売店が見つかりません"
 }</t>
         </is>
       </c>
-      <c r="D72" s="10" t="n"/>
-      <c r="E72" s="10" t="n"/>
-      <c r="F72" s="10" t="n"/>
-      <c r="G72" s="10" t="n"/>
-      <c r="H72" s="10" t="n"/>
-      <c r="I72" s="10" t="n"/>
-      <c r="J72" s="10" t="n"/>
-      <c r="K72" s="10" t="n"/>
-      <c r="L72" s="10" t="n"/>
-      <c r="M72" s="10" t="n"/>
-      <c r="N72" s="10" t="n"/>
-      <c r="O72" s="10" t="n"/>
-      <c r="P72" s="10" t="n"/>
-      <c r="Q72" s="10" t="n"/>
-      <c r="R72" s="10" t="n"/>
-      <c r="S72" s="10" t="n"/>
-      <c r="T72" s="10" t="n"/>
-      <c r="U72" s="10" t="n"/>
-      <c r="V72" s="10" t="n"/>
-      <c r="W72" s="10" t="n"/>
-      <c r="X72" s="10" t="n"/>
-      <c r="Y72" s="10" t="n"/>
-      <c r="Z72" s="10" t="n"/>
-      <c r="AA72" s="10" t="n"/>
-      <c r="AB72" s="10" t="n"/>
-      <c r="AC72" s="10" t="n"/>
-      <c r="AD72" s="10" t="n"/>
-      <c r="AE72" s="10" t="n"/>
-      <c r="AF72" s="10" t="n"/>
-      <c r="AG72" s="10" t="n"/>
-      <c r="AH72" s="10" t="n"/>
-      <c r="AI72" s="10" t="n"/>
-      <c r="AJ72" s="10" t="n"/>
-      <c r="AK72" s="11" t="n"/>
-    </row>
-    <row r="74" ht="19.5" customHeight="1">
-      <c r="B74" s="40" t="inlineStr">
+      <c r="D73" s="10" t="n"/>
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="10" t="n"/>
+      <c r="J73" s="10" t="n"/>
+      <c r="K73" s="10" t="n"/>
+      <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="10" t="n"/>
+      <c r="Q73" s="10" t="n"/>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
+      <c r="U73" s="10" t="n"/>
+      <c r="V73" s="10" t="n"/>
+      <c r="W73" s="10" t="n"/>
+      <c r="X73" s="10" t="n"/>
+      <c r="Y73" s="10" t="n"/>
+      <c r="Z73" s="10" t="n"/>
+      <c r="AA73" s="10" t="n"/>
+      <c r="AB73" s="10" t="n"/>
+      <c r="AC73" s="10" t="n"/>
+      <c r="AD73" s="10" t="n"/>
+      <c r="AE73" s="10" t="n"/>
+      <c r="AF73" s="10" t="n"/>
+      <c r="AG73" s="10" t="n"/>
+      <c r="AH73" s="10" t="n"/>
+      <c r="AI73" s="10" t="n"/>
+      <c r="AJ73" s="10" t="n"/>
+      <c r="AK73" s="11" t="n"/>
+    </row>
+    <row r="75" ht="19.5" customHeight="1">
+      <c r="B75" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="72" customHeight="1">
-      <c r="C75" s="19" t="inlineStr">
+    <row r="76" ht="72" customHeight="1">
+      <c r="C76" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -6217,156 +6278,156 @@
 }</t>
         </is>
       </c>
-      <c r="D75" s="10" t="n"/>
-      <c r="E75" s="10" t="n"/>
-      <c r="F75" s="10" t="n"/>
-      <c r="G75" s="10" t="n"/>
-      <c r="H75" s="10" t="n"/>
-      <c r="I75" s="10" t="n"/>
-      <c r="J75" s="10" t="n"/>
-      <c r="K75" s="10" t="n"/>
-      <c r="L75" s="10" t="n"/>
-      <c r="M75" s="10" t="n"/>
-      <c r="N75" s="10" t="n"/>
-      <c r="O75" s="10" t="n"/>
-      <c r="P75" s="10" t="n"/>
-      <c r="Q75" s="10" t="n"/>
-      <c r="R75" s="10" t="n"/>
-      <c r="S75" s="10" t="n"/>
-      <c r="T75" s="10" t="n"/>
-      <c r="U75" s="10" t="n"/>
-      <c r="V75" s="10" t="n"/>
-      <c r="W75" s="10" t="n"/>
-      <c r="X75" s="10" t="n"/>
-      <c r="Y75" s="10" t="n"/>
-      <c r="Z75" s="10" t="n"/>
-      <c r="AA75" s="10" t="n"/>
-      <c r="AB75" s="10" t="n"/>
-      <c r="AC75" s="10" t="n"/>
-      <c r="AD75" s="10" t="n"/>
-      <c r="AE75" s="10" t="n"/>
-      <c r="AF75" s="10" t="n"/>
-      <c r="AG75" s="10" t="n"/>
-      <c r="AH75" s="10" t="n"/>
-      <c r="AI75" s="10" t="n"/>
-      <c r="AJ75" s="10" t="n"/>
-      <c r="AK75" s="11" t="n"/>
-    </row>
-    <row r="77" ht="19.5" customHeight="1"/>
-    <row r="78" ht="19.5" customHeight="1">
-      <c r="A78" s="27" t="inlineStr">
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="10" t="n"/>
+      <c r="J76" s="10" t="n"/>
+      <c r="K76" s="10" t="n"/>
+      <c r="L76" s="10" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="10" t="n"/>
+      <c r="Q76" s="10" t="n"/>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="10" t="n"/>
+      <c r="U76" s="10" t="n"/>
+      <c r="V76" s="10" t="n"/>
+      <c r="W76" s="10" t="n"/>
+      <c r="X76" s="10" t="n"/>
+      <c r="Y76" s="10" t="n"/>
+      <c r="Z76" s="10" t="n"/>
+      <c r="AA76" s="10" t="n"/>
+      <c r="AB76" s="10" t="n"/>
+      <c r="AC76" s="10" t="n"/>
+      <c r="AD76" s="10" t="n"/>
+      <c r="AE76" s="10" t="n"/>
+      <c r="AF76" s="10" t="n"/>
+      <c r="AG76" s="10" t="n"/>
+      <c r="AH76" s="10" t="n"/>
+      <c r="AI76" s="10" t="n"/>
+      <c r="AJ76" s="10" t="n"/>
+      <c r="AK76" s="11" t="n"/>
+    </row>
+    <row r="78" ht="19.5" customHeight="1"/>
+    <row r="79" ht="19.5" customHeight="1">
+      <c r="A79" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="B79" s="27" t="inlineStr">
+    <row r="80" ht="18" customHeight="1">
+      <c r="B80" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="C80" s="41" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="C81" s="41" t="inlineStr">
         <is>
           <t>パスパラメータの検証：</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="D81" s="41" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="D82" s="41" t="inlineStr">
         <is>
           <t>hanbaiten_id：数値型チェック、必須チェック</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="C82" s="41" t="inlineStr">
+    <row r="83" ht="18" customHeight="1">
+      <c r="C83" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="D83" s="41" t="inlineStr">
+    <row r="84" ht="18" customHeight="1">
+      <c r="D84" s="41" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="B84" s="27" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="B85" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="C85" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="C86" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="C87" s="41" t="inlineStr">
         <is>
+          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="C88" s="41" t="inlineStr">
+        <is>
           <t>権限チェック：`hanbaiten.view` を保持しているか確認する。</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="36" customHeight="1">
-      <c r="D88" s="41" t="inlineStr">
+    <row r="89" ht="36" customHeight="1">
+      <c r="D89" s="41" t="inlineStr">
         <is>
           <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="C89" s="41" t="inlineStr">
+    <row r="90" ht="18" customHeight="1">
+      <c r="C90" s="41" t="inlineStr">
         <is>
           <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="B90" s="27" t="inlineStr">
+    <row r="91" ht="18" customHeight="1">
+      <c r="B91" s="27" t="inlineStr">
         <is>
           <t>4.3 データ取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="C91" s="41" t="inlineStr">
-        <is>
-          <t>ログインユーザーのスコープを取得する（ja_id）。</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="C92" s="41" t="inlineStr">
         <is>
+          <t>ログインユーザーのスコープを取得する（ja_id）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="C93" s="41" t="inlineStr">
+        <is>
           <t>以下の条件でデータを取得する。</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="198" customHeight="1">
-      <c r="C93" s="42" t="inlineStr">
+    <row r="94" ht="198" customHeight="1">
+      <c r="C94" s="42" t="inlineStr">
         <is>
           <t>SELECT hanbaiten_id, ja_id, hanbaiten_code, hanbaiten_name,
        hanbaiten_name_kana, torihikisaki_no, yubin_no, address,
        tel, fax, shocho_name, itaku_kubun, haitatsuryo_tanka_id,
        haitatsuryo_shiharai_cycle, tesuryo_kubun, tesuryo_amount,
        bank_code, bank_name, bank_branch_code, bank_branch_name,
-       yokin_shubetsu, koza_no, koza_meigi, biko,
+       yokin_shubetsu, koza_no, koza_meigi, haiten_flg, biko,
        created_at, updated_at
 FROM m_hanbaiten
 WHERE hanbaiten_id = :hanbaiten_id
@@ -6374,98 +6435,96 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D93" s="10" t="n"/>
-      <c r="E93" s="10" t="n"/>
-      <c r="F93" s="10" t="n"/>
-      <c r="G93" s="10" t="n"/>
-      <c r="H93" s="10" t="n"/>
-      <c r="I93" s="10" t="n"/>
-      <c r="J93" s="10" t="n"/>
-      <c r="K93" s="10" t="n"/>
-      <c r="L93" s="10" t="n"/>
-      <c r="M93" s="10" t="n"/>
-      <c r="N93" s="10" t="n"/>
-      <c r="O93" s="10" t="n"/>
-      <c r="P93" s="10" t="n"/>
-      <c r="Q93" s="10" t="n"/>
-      <c r="R93" s="10" t="n"/>
-      <c r="S93" s="10" t="n"/>
-      <c r="T93" s="10" t="n"/>
-      <c r="U93" s="10" t="n"/>
-      <c r="V93" s="10" t="n"/>
-      <c r="W93" s="10" t="n"/>
-      <c r="X93" s="10" t="n"/>
-      <c r="Y93" s="10" t="n"/>
-      <c r="Z93" s="10" t="n"/>
-      <c r="AA93" s="10" t="n"/>
-      <c r="AB93" s="10" t="n"/>
-      <c r="AC93" s="10" t="n"/>
-      <c r="AD93" s="10" t="n"/>
-      <c r="AE93" s="10" t="n"/>
-      <c r="AF93" s="10" t="n"/>
-      <c r="AG93" s="10" t="n"/>
-      <c r="AH93" s="10" t="n"/>
-      <c r="AI93" s="10" t="n"/>
-      <c r="AJ93" s="10" t="n"/>
-      <c r="AK93" s="11" t="n"/>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="C94" s="41" t="inlineStr">
-        <is>
-          <t>レコードが存在しない場合：HTTP 404 (`HANBAITEN_NOT_FOUND`)</t>
-        </is>
-      </c>
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="10" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="10" t="n"/>
+      <c r="I94" s="10" t="n"/>
+      <c r="J94" s="10" t="n"/>
+      <c r="K94" s="10" t="n"/>
+      <c r="L94" s="10" t="n"/>
+      <c r="M94" s="10" t="n"/>
+      <c r="N94" s="10" t="n"/>
+      <c r="O94" s="10" t="n"/>
+      <c r="P94" s="10" t="n"/>
+      <c r="Q94" s="10" t="n"/>
+      <c r="R94" s="10" t="n"/>
+      <c r="S94" s="10" t="n"/>
+      <c r="T94" s="10" t="n"/>
+      <c r="U94" s="10" t="n"/>
+      <c r="V94" s="10" t="n"/>
+      <c r="W94" s="10" t="n"/>
+      <c r="X94" s="10" t="n"/>
+      <c r="Y94" s="10" t="n"/>
+      <c r="Z94" s="10" t="n"/>
+      <c r="AA94" s="10" t="n"/>
+      <c r="AB94" s="10" t="n"/>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="10" t="n"/>
+      <c r="AF94" s="10" t="n"/>
+      <c r="AG94" s="10" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="10" t="n"/>
+      <c r="AK94" s="11" t="n"/>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="C95" s="41" t="inlineStr">
         <is>
+          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="C96" s="41" t="inlineStr">
+        <is>
           <t>ja_id が一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="B96" s="27" t="inlineStr">
+    <row r="97" ht="18" customHeight="1">
+      <c r="B97" s="27" t="inlineStr">
         <is>
           <t>4.4 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="C97" s="41" t="inlineStr">
+    <row r="98" ht="18" customHeight="1">
+      <c r="C98" s="41" t="inlineStr">
         <is>
           <t>data オブジェクトを含むJSONを返却する。</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="B98" s="27" t="inlineStr">
+    <row r="99" ht="18" customHeight="1">
+      <c r="B99" s="27" t="inlineStr">
         <is>
           <t>4.5 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="C99" s="41" t="inlineStr">
+    <row r="100" ht="18" customHeight="1">
+      <c r="C100" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="261">
+  <mergeCells count="267">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="Y27:AE27"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="Y36:AE36"/>
-    <mergeCell ref="B62:I62"/>
-    <mergeCell ref="C66:AK66"/>
     <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="B72:I72"/>
     <mergeCell ref="D48:L48"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M32:P32"/>
@@ -6475,48 +6534,43 @@
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="C86:AK86"/>
     <mergeCell ref="T53:X53"/>
-    <mergeCell ref="B56:I56"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="M46:P46"/>
+    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
+    <mergeCell ref="D82:AK82"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="Y52:AE52"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="AF50:AK50"/>
+    <mergeCell ref="T55:X55"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C85:AK85"/>
+    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="C94:AK94"/>
-    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="D33:L33"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="D51:L51"/>
     <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="D35:L35"/>
     <mergeCell ref="M54:P54"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
-    <mergeCell ref="B65:I65"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
     <mergeCell ref="AF34:AK34"/>
-    <mergeCell ref="B74:I74"/>
-    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="C95:AK95"/>
     <mergeCell ref="D34:L34"/>
-    <mergeCell ref="A78:AK78"/>
-    <mergeCell ref="C95:AK95"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="T34:X34"/>
@@ -6524,14 +6578,16 @@
     <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="AF49:AK49"/>
+    <mergeCell ref="C70:AK70"/>
+    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="D36:L36"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="T30:X30"/>
+    <mergeCell ref="B75:I75"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="AF44:AK44"/>
-    <mergeCell ref="B59:I59"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="M47:P47"/>
     <mergeCell ref="Z1:AC1"/>
@@ -6540,6 +6596,7 @@
     <mergeCell ref="D47:L47"/>
     <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="B12:I12"/>
+    <mergeCell ref="AF55:AK55"/>
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="D37:L37"/>
@@ -6547,7 +6604,9 @@
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="T54:X54"/>
     <mergeCell ref="AC22:AE22"/>
+    <mergeCell ref="C88:AK88"/>
     <mergeCell ref="Y53:AE53"/>
+    <mergeCell ref="D89:AK89"/>
     <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF41:AK41"/>
@@ -6555,18 +6614,16 @@
     <mergeCell ref="AF35:AK35"/>
     <mergeCell ref="M44:P44"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="D88:AK88"/>
     <mergeCell ref="Q48:S48"/>
     <mergeCell ref="B14:I18"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="D29:L29"/>
-    <mergeCell ref="C99:AK99"/>
+    <mergeCell ref="Y55:AE55"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="D38:L38"/>
     <mergeCell ref="T40:X40"/>
-    <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y30:AE30"/>
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="M51:P51"/>
@@ -6576,13 +6633,14 @@
     <mergeCell ref="Y29:AE29"/>
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="A25:AK25"/>
+    <mergeCell ref="B97:AK97"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="Y31:AE31"/>
+    <mergeCell ref="C61:AK61"/>
     <mergeCell ref="T46:X46"/>
-    <mergeCell ref="B90:AK90"/>
+    <mergeCell ref="B63:I63"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="Y28:AE28"/>
@@ -6593,14 +6651,16 @@
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="D49:L49"/>
-    <mergeCell ref="C72:AK72"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="Q50:S50"/>
+    <mergeCell ref="C96:AK96"/>
     <mergeCell ref="T32:X32"/>
+    <mergeCell ref="B66:I66"/>
+    <mergeCell ref="T45:X45"/>
     <mergeCell ref="C87:AK87"/>
-    <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="Q34:S34"/>
@@ -6611,9 +6671,8 @@
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
     <mergeCell ref="A20:AK20"/>
-    <mergeCell ref="C82:AK82"/>
+    <mergeCell ref="C98:AK98"/>
     <mergeCell ref="M50:P50"/>
-    <mergeCell ref="C29:C54"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
@@ -6622,20 +6681,22 @@
     <mergeCell ref="T50:X50"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="T44:X44"/>
-    <mergeCell ref="C89:AK89"/>
+    <mergeCell ref="C64:AK64"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M34:P34"/>
     <mergeCell ref="Y43:AE43"/>
+    <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
+    <mergeCell ref="M55:P55"/>
     <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="D55:L55"/>
     <mergeCell ref="D30:L30"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
-    <mergeCell ref="C63:AK63"/>
-    <mergeCell ref="B84:AK84"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="T51:X51"/>
+    <mergeCell ref="B69:I69"/>
     <mergeCell ref="C93:AK93"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
@@ -6645,6 +6706,7 @@
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="Y44:AE44"/>
+    <mergeCell ref="B80:AK80"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
@@ -6660,50 +6722,55 @@
     <mergeCell ref="T27:X27"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="T36:X36"/>
+    <mergeCell ref="Q55:S55"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="C67:AK67"/>
     <mergeCell ref="Y46:AE46"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M41:P41"/>
-    <mergeCell ref="B96:AK96"/>
     <mergeCell ref="D32:L32"/>
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="Y48:AE48"/>
-    <mergeCell ref="B71:I71"/>
+    <mergeCell ref="C83:AK83"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="C92:AK92"/>
-    <mergeCell ref="B98:AK98"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="Y32:AE32"/>
     <mergeCell ref="D43:L43"/>
-    <mergeCell ref="D83:AK83"/>
     <mergeCell ref="Y42:AE42"/>
-    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="Y47:AE47"/>
+    <mergeCell ref="B60:I60"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="B99:AK99"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="D50:L50"/>
+    <mergeCell ref="D84:AK84"/>
     <mergeCell ref="D44:L44"/>
     <mergeCell ref="Q53:S53"/>
+    <mergeCell ref="C29:C55"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="A79:AK79"/>
+    <mergeCell ref="C90:AK90"/>
     <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="C60:AK60"/>
+    <mergeCell ref="B85:AK85"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="M22:P22"/>
     <mergeCell ref="Y50:AE50"/>
+    <mergeCell ref="C76:AK76"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="Q52:S52"/>
@@ -6725,7 +6792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK144"/>
+  <dimension ref="A1:AK146"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -6886,7 +6953,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/16</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7236,7 +7303,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -7433,7 +7500,7 @@
       <c r="B18" s="35" t="n"/>
       <c r="I18" s="36" t="n"/>
       <c r="J18" s="17" t="n">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="K18" s="10" t="n"/>
       <c r="L18" s="10" t="n"/>
@@ -8916,7 +8983,7 @@
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t>biko</t>
+          <t>haiten_flg</t>
         </is>
       </c>
       <c r="D45" s="10" t="n"/>
@@ -8930,7 +8997,7 @@
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N45" s="10" t="n"/>
@@ -8961,7 +9028,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>廃店フラグ（true:廃店, false:営業中、省略時はfalse）</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -8970,88 +9037,84 @@
       <c r="AJ45" s="10" t="n"/>
       <c r="AK45" s="11" t="n"/>
     </row>
-    <row r="46" ht="19.5" customHeight="1"/>
-    <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="27" t="inlineStr">
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="31" t="n">
+        <v>23</v>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>biko</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="10" t="n"/>
+      <c r="K46" s="10" t="n"/>
+      <c r="L46" s="11" t="n"/>
+      <c r="M46" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N46" s="10" t="n"/>
+      <c r="O46" s="10" t="n"/>
+      <c r="P46" s="11" t="n"/>
+      <c r="Q46" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R46" s="10" t="n"/>
+      <c r="S46" s="11" t="n"/>
+      <c r="T46" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U46" s="10" t="n"/>
+      <c r="V46" s="10" t="n"/>
+      <c r="W46" s="10" t="n"/>
+      <c r="X46" s="11" t="n"/>
+      <c r="Y46" s="17" t="inlineStr"/>
+      <c r="Z46" s="10" t="n"/>
+      <c r="AA46" s="10" t="n"/>
+      <c r="AB46" s="11" t="n"/>
+      <c r="AC46" s="17" t="inlineStr"/>
+      <c r="AD46" s="10" t="n"/>
+      <c r="AE46" s="11" t="n"/>
+      <c r="AF46" s="19" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="AG46" s="10" t="n"/>
+      <c r="AH46" s="10" t="n"/>
+      <c r="AI46" s="10" t="n"/>
+      <c r="AJ46" s="10" t="n"/>
+      <c r="AK46" s="11" t="n"/>
+    </row>
+    <row r="47" ht="19.5" customHeight="1"/>
+    <row r="48" ht="19.5" customHeight="1">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="19.5" customHeight="1"/>
-    <row r="49" ht="19.5" customHeight="1">
-      <c r="B49" s="30" t="inlineStr">
+    <row r="49" ht="19.5" customHeight="1"/>
+    <row r="50" ht="19.5" customHeight="1">
+      <c r="B50" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="10" t="n"/>
-      <c r="G49" s="10" t="n"/>
-      <c r="H49" s="10" t="n"/>
-      <c r="I49" s="10" t="n"/>
-      <c r="J49" s="10" t="n"/>
-      <c r="K49" s="10" t="n"/>
-      <c r="L49" s="11" t="n"/>
-      <c r="M49" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N49" s="10" t="n"/>
-      <c r="O49" s="10" t="n"/>
-      <c r="P49" s="11" t="n"/>
-      <c r="Q49" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R49" s="10" t="n"/>
-      <c r="S49" s="11" t="n"/>
-      <c r="T49" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U49" s="10" t="n"/>
-      <c r="V49" s="10" t="n"/>
-      <c r="W49" s="10" t="n"/>
-      <c r="X49" s="11" t="n"/>
-      <c r="Y49" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z49" s="10" t="n"/>
-      <c r="AA49" s="10" t="n"/>
-      <c r="AB49" s="10" t="n"/>
-      <c r="AC49" s="10" t="n"/>
-      <c r="AD49" s="10" t="n"/>
-      <c r="AE49" s="11" t="n"/>
-      <c r="AF49" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG49" s="10" t="n"/>
-      <c r="AH49" s="10" t="n"/>
-      <c r="AI49" s="10" t="n"/>
-      <c r="AJ49" s="10" t="n"/>
-      <c r="AK49" s="11" t="n"/>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="B50" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
         </is>
       </c>
       <c r="D50" s="10" t="n"/>
@@ -9063,29 +9126,33 @@
       <c r="J50" s="10" t="n"/>
       <c r="K50" s="10" t="n"/>
       <c r="L50" s="11" t="n"/>
-      <c r="M50" s="17" t="inlineStr">
-        <is>
-          <t>Object</t>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N50" s="10" t="n"/>
       <c r="O50" s="10" t="n"/>
       <c r="P50" s="11" t="n"/>
-      <c r="Q50" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q50" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R50" s="10" t="n"/>
       <c r="S50" s="11" t="n"/>
-      <c r="T50" s="17" t="inlineStr"/>
+      <c r="T50" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U50" s="10" t="n"/>
       <c r="V50" s="10" t="n"/>
       <c r="W50" s="10" t="n"/>
       <c r="X50" s="11" t="n"/>
-      <c r="Y50" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y50" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z50" s="10" t="n"/>
@@ -9094,9 +9161,9 @@
       <c r="AC50" s="10" t="n"/>
       <c r="AD50" s="10" t="n"/>
       <c r="AE50" s="11" t="n"/>
-      <c r="AF50" s="19" t="inlineStr">
-        <is>
-          <t>登録された販売店データ</t>
+      <c r="AF50" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -9107,14 +9174,14 @@
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C51" s="37" t="n"/>
-      <c r="D51" s="19" t="inlineStr">
-        <is>
-          <t>hanbaiten_id</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n"/>
       <c r="E51" s="10" t="n"/>
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
@@ -9125,7 +9192,7 @@
       <c r="L51" s="11" t="n"/>
       <c r="M51" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N51" s="10" t="n"/>
@@ -9156,7 +9223,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>販売店ID</t>
+          <t>登録された販売店データ</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -9167,12 +9234,12 @@
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C52" s="38" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C52" s="37" t="n"/>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>hanbaiten_id</t>
         </is>
       </c>
       <c r="E52" s="10" t="n"/>
@@ -9216,7 +9283,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>販売店ID</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -9227,12 +9294,12 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53" s="38" t="n"/>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_code</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
@@ -9245,7 +9312,7 @@
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N53" s="10" t="n"/>
@@ -9276,7 +9343,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>販売店コード</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -9287,12 +9354,12 @@
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54" s="38" t="n"/>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_name</t>
+          <t>hanbaiten_code</t>
         </is>
       </c>
       <c r="E54" s="10" t="n"/>
@@ -9336,7 +9403,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>販売店名</t>
+          <t>販売店コード</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -9347,12 +9414,12 @@
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="38" t="n"/>
       <c r="D55" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_name_kana</t>
+          <t>hanbaiten_name</t>
         </is>
       </c>
       <c r="E55" s="10" t="n"/>
@@ -9385,7 +9452,7 @@
       <c r="X55" s="11" t="n"/>
       <c r="Y55" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z55" s="10" t="n"/>
@@ -9396,7 +9463,7 @@
       <c r="AE55" s="11" t="n"/>
       <c r="AF55" s="19" t="inlineStr">
         <is>
-          <t>販売店名（カナ）</t>
+          <t>販売店名</t>
         </is>
       </c>
       <c r="AG55" s="10" t="n"/>
@@ -9407,12 +9474,12 @@
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56" s="38" t="n"/>
       <c r="D56" s="19" t="inlineStr">
         <is>
-          <t>torihikisaki_no</t>
+          <t>hanbaiten_name_kana</t>
         </is>
       </c>
       <c r="E56" s="10" t="n"/>
@@ -9445,7 +9512,7 @@
       <c r="X56" s="11" t="n"/>
       <c r="Y56" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z56" s="10" t="n"/>
@@ -9456,7 +9523,7 @@
       <c r="AE56" s="11" t="n"/>
       <c r="AF56" s="19" t="inlineStr">
         <is>
-          <t>適格請求書発行事業者番号</t>
+          <t>販売店名（カナ）</t>
         </is>
       </c>
       <c r="AG56" s="10" t="n"/>
@@ -9467,12 +9534,12 @@
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C57" s="38" t="n"/>
       <c r="D57" s="19" t="inlineStr">
         <is>
-          <t>yubin_no</t>
+          <t>torihikisaki_no</t>
         </is>
       </c>
       <c r="E57" s="10" t="n"/>
@@ -9516,7 +9583,7 @@
       <c r="AE57" s="11" t="n"/>
       <c r="AF57" s="19" t="inlineStr">
         <is>
-          <t>郵便番号</t>
+          <t>適格請求書発行事業者番号</t>
         </is>
       </c>
       <c r="AG57" s="10" t="n"/>
@@ -9527,12 +9594,12 @@
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C58" s="38" t="n"/>
       <c r="D58" s="19" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>yubin_no</t>
         </is>
       </c>
       <c r="E58" s="10" t="n"/>
@@ -9565,7 +9632,7 @@
       <c r="X58" s="11" t="n"/>
       <c r="Y58" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z58" s="10" t="n"/>
@@ -9576,7 +9643,7 @@
       <c r="AE58" s="11" t="n"/>
       <c r="AF58" s="19" t="inlineStr">
         <is>
-          <t>住所</t>
+          <t>郵便番号</t>
         </is>
       </c>
       <c r="AG58" s="10" t="n"/>
@@ -9587,12 +9654,12 @@
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C59" s="38" t="n"/>
       <c r="D59" s="19" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>address</t>
         </is>
       </c>
       <c r="E59" s="10" t="n"/>
@@ -9625,7 +9692,7 @@
       <c r="X59" s="11" t="n"/>
       <c r="Y59" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z59" s="10" t="n"/>
@@ -9636,7 +9703,7 @@
       <c r="AE59" s="11" t="n"/>
       <c r="AF59" s="19" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>住所</t>
         </is>
       </c>
       <c r="AG59" s="10" t="n"/>
@@ -9647,12 +9714,12 @@
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C60" s="38" t="n"/>
       <c r="D60" s="19" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="E60" s="10" t="n"/>
@@ -9685,7 +9752,7 @@
       <c r="X60" s="11" t="n"/>
       <c r="Y60" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z60" s="10" t="n"/>
@@ -9696,7 +9763,7 @@
       <c r="AE60" s="11" t="n"/>
       <c r="AF60" s="19" t="inlineStr">
         <is>
-          <t>FAX番号</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="AG60" s="10" t="n"/>
@@ -9707,12 +9774,12 @@
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C61" s="38" t="n"/>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>shocho_name</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="E61" s="10" t="n"/>
@@ -9745,7 +9812,7 @@
       <c r="X61" s="11" t="n"/>
       <c r="Y61" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z61" s="10" t="n"/>
@@ -9756,7 +9823,7 @@
       <c r="AE61" s="11" t="n"/>
       <c r="AF61" s="19" t="inlineStr">
         <is>
-          <t>所長名</t>
+          <t>FAX番号</t>
         </is>
       </c>
       <c r="AG61" s="10" t="n"/>
@@ -9767,12 +9834,12 @@
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62" s="38" t="n"/>
       <c r="D62" s="19" t="inlineStr">
         <is>
-          <t>itaku_kubun</t>
+          <t>shocho_name</t>
         </is>
       </c>
       <c r="E62" s="10" t="n"/>
@@ -9785,7 +9852,7 @@
       <c r="L62" s="11" t="n"/>
       <c r="M62" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N62" s="10" t="n"/>
@@ -9816,7 +9883,7 @@
       <c r="AE62" s="11" t="n"/>
       <c r="AF62" s="19" t="inlineStr">
         <is>
-          <t>委託区分（1:振込, 2:日農委託, 9:その他）</t>
+          <t>所長名</t>
         </is>
       </c>
       <c r="AG62" s="10" t="n"/>
@@ -9827,12 +9894,12 @@
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C63" s="38" t="n"/>
       <c r="D63" s="19" t="inlineStr">
         <is>
-          <t>haitatsuryo_tanka_id</t>
+          <t>itaku_kubun</t>
         </is>
       </c>
       <c r="E63" s="10" t="n"/>
@@ -9876,7 +9943,7 @@
       <c r="AE63" s="11" t="n"/>
       <c r="AF63" s="19" t="inlineStr">
         <is>
-          <t>配達手数料単価ID</t>
+          <t>委託区分（1:振込, 2:日農委託, 9:その他）</t>
         </is>
       </c>
       <c r="AG63" s="10" t="n"/>
@@ -9887,12 +9954,12 @@
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="B64" s="31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C64" s="38" t="n"/>
       <c r="D64" s="19" t="inlineStr">
         <is>
-          <t>haitatsuryo_shiharai_cycle</t>
+          <t>haitatsuryo_tanka_id</t>
         </is>
       </c>
       <c r="E64" s="10" t="n"/>
@@ -9936,7 +10003,7 @@
       <c r="AE64" s="11" t="n"/>
       <c r="AF64" s="19" t="inlineStr">
         <is>
-          <t>配達手数料支払サイクル（月数）</t>
+          <t>配達手数料単価ID</t>
         </is>
       </c>
       <c r="AG64" s="10" t="n"/>
@@ -9947,12 +10014,12 @@
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="B65" s="31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C65" s="38" t="n"/>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t>tesuryo_kubun</t>
+          <t>haitatsuryo_shiharai_cycle</t>
         </is>
       </c>
       <c r="E65" s="10" t="n"/>
@@ -9996,7 +10063,7 @@
       <c r="AE65" s="11" t="n"/>
       <c r="AF65" s="19" t="inlineStr">
         <is>
-          <t>手数料区分（1:JA, 2:販売店）</t>
+          <t>配達手数料支払サイクル（月数）</t>
         </is>
       </c>
       <c r="AG65" s="10" t="n"/>
@@ -10007,12 +10074,12 @@
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="B66" s="31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C66" s="38" t="n"/>
       <c r="D66" s="19" t="inlineStr">
         <is>
-          <t>tesuryo_amount</t>
+          <t>tesuryo_kubun</t>
         </is>
       </c>
       <c r="E66" s="10" t="n"/>
@@ -10038,9 +10105,7 @@
       </c>
       <c r="R66" s="10" t="n"/>
       <c r="S66" s="11" t="n"/>
-      <c r="T66" s="17" t="n">
-        <v>0</v>
-      </c>
+      <c r="T66" s="17" t="inlineStr"/>
       <c r="U66" s="10" t="n"/>
       <c r="V66" s="10" t="n"/>
       <c r="W66" s="10" t="n"/>
@@ -10058,7 +10123,7 @@
       <c r="AE66" s="11" t="n"/>
       <c r="AF66" s="19" t="inlineStr">
         <is>
-          <t>手数料金額</t>
+          <t>手数料区分（1:JA, 2:販売店）</t>
         </is>
       </c>
       <c r="AG66" s="10" t="n"/>
@@ -10069,12 +10134,12 @@
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="B67" s="31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C67" s="38" t="n"/>
       <c r="D67" s="19" t="inlineStr">
         <is>
-          <t>bank_code</t>
+          <t>tesuryo_amount</t>
         </is>
       </c>
       <c r="E67" s="10" t="n"/>
@@ -10087,7 +10152,7 @@
       <c r="L67" s="11" t="n"/>
       <c r="M67" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N67" s="10" t="n"/>
@@ -10100,7 +10165,9 @@
       </c>
       <c r="R67" s="10" t="n"/>
       <c r="S67" s="11" t="n"/>
-      <c r="T67" s="17" t="inlineStr"/>
+      <c r="T67" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="U67" s="10" t="n"/>
       <c r="V67" s="10" t="n"/>
       <c r="W67" s="10" t="n"/>
@@ -10118,7 +10185,7 @@
       <c r="AE67" s="11" t="n"/>
       <c r="AF67" s="19" t="inlineStr">
         <is>
-          <t>銀行コード</t>
+          <t>手数料金額</t>
         </is>
       </c>
       <c r="AG67" s="10" t="n"/>
@@ -10129,12 +10196,12 @@
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="B68" s="31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C68" s="38" t="n"/>
       <c r="D68" s="19" t="inlineStr">
         <is>
-          <t>bank_name</t>
+          <t>bank_code</t>
         </is>
       </c>
       <c r="E68" s="10" t="n"/>
@@ -10167,7 +10234,7 @@
       <c r="X68" s="11" t="n"/>
       <c r="Y68" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z68" s="10" t="n"/>
@@ -10178,7 +10245,7 @@
       <c r="AE68" s="11" t="n"/>
       <c r="AF68" s="19" t="inlineStr">
         <is>
-          <t>銀行名</t>
+          <t>銀行コード</t>
         </is>
       </c>
       <c r="AG68" s="10" t="n"/>
@@ -10189,12 +10256,12 @@
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="B69" s="31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C69" s="38" t="n"/>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t>bank_branch_code</t>
+          <t>bank_name</t>
         </is>
       </c>
       <c r="E69" s="10" t="n"/>
@@ -10227,7 +10294,7 @@
       <c r="X69" s="11" t="n"/>
       <c r="Y69" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z69" s="10" t="n"/>
@@ -10238,7 +10305,7 @@
       <c r="AE69" s="11" t="n"/>
       <c r="AF69" s="19" t="inlineStr">
         <is>
-          <t>支店コード</t>
+          <t>銀行名</t>
         </is>
       </c>
       <c r="AG69" s="10" t="n"/>
@@ -10249,12 +10316,12 @@
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="B70" s="31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C70" s="38" t="n"/>
       <c r="D70" s="19" t="inlineStr">
         <is>
-          <t>bank_branch_name</t>
+          <t>bank_branch_code</t>
         </is>
       </c>
       <c r="E70" s="10" t="n"/>
@@ -10298,7 +10365,7 @@
       <c r="AE70" s="11" t="n"/>
       <c r="AF70" s="19" t="inlineStr">
         <is>
-          <t>支店名</t>
+          <t>支店コード</t>
         </is>
       </c>
       <c r="AG70" s="10" t="n"/>
@@ -10309,12 +10376,12 @@
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="B71" s="31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C71" s="38" t="n"/>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t>yokin_shubetsu</t>
+          <t>bank_branch_name</t>
         </is>
       </c>
       <c r="E71" s="10" t="n"/>
@@ -10327,7 +10394,7 @@
       <c r="L71" s="11" t="n"/>
       <c r="M71" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N71" s="10" t="n"/>
@@ -10358,7 +10425,7 @@
       <c r="AE71" s="11" t="n"/>
       <c r="AF71" s="19" t="inlineStr">
         <is>
-          <t>預金種別（1:普通, 2:当座）</t>
+          <t>支店名</t>
         </is>
       </c>
       <c r="AG71" s="10" t="n"/>
@@ -10369,12 +10436,12 @@
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C72" s="38" t="n"/>
       <c r="D72" s="19" t="inlineStr">
         <is>
-          <t>koza_no</t>
+          <t>yokin_shubetsu</t>
         </is>
       </c>
       <c r="E72" s="10" t="n"/>
@@ -10387,7 +10454,7 @@
       <c r="L72" s="11" t="n"/>
       <c r="M72" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N72" s="10" t="n"/>
@@ -10418,7 +10485,7 @@
       <c r="AE72" s="11" t="n"/>
       <c r="AF72" s="19" t="inlineStr">
         <is>
-          <t>口座番号</t>
+          <t>預金種別（1:普通, 2:当座）</t>
         </is>
       </c>
       <c r="AG72" s="10" t="n"/>
@@ -10429,12 +10496,12 @@
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="B73" s="31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C73" s="38" t="n"/>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t>koza_meigi</t>
+          <t>koza_no</t>
         </is>
       </c>
       <c r="E73" s="10" t="n"/>
@@ -10478,7 +10545,7 @@
       <c r="AE73" s="11" t="n"/>
       <c r="AF73" s="19" t="inlineStr">
         <is>
-          <t>口座名義</t>
+          <t>口座番号</t>
         </is>
       </c>
       <c r="AG73" s="10" t="n"/>
@@ -10489,12 +10556,12 @@
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="B74" s="31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C74" s="38" t="n"/>
       <c r="D74" s="19" t="inlineStr">
         <is>
-          <t>biko</t>
+          <t>koza_meigi</t>
         </is>
       </c>
       <c r="E74" s="10" t="n"/>
@@ -10538,7 +10605,7 @@
       <c r="AE74" s="11" t="n"/>
       <c r="AF74" s="19" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>口座名義</t>
         </is>
       </c>
       <c r="AG74" s="10" t="n"/>
@@ -10549,12 +10616,12 @@
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C75" s="38" t="n"/>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>haiten_flg</t>
         </is>
       </c>
       <c r="E75" s="10" t="n"/>
@@ -10567,7 +10634,7 @@
       <c r="L75" s="11" t="n"/>
       <c r="M75" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N75" s="10" t="n"/>
@@ -10580,11 +10647,7 @@
       </c>
       <c r="R75" s="10" t="n"/>
       <c r="S75" s="11" t="n"/>
-      <c r="T75" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T75" s="17" t="inlineStr"/>
       <c r="U75" s="10" t="n"/>
       <c r="V75" s="10" t="n"/>
       <c r="W75" s="10" t="n"/>
@@ -10602,7 +10665,7 @@
       <c r="AE75" s="11" t="n"/>
       <c r="AF75" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>廃店フラグ（true:廃店, false:営業中）</t>
         </is>
       </c>
       <c r="AG75" s="10" t="n"/>
@@ -10613,12 +10676,12 @@
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="B76" s="31" t="n">
-        <v>27</v>
-      </c>
-      <c r="C76" s="39" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="C76" s="38" t="n"/>
       <c r="D76" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>biko</t>
         </is>
       </c>
       <c r="E76" s="10" t="n"/>
@@ -10644,18 +10707,14 @@
       </c>
       <c r="R76" s="10" t="n"/>
       <c r="S76" s="11" t="n"/>
-      <c r="T76" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T76" s="17" t="inlineStr"/>
       <c r="U76" s="10" t="n"/>
       <c r="V76" s="10" t="n"/>
       <c r="W76" s="10" t="n"/>
       <c r="X76" s="11" t="n"/>
       <c r="Y76" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z76" s="10" t="n"/>
@@ -10666,7 +10725,7 @@
       <c r="AE76" s="11" t="n"/>
       <c r="AF76" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="AG76" s="10" t="n"/>
@@ -10675,16 +10734,144 @@
       <c r="AJ76" s="10" t="n"/>
       <c r="AK76" s="11" t="n"/>
     </row>
-    <row r="77" ht="19.5" customHeight="1"/>
-    <row r="78" ht="19.5" customHeight="1">
-      <c r="B78" s="40" t="inlineStr">
+    <row r="77" ht="18" customHeight="1">
+      <c r="B77" s="31" t="n">
+        <v>27</v>
+      </c>
+      <c r="C77" s="38" t="n"/>
+      <c r="D77" s="19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="10" t="n"/>
+      <c r="J77" s="10" t="n"/>
+      <c r="K77" s="10" t="n"/>
+      <c r="L77" s="11" t="n"/>
+      <c r="M77" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="11" t="n"/>
+      <c r="Q77" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="11" t="n"/>
+      <c r="T77" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U77" s="10" t="n"/>
+      <c r="V77" s="10" t="n"/>
+      <c r="W77" s="10" t="n"/>
+      <c r="X77" s="11" t="n"/>
+      <c r="Y77" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z77" s="10" t="n"/>
+      <c r="AA77" s="10" t="n"/>
+      <c r="AB77" s="10" t="n"/>
+      <c r="AC77" s="10" t="n"/>
+      <c r="AD77" s="10" t="n"/>
+      <c r="AE77" s="11" t="n"/>
+      <c r="AF77" s="19" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="AG77" s="10" t="n"/>
+      <c r="AH77" s="10" t="n"/>
+      <c r="AI77" s="10" t="n"/>
+      <c r="AJ77" s="10" t="n"/>
+      <c r="AK77" s="11" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="B78" s="31" t="n">
+        <v>28</v>
+      </c>
+      <c r="C78" s="39" t="n"/>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="10" t="n"/>
+      <c r="J78" s="10" t="n"/>
+      <c r="K78" s="10" t="n"/>
+      <c r="L78" s="11" t="n"/>
+      <c r="M78" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="11" t="n"/>
+      <c r="Q78" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="11" t="n"/>
+      <c r="T78" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U78" s="10" t="n"/>
+      <c r="V78" s="10" t="n"/>
+      <c r="W78" s="10" t="n"/>
+      <c r="X78" s="11" t="n"/>
+      <c r="Y78" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
+      <c r="AB78" s="10" t="n"/>
+      <c r="AC78" s="10" t="n"/>
+      <c r="AD78" s="10" t="n"/>
+      <c r="AE78" s="11" t="n"/>
+      <c r="AF78" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AG78" s="10" t="n"/>
+      <c r="AH78" s="10" t="n"/>
+      <c r="AI78" s="10" t="n"/>
+      <c r="AJ78" s="10" t="n"/>
+      <c r="AK78" s="11" t="n"/>
+    </row>
+    <row r="79" ht="19.5" customHeight="1"/>
+    <row r="80" ht="19.5" customHeight="1">
+      <c r="B80" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="409" customHeight="1">
-      <c r="C79" s="19" t="inlineStr">
+    <row r="81" ht="409" customHeight="1">
+      <c r="C81" s="19" t="inlineStr">
         <is>
           <t>POST /api/v1/hanbaiten
 Content-Type: application/json
@@ -10710,54 +10897,55 @@
   "yokin_shubetsu": 1,
   "koza_no": "1234567",
   "koza_meigi": "販売店A代表",
+  "haiten_flg": false,
   "biko": "特別な対応なし"
 }</t>
         </is>
       </c>
-      <c r="D79" s="10" t="n"/>
-      <c r="E79" s="10" t="n"/>
-      <c r="F79" s="10" t="n"/>
-      <c r="G79" s="10" t="n"/>
-      <c r="H79" s="10" t="n"/>
-      <c r="I79" s="10" t="n"/>
-      <c r="J79" s="10" t="n"/>
-      <c r="K79" s="10" t="n"/>
-      <c r="L79" s="10" t="n"/>
-      <c r="M79" s="10" t="n"/>
-      <c r="N79" s="10" t="n"/>
-      <c r="O79" s="10" t="n"/>
-      <c r="P79" s="10" t="n"/>
-      <c r="Q79" s="10" t="n"/>
-      <c r="R79" s="10" t="n"/>
-      <c r="S79" s="10" t="n"/>
-      <c r="T79" s="10" t="n"/>
-      <c r="U79" s="10" t="n"/>
-      <c r="V79" s="10" t="n"/>
-      <c r="W79" s="10" t="n"/>
-      <c r="X79" s="10" t="n"/>
-      <c r="Y79" s="10" t="n"/>
-      <c r="Z79" s="10" t="n"/>
-      <c r="AA79" s="10" t="n"/>
-      <c r="AB79" s="10" t="n"/>
-      <c r="AC79" s="10" t="n"/>
-      <c r="AD79" s="10" t="n"/>
-      <c r="AE79" s="10" t="n"/>
-      <c r="AF79" s="10" t="n"/>
-      <c r="AG79" s="10" t="n"/>
-      <c r="AH79" s="10" t="n"/>
-      <c r="AI79" s="10" t="n"/>
-      <c r="AJ79" s="10" t="n"/>
-      <c r="AK79" s="11" t="n"/>
-    </row>
-    <row r="81" ht="19.5" customHeight="1">
-      <c r="B81" s="40" t="inlineStr">
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="10" t="n"/>
+      <c r="K81" s="10" t="n"/>
+      <c r="L81" s="10" t="n"/>
+      <c r="M81" s="10" t="n"/>
+      <c r="N81" s="10" t="n"/>
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="10" t="n"/>
+      <c r="R81" s="10" t="n"/>
+      <c r="S81" s="10" t="n"/>
+      <c r="T81" s="10" t="n"/>
+      <c r="U81" s="10" t="n"/>
+      <c r="V81" s="10" t="n"/>
+      <c r="W81" s="10" t="n"/>
+      <c r="X81" s="10" t="n"/>
+      <c r="Y81" s="10" t="n"/>
+      <c r="Z81" s="10" t="n"/>
+      <c r="AA81" s="10" t="n"/>
+      <c r="AB81" s="10" t="n"/>
+      <c r="AC81" s="10" t="n"/>
+      <c r="AD81" s="10" t="n"/>
+      <c r="AE81" s="10" t="n"/>
+      <c r="AF81" s="10" t="n"/>
+      <c r="AG81" s="10" t="n"/>
+      <c r="AH81" s="10" t="n"/>
+      <c r="AI81" s="10" t="n"/>
+      <c r="AJ81" s="10" t="n"/>
+      <c r="AK81" s="11" t="n"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="B83" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="409" customHeight="1">
-      <c r="C82" s="19" t="inlineStr">
+    <row r="84" ht="409" customHeight="1">
+      <c r="C84" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
@@ -10784,6 +10972,7 @@
     "yokin_shubetsu": 1,
     "koza_no": "1234567",
     "koza_meigi": "販売店A代表",
+    "haiten_flg": false,
     "biko": "特別な対応なし",
     "created_at": "2026-04-16T10:00:00Z",
     "updated_at": null
@@ -10791,50 +10980,50 @@
 }</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n"/>
-      <c r="E82" s="10" t="n"/>
-      <c r="F82" s="10" t="n"/>
-      <c r="G82" s="10" t="n"/>
-      <c r="H82" s="10" t="n"/>
-      <c r="I82" s="10" t="n"/>
-      <c r="J82" s="10" t="n"/>
-      <c r="K82" s="10" t="n"/>
-      <c r="L82" s="10" t="n"/>
-      <c r="M82" s="10" t="n"/>
-      <c r="N82" s="10" t="n"/>
-      <c r="O82" s="10" t="n"/>
-      <c r="P82" s="10" t="n"/>
-      <c r="Q82" s="10" t="n"/>
-      <c r="R82" s="10" t="n"/>
-      <c r="S82" s="10" t="n"/>
-      <c r="T82" s="10" t="n"/>
-      <c r="U82" s="10" t="n"/>
-      <c r="V82" s="10" t="n"/>
-      <c r="W82" s="10" t="n"/>
-      <c r="X82" s="10" t="n"/>
-      <c r="Y82" s="10" t="n"/>
-      <c r="Z82" s="10" t="n"/>
-      <c r="AA82" s="10" t="n"/>
-      <c r="AB82" s="10" t="n"/>
-      <c r="AC82" s="10" t="n"/>
-      <c r="AD82" s="10" t="n"/>
-      <c r="AE82" s="10" t="n"/>
-      <c r="AF82" s="10" t="n"/>
-      <c r="AG82" s="10" t="n"/>
-      <c r="AH82" s="10" t="n"/>
-      <c r="AI82" s="10" t="n"/>
-      <c r="AJ82" s="10" t="n"/>
-      <c r="AK82" s="11" t="n"/>
-    </row>
-    <row r="84" ht="19.5" customHeight="1">
-      <c r="B84" s="40" t="inlineStr">
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="10" t="n"/>
+      <c r="I84" s="10" t="n"/>
+      <c r="J84" s="10" t="n"/>
+      <c r="K84" s="10" t="n"/>
+      <c r="L84" s="10" t="n"/>
+      <c r="M84" s="10" t="n"/>
+      <c r="N84" s="10" t="n"/>
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="10" t="n"/>
+      <c r="Q84" s="10" t="n"/>
+      <c r="R84" s="10" t="n"/>
+      <c r="S84" s="10" t="n"/>
+      <c r="T84" s="10" t="n"/>
+      <c r="U84" s="10" t="n"/>
+      <c r="V84" s="10" t="n"/>
+      <c r="W84" s="10" t="n"/>
+      <c r="X84" s="10" t="n"/>
+      <c r="Y84" s="10" t="n"/>
+      <c r="Z84" s="10" t="n"/>
+      <c r="AA84" s="10" t="n"/>
+      <c r="AB84" s="10" t="n"/>
+      <c r="AC84" s="10" t="n"/>
+      <c r="AD84" s="10" t="n"/>
+      <c r="AE84" s="10" t="n"/>
+      <c r="AF84" s="10" t="n"/>
+      <c r="AG84" s="10" t="n"/>
+      <c r="AH84" s="10" t="n"/>
+      <c r="AI84" s="10" t="n"/>
+      <c r="AJ84" s="10" t="n"/>
+      <c r="AK84" s="11" t="n"/>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
+      <c r="B86" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (Validation Error)）</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="162" customHeight="1">
-      <c r="C85" s="19" t="inlineStr">
+    <row r="87" ht="162" customHeight="1">
+      <c r="C87" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
@@ -10847,50 +11036,50 @@
 }</t>
         </is>
       </c>
-      <c r="D85" s="10" t="n"/>
-      <c r="E85" s="10" t="n"/>
-      <c r="F85" s="10" t="n"/>
-      <c r="G85" s="10" t="n"/>
-      <c r="H85" s="10" t="n"/>
-      <c r="I85" s="10" t="n"/>
-      <c r="J85" s="10" t="n"/>
-      <c r="K85" s="10" t="n"/>
-      <c r="L85" s="10" t="n"/>
-      <c r="M85" s="10" t="n"/>
-      <c r="N85" s="10" t="n"/>
-      <c r="O85" s="10" t="n"/>
-      <c r="P85" s="10" t="n"/>
-      <c r="Q85" s="10" t="n"/>
-      <c r="R85" s="10" t="n"/>
-      <c r="S85" s="10" t="n"/>
-      <c r="T85" s="10" t="n"/>
-      <c r="U85" s="10" t="n"/>
-      <c r="V85" s="10" t="n"/>
-      <c r="W85" s="10" t="n"/>
-      <c r="X85" s="10" t="n"/>
-      <c r="Y85" s="10" t="n"/>
-      <c r="Z85" s="10" t="n"/>
-      <c r="AA85" s="10" t="n"/>
-      <c r="AB85" s="10" t="n"/>
-      <c r="AC85" s="10" t="n"/>
-      <c r="AD85" s="10" t="n"/>
-      <c r="AE85" s="10" t="n"/>
-      <c r="AF85" s="10" t="n"/>
-      <c r="AG85" s="10" t="n"/>
-      <c r="AH85" s="10" t="n"/>
-      <c r="AI85" s="10" t="n"/>
-      <c r="AJ85" s="10" t="n"/>
-      <c r="AK85" s="11" t="n"/>
-    </row>
-    <row r="87" ht="19.5" customHeight="1">
-      <c r="B87" s="40" t="inlineStr">
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="10" t="n"/>
+      <c r="J87" s="10" t="n"/>
+      <c r="K87" s="10" t="n"/>
+      <c r="L87" s="10" t="n"/>
+      <c r="M87" s="10" t="n"/>
+      <c r="N87" s="10" t="n"/>
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="10" t="n"/>
+      <c r="R87" s="10" t="n"/>
+      <c r="S87" s="10" t="n"/>
+      <c r="T87" s="10" t="n"/>
+      <c r="U87" s="10" t="n"/>
+      <c r="V87" s="10" t="n"/>
+      <c r="W87" s="10" t="n"/>
+      <c r="X87" s="10" t="n"/>
+      <c r="Y87" s="10" t="n"/>
+      <c r="Z87" s="10" t="n"/>
+      <c r="AA87" s="10" t="n"/>
+      <c r="AB87" s="10" t="n"/>
+      <c r="AC87" s="10" t="n"/>
+      <c r="AD87" s="10" t="n"/>
+      <c r="AE87" s="10" t="n"/>
+      <c r="AF87" s="10" t="n"/>
+      <c r="AG87" s="10" t="n"/>
+      <c r="AH87" s="10" t="n"/>
+      <c r="AI87" s="10" t="n"/>
+      <c r="AJ87" s="10" t="n"/>
+      <c r="AK87" s="11" t="n"/>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="B89" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="72" customHeight="1">
-      <c r="C88" s="19" t="inlineStr">
+    <row r="90" ht="72" customHeight="1">
+      <c r="C90" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -10898,50 +11087,50 @@
 }</t>
         </is>
       </c>
-      <c r="D88" s="10" t="n"/>
-      <c r="E88" s="10" t="n"/>
-      <c r="F88" s="10" t="n"/>
-      <c r="G88" s="10" t="n"/>
-      <c r="H88" s="10" t="n"/>
-      <c r="I88" s="10" t="n"/>
-      <c r="J88" s="10" t="n"/>
-      <c r="K88" s="10" t="n"/>
-      <c r="L88" s="10" t="n"/>
-      <c r="M88" s="10" t="n"/>
-      <c r="N88" s="10" t="n"/>
-      <c r="O88" s="10" t="n"/>
-      <c r="P88" s="10" t="n"/>
-      <c r="Q88" s="10" t="n"/>
-      <c r="R88" s="10" t="n"/>
-      <c r="S88" s="10" t="n"/>
-      <c r="T88" s="10" t="n"/>
-      <c r="U88" s="10" t="n"/>
-      <c r="V88" s="10" t="n"/>
-      <c r="W88" s="10" t="n"/>
-      <c r="X88" s="10" t="n"/>
-      <c r="Y88" s="10" t="n"/>
-      <c r="Z88" s="10" t="n"/>
-      <c r="AA88" s="10" t="n"/>
-      <c r="AB88" s="10" t="n"/>
-      <c r="AC88" s="10" t="n"/>
-      <c r="AD88" s="10" t="n"/>
-      <c r="AE88" s="10" t="n"/>
-      <c r="AF88" s="10" t="n"/>
-      <c r="AG88" s="10" t="n"/>
-      <c r="AH88" s="10" t="n"/>
-      <c r="AI88" s="10" t="n"/>
-      <c r="AJ88" s="10" t="n"/>
-      <c r="AK88" s="11" t="n"/>
-    </row>
-    <row r="90" ht="19.5" customHeight="1">
-      <c r="B90" s="40" t="inlineStr">
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="10" t="n"/>
+      <c r="J90" s="10" t="n"/>
+      <c r="K90" s="10" t="n"/>
+      <c r="L90" s="10" t="n"/>
+      <c r="M90" s="10" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="10" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="10" t="n"/>
+      <c r="Y90" s="10" t="n"/>
+      <c r="Z90" s="10" t="n"/>
+      <c r="AA90" s="10" t="n"/>
+      <c r="AB90" s="10" t="n"/>
+      <c r="AC90" s="10" t="n"/>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="10" t="n"/>
+      <c r="AF90" s="10" t="n"/>
+      <c r="AG90" s="10" t="n"/>
+      <c r="AH90" s="10" t="n"/>
+      <c r="AI90" s="10" t="n"/>
+      <c r="AJ90" s="10" t="n"/>
+      <c r="AK90" s="11" t="n"/>
+    </row>
+    <row r="92" ht="19.5" customHeight="1">
+      <c r="B92" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="72" customHeight="1">
-      <c r="C91" s="19" t="inlineStr">
+    <row r="93" ht="72" customHeight="1">
+      <c r="C93" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -10949,50 +11138,50 @@
 }</t>
         </is>
       </c>
-      <c r="D91" s="10" t="n"/>
-      <c r="E91" s="10" t="n"/>
-      <c r="F91" s="10" t="n"/>
-      <c r="G91" s="10" t="n"/>
-      <c r="H91" s="10" t="n"/>
-      <c r="I91" s="10" t="n"/>
-      <c r="J91" s="10" t="n"/>
-      <c r="K91" s="10" t="n"/>
-      <c r="L91" s="10" t="n"/>
-      <c r="M91" s="10" t="n"/>
-      <c r="N91" s="10" t="n"/>
-      <c r="O91" s="10" t="n"/>
-      <c r="P91" s="10" t="n"/>
-      <c r="Q91" s="10" t="n"/>
-      <c r="R91" s="10" t="n"/>
-      <c r="S91" s="10" t="n"/>
-      <c r="T91" s="10" t="n"/>
-      <c r="U91" s="10" t="n"/>
-      <c r="V91" s="10" t="n"/>
-      <c r="W91" s="10" t="n"/>
-      <c r="X91" s="10" t="n"/>
-      <c r="Y91" s="10" t="n"/>
-      <c r="Z91" s="10" t="n"/>
-      <c r="AA91" s="10" t="n"/>
-      <c r="AB91" s="10" t="n"/>
-      <c r="AC91" s="10" t="n"/>
-      <c r="AD91" s="10" t="n"/>
-      <c r="AE91" s="10" t="n"/>
-      <c r="AF91" s="10" t="n"/>
-      <c r="AG91" s="10" t="n"/>
-      <c r="AH91" s="10" t="n"/>
-      <c r="AI91" s="10" t="n"/>
-      <c r="AJ91" s="10" t="n"/>
-      <c r="AK91" s="11" t="n"/>
-    </row>
-    <row r="93" ht="19.5" customHeight="1">
-      <c r="B93" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（失敗 409 Conflict）</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="72" customHeight="1">
-      <c r="C94" s="19" t="inlineStr">
+      <c r="D93" s="10" t="n"/>
+      <c r="E93" s="10" t="n"/>
+      <c r="F93" s="10" t="n"/>
+      <c r="G93" s="10" t="n"/>
+      <c r="H93" s="10" t="n"/>
+      <c r="I93" s="10" t="n"/>
+      <c r="J93" s="10" t="n"/>
+      <c r="K93" s="10" t="n"/>
+      <c r="L93" s="10" t="n"/>
+      <c r="M93" s="10" t="n"/>
+      <c r="N93" s="10" t="n"/>
+      <c r="O93" s="10" t="n"/>
+      <c r="P93" s="10" t="n"/>
+      <c r="Q93" s="10" t="n"/>
+      <c r="R93" s="10" t="n"/>
+      <c r="S93" s="10" t="n"/>
+      <c r="T93" s="10" t="n"/>
+      <c r="U93" s="10" t="n"/>
+      <c r="V93" s="10" t="n"/>
+      <c r="W93" s="10" t="n"/>
+      <c r="X93" s="10" t="n"/>
+      <c r="Y93" s="10" t="n"/>
+      <c r="Z93" s="10" t="n"/>
+      <c r="AA93" s="10" t="n"/>
+      <c r="AB93" s="10" t="n"/>
+      <c r="AC93" s="10" t="n"/>
+      <c r="AD93" s="10" t="n"/>
+      <c r="AE93" s="10" t="n"/>
+      <c r="AF93" s="10" t="n"/>
+      <c r="AG93" s="10" t="n"/>
+      <c r="AH93" s="10" t="n"/>
+      <c r="AI93" s="10" t="n"/>
+      <c r="AJ93" s="10" t="n"/>
+      <c r="AK93" s="11" t="n"/>
+    </row>
+    <row r="95" ht="19.5" customHeight="1">
+      <c r="B95" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 400 Bad Request（重複））</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="72" customHeight="1">
+      <c r="C96" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "DUPLICATE_CODE",
@@ -11000,50 +11189,50 @@
 }</t>
         </is>
       </c>
-      <c r="D94" s="10" t="n"/>
-      <c r="E94" s="10" t="n"/>
-      <c r="F94" s="10" t="n"/>
-      <c r="G94" s="10" t="n"/>
-      <c r="H94" s="10" t="n"/>
-      <c r="I94" s="10" t="n"/>
-      <c r="J94" s="10" t="n"/>
-      <c r="K94" s="10" t="n"/>
-      <c r="L94" s="10" t="n"/>
-      <c r="M94" s="10" t="n"/>
-      <c r="N94" s="10" t="n"/>
-      <c r="O94" s="10" t="n"/>
-      <c r="P94" s="10" t="n"/>
-      <c r="Q94" s="10" t="n"/>
-      <c r="R94" s="10" t="n"/>
-      <c r="S94" s="10" t="n"/>
-      <c r="T94" s="10" t="n"/>
-      <c r="U94" s="10" t="n"/>
-      <c r="V94" s="10" t="n"/>
-      <c r="W94" s="10" t="n"/>
-      <c r="X94" s="10" t="n"/>
-      <c r="Y94" s="10" t="n"/>
-      <c r="Z94" s="10" t="n"/>
-      <c r="AA94" s="10" t="n"/>
-      <c r="AB94" s="10" t="n"/>
-      <c r="AC94" s="10" t="n"/>
-      <c r="AD94" s="10" t="n"/>
-      <c r="AE94" s="10" t="n"/>
-      <c r="AF94" s="10" t="n"/>
-      <c r="AG94" s="10" t="n"/>
-      <c r="AH94" s="10" t="n"/>
-      <c r="AI94" s="10" t="n"/>
-      <c r="AJ94" s="10" t="n"/>
-      <c r="AK94" s="11" t="n"/>
-    </row>
-    <row r="96" ht="19.5" customHeight="1">
-      <c r="B96" s="40" t="inlineStr">
+      <c r="D96" s="10" t="n"/>
+      <c r="E96" s="10" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
+      <c r="H96" s="10" t="n"/>
+      <c r="I96" s="10" t="n"/>
+      <c r="J96" s="10" t="n"/>
+      <c r="K96" s="10" t="n"/>
+      <c r="L96" s="10" t="n"/>
+      <c r="M96" s="10" t="n"/>
+      <c r="N96" s="10" t="n"/>
+      <c r="O96" s="10" t="n"/>
+      <c r="P96" s="10" t="n"/>
+      <c r="Q96" s="10" t="n"/>
+      <c r="R96" s="10" t="n"/>
+      <c r="S96" s="10" t="n"/>
+      <c r="T96" s="10" t="n"/>
+      <c r="U96" s="10" t="n"/>
+      <c r="V96" s="10" t="n"/>
+      <c r="W96" s="10" t="n"/>
+      <c r="X96" s="10" t="n"/>
+      <c r="Y96" s="10" t="n"/>
+      <c r="Z96" s="10" t="n"/>
+      <c r="AA96" s="10" t="n"/>
+      <c r="AB96" s="10" t="n"/>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="10" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="10" t="n"/>
+      <c r="AK96" s="11" t="n"/>
+    </row>
+    <row r="98" ht="19.5" customHeight="1">
+      <c r="B98" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="72" customHeight="1">
-      <c r="C97" s="19" t="inlineStr">
+    <row r="99" ht="72" customHeight="1">
+      <c r="C99" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -11051,254 +11240,291 @@
 }</t>
         </is>
       </c>
-      <c r="D97" s="10" t="n"/>
-      <c r="E97" s="10" t="n"/>
-      <c r="F97" s="10" t="n"/>
-      <c r="G97" s="10" t="n"/>
-      <c r="H97" s="10" t="n"/>
-      <c r="I97" s="10" t="n"/>
-      <c r="J97" s="10" t="n"/>
-      <c r="K97" s="10" t="n"/>
-      <c r="L97" s="10" t="n"/>
-      <c r="M97" s="10" t="n"/>
-      <c r="N97" s="10" t="n"/>
-      <c r="O97" s="10" t="n"/>
-      <c r="P97" s="10" t="n"/>
-      <c r="Q97" s="10" t="n"/>
-      <c r="R97" s="10" t="n"/>
-      <c r="S97" s="10" t="n"/>
-      <c r="T97" s="10" t="n"/>
-      <c r="U97" s="10" t="n"/>
-      <c r="V97" s="10" t="n"/>
-      <c r="W97" s="10" t="n"/>
-      <c r="X97" s="10" t="n"/>
-      <c r="Y97" s="10" t="n"/>
-      <c r="Z97" s="10" t="n"/>
-      <c r="AA97" s="10" t="n"/>
-      <c r="AB97" s="10" t="n"/>
-      <c r="AC97" s="10" t="n"/>
-      <c r="AD97" s="10" t="n"/>
-      <c r="AE97" s="10" t="n"/>
-      <c r="AF97" s="10" t="n"/>
-      <c r="AG97" s="10" t="n"/>
-      <c r="AH97" s="10" t="n"/>
-      <c r="AI97" s="10" t="n"/>
-      <c r="AJ97" s="10" t="n"/>
-      <c r="AK97" s="11" t="n"/>
-    </row>
-    <row r="99" ht="19.5" customHeight="1"/>
-    <row r="100" ht="19.5" customHeight="1">
-      <c r="A100" s="27" t="inlineStr">
+      <c r="D99" s="10" t="n"/>
+      <c r="E99" s="10" t="n"/>
+      <c r="F99" s="10" t="n"/>
+      <c r="G99" s="10" t="n"/>
+      <c r="H99" s="10" t="n"/>
+      <c r="I99" s="10" t="n"/>
+      <c r="J99" s="10" t="n"/>
+      <c r="K99" s="10" t="n"/>
+      <c r="L99" s="10" t="n"/>
+      <c r="M99" s="10" t="n"/>
+      <c r="N99" s="10" t="n"/>
+      <c r="O99" s="10" t="n"/>
+      <c r="P99" s="10" t="n"/>
+      <c r="Q99" s="10" t="n"/>
+      <c r="R99" s="10" t="n"/>
+      <c r="S99" s="10" t="n"/>
+      <c r="T99" s="10" t="n"/>
+      <c r="U99" s="10" t="n"/>
+      <c r="V99" s="10" t="n"/>
+      <c r="W99" s="10" t="n"/>
+      <c r="X99" s="10" t="n"/>
+      <c r="Y99" s="10" t="n"/>
+      <c r="Z99" s="10" t="n"/>
+      <c r="AA99" s="10" t="n"/>
+      <c r="AB99" s="10" t="n"/>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="10" t="n"/>
+      <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="10" t="n"/>
+      <c r="AK99" s="11" t="n"/>
+    </row>
+    <row r="101" ht="19.5" customHeight="1"/>
+    <row r="102" ht="19.5" customHeight="1">
+      <c r="A102" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="B101" s="27" t="inlineStr">
+    <row r="103" ht="54" customHeight="1">
+      <c r="B103" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="n"/>
+      <c r="D103" s="10" t="n"/>
+      <c r="E103" s="10" t="n"/>
+      <c r="F103" s="10" t="n"/>
+      <c r="G103" s="10" t="n"/>
+      <c r="H103" s="10" t="n"/>
+      <c r="I103" s="10" t="n"/>
+      <c r="J103" s="10" t="n"/>
+      <c r="K103" s="10" t="n"/>
+      <c r="L103" s="10" t="n"/>
+      <c r="M103" s="10" t="n"/>
+      <c r="N103" s="10" t="n"/>
+      <c r="O103" s="10" t="n"/>
+      <c r="P103" s="10" t="n"/>
+      <c r="Q103" s="10" t="n"/>
+      <c r="R103" s="10" t="n"/>
+      <c r="S103" s="10" t="n"/>
+      <c r="T103" s="10" t="n"/>
+      <c r="U103" s="10" t="n"/>
+      <c r="V103" s="10" t="n"/>
+      <c r="W103" s="10" t="n"/>
+      <c r="X103" s="10" t="n"/>
+      <c r="Y103" s="10" t="n"/>
+      <c r="Z103" s="10" t="n"/>
+      <c r="AA103" s="10" t="n"/>
+      <c r="AB103" s="10" t="n"/>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="10" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="10" t="n"/>
+      <c r="AK103" s="11" t="n"/>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="B104" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="C102" s="41" t="inlineStr">
+    <row r="105" ht="18" customHeight="1">
+      <c r="C105" s="41" t="inlineStr">
         <is>
           <t>リクエストボディの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="D103" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_code：必須、最大10桁、同一JA内で一意</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="D104" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_name：必須、最大100桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="D105" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_name_kana：最大100桁</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
       <c r="D106" s="41" t="inlineStr">
         <is>
-          <t>torihikisaki_no：最大20桁</t>
+          <t>hanbaiten_code：必須、最大10桁、同一JA内で一意</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="D107" s="41" t="inlineStr">
         <is>
-          <t>yubin_no：最大7桁（郵便番号形式チェック）</t>
+          <t>hanbaiten_name：必須、最大100桁</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
       <c r="D108" s="41" t="inlineStr">
         <is>
-          <t>address：最大200桁</t>
+          <t>hanbaiten_name_kana：最大100桁</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="D109" s="41" t="inlineStr">
         <is>
-          <t>tel：最大15桁</t>
+          <t>torihikisaki_no：最大20桁</t>
         </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="D110" s="41" t="inlineStr">
         <is>
-          <t>fax：最大15桁</t>
+          <t>yubin_no：最大7桁（郵便番号形式チェック）</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="D111" s="41" t="inlineStr">
         <is>
-          <t>shocho_name：最大50桁</t>
+          <t>address：最大200桁</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="D112" s="41" t="inlineStr">
         <is>
-          <t>itaku_kubun：1, 2, 9 のいずれか</t>
+          <t>tel：最大15桁</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="D113" s="41" t="inlineStr">
         <is>
-          <t>haitatsuryo_tanka_id：数値型チェック</t>
+          <t>shocho_name：最大50桁</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="D114" s="41" t="inlineStr">
         <is>
-          <t>haitatsuryo_shiharai_cycle：数値型チェック、≧ 0</t>
+          <t>itaku_kubun：1, 2, 9 のいずれか</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="D115" s="41" t="inlineStr">
         <is>
-          <t>tesuryo_kubun：1, 2 のいずれか</t>
+          <t>haitatsuryo_tanka_id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="D116" s="41" t="inlineStr">
         <is>
-          <t>tesuryo_amount：数値型チェック、≧ 0</t>
+          <t>tesuryo_kubun：1, 2 のいずれか</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="D117" s="41" t="inlineStr">
         <is>
-          <t>itaku_kubun = 1（振込）の場合：</t>
+          <t>tesuryo_amount：数値型チェック、≧ 0</t>
         </is>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="D118" s="41" t="inlineStr">
         <is>
-          <t>koza_meigi：最大50桁</t>
+          <t>itaku_kubun = 1（振込）の場合：</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="D119" s="41" t="inlineStr">
         <is>
+          <t>koza_meigi：最大50桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="D120" s="41" t="inlineStr">
+        <is>
+          <t>haiten_flg：Boolean型チェック（省略時は false）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="D121" s="41" t="inlineStr">
+        <is>
           <t>biko：テキスト型</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="36" customHeight="1">
-      <c r="C120" s="41" t="inlineStr">
-        <is>
-          <t>バリデーションエラーの場合：HTTP 422 (`VALIDATION_ERROR`) + errors配列</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="B121" s="27" t="inlineStr">
+    <row r="122" ht="36" customHeight="1">
+      <c r="C122" s="41" t="inlineStr">
+        <is>
+          <t>バリデーションエラーの場合：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="B123" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="C122" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="C123" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1">
       <c r="C124" s="41" t="inlineStr">
         <is>
-          <t>権限チェック：`hanbaiten.create` を保持しているか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="36" customHeight="1">
-      <c r="D125" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="C125" s="41" t="inlineStr">
+        <is>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="C126" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="B127" s="27" t="inlineStr">
-        <is>
-          <t>4.3 重複チェック</t>
+          <t>権限チェック：`hanbaiten.create` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="36" customHeight="1">
+      <c r="D127" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="C128" s="41" t="inlineStr">
         <is>
+          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="B129" s="27" t="inlineStr">
+        <is>
+          <t>4.3 重複チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="C130" s="41" t="inlineStr">
+        <is>
           <t>ログインユーザーのスコープを取得する（ja_id）。</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="C129" s="41" t="inlineStr">
+    <row r="131" ht="18" customHeight="1">
+      <c r="C131" s="41" t="inlineStr">
         <is>
           <t>以下の条件で重複を確認する。</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="72" customHeight="1">
-      <c r="C130" s="42" t="inlineStr">
+    <row r="132" ht="72" customHeight="1">
+      <c r="C132" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) FROM m_hanbaiten
 WHERE hanbaiten_code = :hanbaiten_code
@@ -11306,64 +11532,64 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D130" s="10" t="n"/>
-      <c r="E130" s="10" t="n"/>
-      <c r="F130" s="10" t="n"/>
-      <c r="G130" s="10" t="n"/>
-      <c r="H130" s="10" t="n"/>
-      <c r="I130" s="10" t="n"/>
-      <c r="J130" s="10" t="n"/>
-      <c r="K130" s="10" t="n"/>
-      <c r="L130" s="10" t="n"/>
-      <c r="M130" s="10" t="n"/>
-      <c r="N130" s="10" t="n"/>
-      <c r="O130" s="10" t="n"/>
-      <c r="P130" s="10" t="n"/>
-      <c r="Q130" s="10" t="n"/>
-      <c r="R130" s="10" t="n"/>
-      <c r="S130" s="10" t="n"/>
-      <c r="T130" s="10" t="n"/>
-      <c r="U130" s="10" t="n"/>
-      <c r="V130" s="10" t="n"/>
-      <c r="W130" s="10" t="n"/>
-      <c r="X130" s="10" t="n"/>
-      <c r="Y130" s="10" t="n"/>
-      <c r="Z130" s="10" t="n"/>
-      <c r="AA130" s="10" t="n"/>
-      <c r="AB130" s="10" t="n"/>
-      <c r="AC130" s="10" t="n"/>
-      <c r="AD130" s="10" t="n"/>
-      <c r="AE130" s="10" t="n"/>
-      <c r="AF130" s="10" t="n"/>
-      <c r="AG130" s="10" t="n"/>
-      <c r="AH130" s="10" t="n"/>
-      <c r="AI130" s="10" t="n"/>
-      <c r="AJ130" s="10" t="n"/>
-      <c r="AK130" s="11" t="n"/>
-    </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="C131" s="41" t="inlineStr">
-        <is>
-          <t>重複がある場合：HTTP 409 (`DUPLICATE_CODE`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="B132" s="27" t="inlineStr">
-        <is>
-          <t>4.4 データ登録</t>
-        </is>
-      </c>
+      <c r="D132" s="10" t="n"/>
+      <c r="E132" s="10" t="n"/>
+      <c r="F132" s="10" t="n"/>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="10" t="n"/>
+      <c r="I132" s="10" t="n"/>
+      <c r="J132" s="10" t="n"/>
+      <c r="K132" s="10" t="n"/>
+      <c r="L132" s="10" t="n"/>
+      <c r="M132" s="10" t="n"/>
+      <c r="N132" s="10" t="n"/>
+      <c r="O132" s="10" t="n"/>
+      <c r="P132" s="10" t="n"/>
+      <c r="Q132" s="10" t="n"/>
+      <c r="R132" s="10" t="n"/>
+      <c r="S132" s="10" t="n"/>
+      <c r="T132" s="10" t="n"/>
+      <c r="U132" s="10" t="n"/>
+      <c r="V132" s="10" t="n"/>
+      <c r="W132" s="10" t="n"/>
+      <c r="X132" s="10" t="n"/>
+      <c r="Y132" s="10" t="n"/>
+      <c r="Z132" s="10" t="n"/>
+      <c r="AA132" s="10" t="n"/>
+      <c r="AB132" s="10" t="n"/>
+      <c r="AC132" s="10" t="n"/>
+      <c r="AD132" s="10" t="n"/>
+      <c r="AE132" s="10" t="n"/>
+      <c r="AF132" s="10" t="n"/>
+      <c r="AG132" s="10" t="n"/>
+      <c r="AH132" s="10" t="n"/>
+      <c r="AI132" s="10" t="n"/>
+      <c r="AJ132" s="10" t="n"/>
+      <c r="AK132" s="11" t="n"/>
     </row>
     <row r="133" ht="18" customHeight="1">
       <c r="C133" s="41" t="inlineStr">
         <is>
+          <t>重複がある場合：HTTP 400 (`DUPLICATE_CODE`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="B134" s="27" t="inlineStr">
+        <is>
+          <t>4.4 データ登録</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="C135" s="41" t="inlineStr">
+        <is>
           <t>以下のSQLを実行して登録する。</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="306" customHeight="1">
-      <c r="C134" s="42" t="inlineStr">
+    <row r="136" ht="306" customHeight="1">
+      <c r="C136" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO m_hanbaiten (ja_id, hanbaiten_code, hanbaiten_name,
                          hanbaiten_name_kana, torihikisaki_no, yubin_no, address,
@@ -11371,7 +11597,7 @@
                          haitatsuryo_tanka_id, haitatsuryo_shiharai_cycle,
                          tesuryo_kubun, tesuryo_amount,
                          bank_code, bank_name, bank_branch_code, bank_branch_name,
-                         yokin_shubetsu, koza_no, koza_meigi, biko,
+                         yokin_shubetsu, koza_no, koza_meigi, haiten_flg, biko,
                          created_at, created_by, updated_at, updated_by)
 VALUES (:ja_id, :hanbaiten_code, :hanbaiten_name,
         :hanbaiten_name_kana, :torihikisaki_no, :yubin_no, :address,
@@ -11379,62 +11605,62 @@
         :haitatsuryo_tanka_id, :haitatsuryo_shiharai_cycle,
         :tesuryo_kubun, :tesuryo_amount,
         :bank_code, :bank_name, :bank_branch_code, :bank_branch_name,
-        :yokin_shubetsu, :koza_no, :koza_meigi, :biko,
+        :yokin_shubetsu, :koza_no, :koza_meigi, :haiten_flg, :biko,
         NOW(), :user_account_id, NOW(), :user_account_id)
 RETURNING *</t>
         </is>
       </c>
-      <c r="D134" s="10" t="n"/>
-      <c r="E134" s="10" t="n"/>
-      <c r="F134" s="10" t="n"/>
-      <c r="G134" s="10" t="n"/>
-      <c r="H134" s="10" t="n"/>
-      <c r="I134" s="10" t="n"/>
-      <c r="J134" s="10" t="n"/>
-      <c r="K134" s="10" t="n"/>
-      <c r="L134" s="10" t="n"/>
-      <c r="M134" s="10" t="n"/>
-      <c r="N134" s="10" t="n"/>
-      <c r="O134" s="10" t="n"/>
-      <c r="P134" s="10" t="n"/>
-      <c r="Q134" s="10" t="n"/>
-      <c r="R134" s="10" t="n"/>
-      <c r="S134" s="10" t="n"/>
-      <c r="T134" s="10" t="n"/>
-      <c r="U134" s="10" t="n"/>
-      <c r="V134" s="10" t="n"/>
-      <c r="W134" s="10" t="n"/>
-      <c r="X134" s="10" t="n"/>
-      <c r="Y134" s="10" t="n"/>
-      <c r="Z134" s="10" t="n"/>
-      <c r="AA134" s="10" t="n"/>
-      <c r="AB134" s="10" t="n"/>
-      <c r="AC134" s="10" t="n"/>
-      <c r="AD134" s="10" t="n"/>
-      <c r="AE134" s="10" t="n"/>
-      <c r="AF134" s="10" t="n"/>
-      <c r="AG134" s="10" t="n"/>
-      <c r="AH134" s="10" t="n"/>
-      <c r="AI134" s="10" t="n"/>
-      <c r="AJ134" s="10" t="n"/>
-      <c r="AK134" s="11" t="n"/>
-    </row>
-    <row r="135" ht="18" customHeight="1">
-      <c r="B135" s="27" t="inlineStr">
+      <c r="D136" s="10" t="n"/>
+      <c r="E136" s="10" t="n"/>
+      <c r="F136" s="10" t="n"/>
+      <c r="G136" s="10" t="n"/>
+      <c r="H136" s="10" t="n"/>
+      <c r="I136" s="10" t="n"/>
+      <c r="J136" s="10" t="n"/>
+      <c r="K136" s="10" t="n"/>
+      <c r="L136" s="10" t="n"/>
+      <c r="M136" s="10" t="n"/>
+      <c r="N136" s="10" t="n"/>
+      <c r="O136" s="10" t="n"/>
+      <c r="P136" s="10" t="n"/>
+      <c r="Q136" s="10" t="n"/>
+      <c r="R136" s="10" t="n"/>
+      <c r="S136" s="10" t="n"/>
+      <c r="T136" s="10" t="n"/>
+      <c r="U136" s="10" t="n"/>
+      <c r="V136" s="10" t="n"/>
+      <c r="W136" s="10" t="n"/>
+      <c r="X136" s="10" t="n"/>
+      <c r="Y136" s="10" t="n"/>
+      <c r="Z136" s="10" t="n"/>
+      <c r="AA136" s="10" t="n"/>
+      <c r="AB136" s="10" t="n"/>
+      <c r="AC136" s="10" t="n"/>
+      <c r="AD136" s="10" t="n"/>
+      <c r="AE136" s="10" t="n"/>
+      <c r="AF136" s="10" t="n"/>
+      <c r="AG136" s="10" t="n"/>
+      <c r="AH136" s="10" t="n"/>
+      <c r="AI136" s="10" t="n"/>
+      <c r="AJ136" s="10" t="n"/>
+      <c r="AK136" s="11" t="n"/>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="B137" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="18" customHeight="1">
-      <c r="C136" s="41" t="inlineStr">
+    <row r="138" ht="18" customHeight="1">
+      <c r="C138" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="216" customHeight="1">
-      <c r="C137" s="42" t="inlineStr">
+    <row r="139" ht="216" customHeight="1">
+      <c r="C139" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -11450,43 +11676,43 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D137" s="10" t="n"/>
-      <c r="E137" s="10" t="n"/>
-      <c r="F137" s="10" t="n"/>
-      <c r="G137" s="10" t="n"/>
-      <c r="H137" s="10" t="n"/>
-      <c r="I137" s="10" t="n"/>
-      <c r="J137" s="10" t="n"/>
-      <c r="K137" s="10" t="n"/>
-      <c r="L137" s="10" t="n"/>
-      <c r="M137" s="10" t="n"/>
-      <c r="N137" s="10" t="n"/>
-      <c r="O137" s="10" t="n"/>
-      <c r="P137" s="10" t="n"/>
-      <c r="Q137" s="10" t="n"/>
-      <c r="R137" s="10" t="n"/>
-      <c r="S137" s="10" t="n"/>
-      <c r="T137" s="10" t="n"/>
-      <c r="U137" s="10" t="n"/>
-      <c r="V137" s="10" t="n"/>
-      <c r="W137" s="10" t="n"/>
-      <c r="X137" s="10" t="n"/>
-      <c r="Y137" s="10" t="n"/>
-      <c r="Z137" s="10" t="n"/>
-      <c r="AA137" s="10" t="n"/>
-      <c r="AB137" s="10" t="n"/>
-      <c r="AC137" s="10" t="n"/>
-      <c r="AD137" s="10" t="n"/>
-      <c r="AE137" s="10" t="n"/>
-      <c r="AF137" s="10" t="n"/>
-      <c r="AG137" s="10" t="n"/>
-      <c r="AH137" s="10" t="n"/>
-      <c r="AI137" s="10" t="n"/>
-      <c r="AJ137" s="10" t="n"/>
-      <c r="AK137" s="11" t="n"/>
-    </row>
-    <row r="138" ht="409" customHeight="1">
-      <c r="C138" s="42" t="inlineStr">
+      <c r="D139" s="10" t="n"/>
+      <c r="E139" s="10" t="n"/>
+      <c r="F139" s="10" t="n"/>
+      <c r="G139" s="10" t="n"/>
+      <c r="H139" s="10" t="n"/>
+      <c r="I139" s="10" t="n"/>
+      <c r="J139" s="10" t="n"/>
+      <c r="K139" s="10" t="n"/>
+      <c r="L139" s="10" t="n"/>
+      <c r="M139" s="10" t="n"/>
+      <c r="N139" s="10" t="n"/>
+      <c r="O139" s="10" t="n"/>
+      <c r="P139" s="10" t="n"/>
+      <c r="Q139" s="10" t="n"/>
+      <c r="R139" s="10" t="n"/>
+      <c r="S139" s="10" t="n"/>
+      <c r="T139" s="10" t="n"/>
+      <c r="U139" s="10" t="n"/>
+      <c r="V139" s="10" t="n"/>
+      <c r="W139" s="10" t="n"/>
+      <c r="X139" s="10" t="n"/>
+      <c r="Y139" s="10" t="n"/>
+      <c r="Z139" s="10" t="n"/>
+      <c r="AA139" s="10" t="n"/>
+      <c r="AB139" s="10" t="n"/>
+      <c r="AC139" s="10" t="n"/>
+      <c r="AD139" s="10" t="n"/>
+      <c r="AE139" s="10" t="n"/>
+      <c r="AF139" s="10" t="n"/>
+      <c r="AG139" s="10" t="n"/>
+      <c r="AH139" s="10" t="n"/>
+      <c r="AI139" s="10" t="n"/>
+      <c r="AJ139" s="10" t="n"/>
+      <c r="AK139" s="11" t="n"/>
+    </row>
+    <row r="140" ht="409" customHeight="1">
+      <c r="C140" s="42" t="inlineStr">
         <is>
           <t>`before_value`：INSERT のため空文字列を設定する。
 `after_value`：登録されたデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
@@ -11514,82 +11740,83 @@
   "yokin_shubetsu": 1,
   "koza_no": "1234567",
   "koza_meigi": "販売店A代表",
+  "haiten_flg": false,
   "biko": "特別な対応なし"
 }</t>
         </is>
       </c>
-      <c r="D138" s="10" t="n"/>
-      <c r="E138" s="10" t="n"/>
-      <c r="F138" s="10" t="n"/>
-      <c r="G138" s="10" t="n"/>
-      <c r="H138" s="10" t="n"/>
-      <c r="I138" s="10" t="n"/>
-      <c r="J138" s="10" t="n"/>
-      <c r="K138" s="10" t="n"/>
-      <c r="L138" s="10" t="n"/>
-      <c r="M138" s="10" t="n"/>
-      <c r="N138" s="10" t="n"/>
-      <c r="O138" s="10" t="n"/>
-      <c r="P138" s="10" t="n"/>
-      <c r="Q138" s="10" t="n"/>
-      <c r="R138" s="10" t="n"/>
-      <c r="S138" s="10" t="n"/>
-      <c r="T138" s="10" t="n"/>
-      <c r="U138" s="10" t="n"/>
-      <c r="V138" s="10" t="n"/>
-      <c r="W138" s="10" t="n"/>
-      <c r="X138" s="10" t="n"/>
-      <c r="Y138" s="10" t="n"/>
-      <c r="Z138" s="10" t="n"/>
-      <c r="AA138" s="10" t="n"/>
-      <c r="AB138" s="10" t="n"/>
-      <c r="AC138" s="10" t="n"/>
-      <c r="AD138" s="10" t="n"/>
-      <c r="AE138" s="10" t="n"/>
-      <c r="AF138" s="10" t="n"/>
-      <c r="AG138" s="10" t="n"/>
-      <c r="AH138" s="10" t="n"/>
-      <c r="AI138" s="10" t="n"/>
-      <c r="AJ138" s="10" t="n"/>
-      <c r="AK138" s="11" t="n"/>
-    </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="B139" s="27" t="inlineStr">
-        <is>
-          <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="18" customHeight="1">
-      <c r="C140" s="41" t="inlineStr">
-        <is>
-          <t>登録されたデータをdata オブジェクトとして返却する。HTTP 201。</t>
-        </is>
-      </c>
+      <c r="D140" s="10" t="n"/>
+      <c r="E140" s="10" t="n"/>
+      <c r="F140" s="10" t="n"/>
+      <c r="G140" s="10" t="n"/>
+      <c r="H140" s="10" t="n"/>
+      <c r="I140" s="10" t="n"/>
+      <c r="J140" s="10" t="n"/>
+      <c r="K140" s="10" t="n"/>
+      <c r="L140" s="10" t="n"/>
+      <c r="M140" s="10" t="n"/>
+      <c r="N140" s="10" t="n"/>
+      <c r="O140" s="10" t="n"/>
+      <c r="P140" s="10" t="n"/>
+      <c r="Q140" s="10" t="n"/>
+      <c r="R140" s="10" t="n"/>
+      <c r="S140" s="10" t="n"/>
+      <c r="T140" s="10" t="n"/>
+      <c r="U140" s="10" t="n"/>
+      <c r="V140" s="10" t="n"/>
+      <c r="W140" s="10" t="n"/>
+      <c r="X140" s="10" t="n"/>
+      <c r="Y140" s="10" t="n"/>
+      <c r="Z140" s="10" t="n"/>
+      <c r="AA140" s="10" t="n"/>
+      <c r="AB140" s="10" t="n"/>
+      <c r="AC140" s="10" t="n"/>
+      <c r="AD140" s="10" t="n"/>
+      <c r="AE140" s="10" t="n"/>
+      <c r="AF140" s="10" t="n"/>
+      <c r="AG140" s="10" t="n"/>
+      <c r="AH140" s="10" t="n"/>
+      <c r="AI140" s="10" t="n"/>
+      <c r="AJ140" s="10" t="n"/>
+      <c r="AK140" s="11" t="n"/>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="B141" s="27" t="inlineStr">
         <is>
-          <t>4.7 例外処理</t>
+          <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
       <c r="C142" s="41" t="inlineStr">
         <is>
+          <t>登録されたデータをdata オブジェクトとして返却する。HTTP 201。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="B143" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="C144" s="41" t="inlineStr">
+        <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="C143" s="41" t="inlineStr">
+    <row r="145" ht="18" customHeight="1">
+      <c r="C145" s="41" t="inlineStr">
         <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="216" customHeight="1">
-      <c r="C144" s="42" t="inlineStr">
+    <row r="146" ht="216" customHeight="1">
+      <c r="C146" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -11605,46 +11832,48 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D144" s="10" t="n"/>
-      <c r="E144" s="10" t="n"/>
-      <c r="F144" s="10" t="n"/>
-      <c r="G144" s="10" t="n"/>
-      <c r="H144" s="10" t="n"/>
-      <c r="I144" s="10" t="n"/>
-      <c r="J144" s="10" t="n"/>
-      <c r="K144" s="10" t="n"/>
-      <c r="L144" s="10" t="n"/>
-      <c r="M144" s="10" t="n"/>
-      <c r="N144" s="10" t="n"/>
-      <c r="O144" s="10" t="n"/>
-      <c r="P144" s="10" t="n"/>
-      <c r="Q144" s="10" t="n"/>
-      <c r="R144" s="10" t="n"/>
-      <c r="S144" s="10" t="n"/>
-      <c r="T144" s="10" t="n"/>
-      <c r="U144" s="10" t="n"/>
-      <c r="V144" s="10" t="n"/>
-      <c r="W144" s="10" t="n"/>
-      <c r="X144" s="10" t="n"/>
-      <c r="Y144" s="10" t="n"/>
-      <c r="Z144" s="10" t="n"/>
-      <c r="AA144" s="10" t="n"/>
-      <c r="AB144" s="10" t="n"/>
-      <c r="AC144" s="10" t="n"/>
-      <c r="AD144" s="10" t="n"/>
-      <c r="AE144" s="10" t="n"/>
-      <c r="AF144" s="10" t="n"/>
-      <c r="AG144" s="10" t="n"/>
-      <c r="AH144" s="10" t="n"/>
-      <c r="AI144" s="10" t="n"/>
-      <c r="AJ144" s="10" t="n"/>
-      <c r="AK144" s="11" t="n"/>
+      <c r="D146" s="10" t="n"/>
+      <c r="E146" s="10" t="n"/>
+      <c r="F146" s="10" t="n"/>
+      <c r="G146" s="10" t="n"/>
+      <c r="H146" s="10" t="n"/>
+      <c r="I146" s="10" t="n"/>
+      <c r="J146" s="10" t="n"/>
+      <c r="K146" s="10" t="n"/>
+      <c r="L146" s="10" t="n"/>
+      <c r="M146" s="10" t="n"/>
+      <c r="N146" s="10" t="n"/>
+      <c r="O146" s="10" t="n"/>
+      <c r="P146" s="10" t="n"/>
+      <c r="Q146" s="10" t="n"/>
+      <c r="R146" s="10" t="n"/>
+      <c r="S146" s="10" t="n"/>
+      <c r="T146" s="10" t="n"/>
+      <c r="U146" s="10" t="n"/>
+      <c r="V146" s="10" t="n"/>
+      <c r="W146" s="10" t="n"/>
+      <c r="X146" s="10" t="n"/>
+      <c r="Y146" s="10" t="n"/>
+      <c r="Z146" s="10" t="n"/>
+      <c r="AA146" s="10" t="n"/>
+      <c r="AB146" s="10" t="n"/>
+      <c r="AC146" s="10" t="n"/>
+      <c r="AD146" s="10" t="n"/>
+      <c r="AE146" s="10" t="n"/>
+      <c r="AF146" s="10" t="n"/>
+      <c r="AG146" s="10" t="n"/>
+      <c r="AH146" s="10" t="n"/>
+      <c r="AI146" s="10" t="n"/>
+      <c r="AJ146" s="10" t="n"/>
+      <c r="AK146" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="433">
+  <mergeCells count="446">
+    <mergeCell ref="Y46:AB46"/>
     <mergeCell ref="AF65:AK65"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="D61:L61"/>
+    <mergeCell ref="Q78:S78"/>
     <mergeCell ref="M72:P72"/>
     <mergeCell ref="T53:X53"/>
     <mergeCell ref="Y41:AB41"/>
@@ -11659,13 +11888,11 @@
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="D64:L64"/>
-    <mergeCell ref="C94:AK94"/>
-    <mergeCell ref="D51:L51"/>
     <mergeCell ref="C142:AK142"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="C129:AK129"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
+    <mergeCell ref="Q77:S77"/>
     <mergeCell ref="Q33:S33"/>
     <mergeCell ref="Y34:AB34"/>
     <mergeCell ref="T37:X37"/>
@@ -11678,10 +11905,10 @@
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="C38:L38"/>
     <mergeCell ref="Q59:S59"/>
+    <mergeCell ref="Q46:S46"/>
     <mergeCell ref="Y66:AE66"/>
-    <mergeCell ref="C88:AK88"/>
+    <mergeCell ref="C126:AK126"/>
     <mergeCell ref="Y53:AE53"/>
-    <mergeCell ref="C126:AK126"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="Q61:S61"/>
     <mergeCell ref="AF35:AK35"/>
@@ -11689,7 +11916,6 @@
     <mergeCell ref="Y68:AE68"/>
     <mergeCell ref="T74:X74"/>
     <mergeCell ref="Y55:AE55"/>
-    <mergeCell ref="B87:I87"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C35:L35"/>
     <mergeCell ref="T76:X76"/>
@@ -11697,8 +11923,10 @@
     <mergeCell ref="C144:AK144"/>
     <mergeCell ref="D65:L65"/>
     <mergeCell ref="M27:P27"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="C145:AK145"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="Y33:AB33"/>
@@ -11707,16 +11935,15 @@
     <mergeCell ref="C28:L28"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
-    <mergeCell ref="Q49:S49"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="Y56:AE56"/>
     <mergeCell ref="T59:X59"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="C134:AK134"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
+    <mergeCell ref="B143:AK143"/>
     <mergeCell ref="Y39:AB39"/>
     <mergeCell ref="Y74:AE74"/>
     <mergeCell ref="AF56:AK56"/>
@@ -11725,18 +11952,20 @@
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="C41:L41"/>
     <mergeCell ref="M75:P75"/>
-    <mergeCell ref="D105:AK105"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="Q62:S62"/>
+    <mergeCell ref="B95:I95"/>
+    <mergeCell ref="B89:I89"/>
     <mergeCell ref="Y69:AE69"/>
+    <mergeCell ref="D120:AK120"/>
     <mergeCell ref="C43:L43"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
+    <mergeCell ref="B134:AK134"/>
     <mergeCell ref="Q64:S64"/>
-    <mergeCell ref="B121:AK121"/>
+    <mergeCell ref="T77:X77"/>
     <mergeCell ref="M41:P41"/>
-    <mergeCell ref="B90:I90"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
@@ -11757,38 +11986,37 @@
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="M46:P46"/>
     <mergeCell ref="M37:P37"/>
     <mergeCell ref="AC30:AE30"/>
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="C102:AK102"/>
+    <mergeCell ref="Y77:AE77"/>
     <mergeCell ref="J18:M18"/>
-    <mergeCell ref="B96:I96"/>
+    <mergeCell ref="D121:AK121"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="C49:L49"/>
     <mergeCell ref="M56:P56"/>
     <mergeCell ref="D113:AK113"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="AF50:AK50"/>
     <mergeCell ref="Q70:S70"/>
+    <mergeCell ref="B98:I98"/>
     <mergeCell ref="Y72:AE72"/>
     <mergeCell ref="C42:L42"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C143:AK143"/>
+    <mergeCell ref="B137:AK137"/>
     <mergeCell ref="D115:AK115"/>
     <mergeCell ref="AF52:AK52"/>
-    <mergeCell ref="B139:AK139"/>
     <mergeCell ref="AF34:AK34"/>
     <mergeCell ref="T75:X75"/>
     <mergeCell ref="M25:P25"/>
-    <mergeCell ref="AF49:AK49"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="Q58:S58"/>
+    <mergeCell ref="AF78:AK78"/>
     <mergeCell ref="Y65:AE65"/>
     <mergeCell ref="D76:L76"/>
     <mergeCell ref="C39:L39"/>
-    <mergeCell ref="D103:AK103"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="Q60:S60"/>
     <mergeCell ref="M62:P62"/>
@@ -11797,10 +12025,9 @@
     <mergeCell ref="D118:AK118"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="AF55:AK55"/>
-    <mergeCell ref="B132:AK132"/>
+    <mergeCell ref="B86:I86"/>
     <mergeCell ref="AC44:AE44"/>
     <mergeCell ref="AC31:AE31"/>
-    <mergeCell ref="B127:AK127"/>
     <mergeCell ref="M64:P64"/>
     <mergeCell ref="AF71:AK71"/>
     <mergeCell ref="M51:P51"/>
@@ -11811,19 +12038,24 @@
     <mergeCell ref="AF73:AK73"/>
     <mergeCell ref="Q71:S71"/>
     <mergeCell ref="M65:P65"/>
+    <mergeCell ref="Y78:AE78"/>
+    <mergeCell ref="T46:X46"/>
     <mergeCell ref="AF66:AK66"/>
     <mergeCell ref="D116:AK116"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q73:S73"/>
     <mergeCell ref="AF68:AK68"/>
+    <mergeCell ref="C96:AK96"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="M34:P34"/>
-    <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
+    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="D119:AK119"/>
     <mergeCell ref="D54:L54"/>
     <mergeCell ref="T41:X41"/>
+    <mergeCell ref="M78:P78"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="J9:AK9"/>
@@ -11832,7 +12064,6 @@
     <mergeCell ref="AC32:AE32"/>
     <mergeCell ref="AC37:AE37"/>
     <mergeCell ref="T43:X43"/>
-    <mergeCell ref="B135:AK135"/>
     <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="D57:L57"/>
@@ -11848,13 +12079,15 @@
     <mergeCell ref="T62:X62"/>
     <mergeCell ref="Q76:S76"/>
     <mergeCell ref="AC27:AE27"/>
-    <mergeCell ref="C137:AK137"/>
     <mergeCell ref="T64:X64"/>
     <mergeCell ref="C124:AK124"/>
     <mergeCell ref="Y44:AB44"/>
+    <mergeCell ref="C90:AK90"/>
     <mergeCell ref="D60:L60"/>
+    <mergeCell ref="C139:AK139"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="C138:AK138"/>
+    <mergeCell ref="C132:AK132"/>
     <mergeCell ref="Y59:AE59"/>
     <mergeCell ref="B141:AK141"/>
     <mergeCell ref="M42:P42"/>
@@ -11862,7 +12095,6 @@
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
     <mergeCell ref="T33:X33"/>
@@ -11870,13 +12102,15 @@
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="AC38:AE38"/>
     <mergeCell ref="Y32:AB32"/>
+    <mergeCell ref="D78:L78"/>
     <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="AC46:AE46"/>
     <mergeCell ref="AC40:AE40"/>
     <mergeCell ref="D71:L71"/>
     <mergeCell ref="C34:L34"/>
-    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="Y62:AE62"/>
     <mergeCell ref="D73:L73"/>
+    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="C133:AK133"/>
     <mergeCell ref="M70:P70"/>
     <mergeCell ref="Y54:AE54"/>
@@ -11884,6 +12118,8 @@
     <mergeCell ref="AC41:AE41"/>
     <mergeCell ref="Y64:AE64"/>
     <mergeCell ref="J2:P3"/>
+    <mergeCell ref="AF77:AK77"/>
+    <mergeCell ref="B83:I83"/>
     <mergeCell ref="M74:P74"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
@@ -11899,7 +12135,6 @@
     <mergeCell ref="D53:L53"/>
     <mergeCell ref="AF59:AK59"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B101:AK101"/>
     <mergeCell ref="Q44:S44"/>
     <mergeCell ref="T58:X58"/>
     <mergeCell ref="T54:X54"/>
@@ -11912,16 +12147,18 @@
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="B78:I78"/>
+    <mergeCell ref="C99:AK99"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
+    <mergeCell ref="B104:AK104"/>
     <mergeCell ref="T60:X60"/>
     <mergeCell ref="C130:AK130"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C122:AK122"/>
     <mergeCell ref="M36:P36"/>
+    <mergeCell ref="C125:AK125"/>
     <mergeCell ref="Q63:S63"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="Y70:AE70"/>
@@ -11929,8 +12166,8 @@
     <mergeCell ref="Y57:AE57"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="B93:I93"/>
     <mergeCell ref="C37:L37"/>
+    <mergeCell ref="T78:X78"/>
     <mergeCell ref="T65:X65"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
@@ -11939,12 +12176,13 @@
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="D55:L55"/>
     <mergeCell ref="AF40:AK40"/>
+    <mergeCell ref="C146:AK146"/>
     <mergeCell ref="D67:L67"/>
     <mergeCell ref="T73:X73"/>
     <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="C105:AK105"/>
     <mergeCell ref="D69:L69"/>
     <mergeCell ref="M31:P31"/>
-    <mergeCell ref="C120:AK120"/>
     <mergeCell ref="Y60:AE60"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="Q55:S55"/>
@@ -11953,7 +12191,6 @@
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="M26:P26"/>
-    <mergeCell ref="B81:I81"/>
     <mergeCell ref="D106:AK106"/>
     <mergeCell ref="Q40:S40"/>
     <mergeCell ref="AC26:AE26"/>
@@ -11963,6 +12200,7 @@
     <mergeCell ref="C45:L45"/>
     <mergeCell ref="Y58:AE58"/>
     <mergeCell ref="D109:AK109"/>
+    <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="Q66:S66"/>
     <mergeCell ref="Q53:S53"/>
     <mergeCell ref="Y73:AE73"/>
@@ -11971,12 +12209,12 @@
     <mergeCell ref="T70:X70"/>
     <mergeCell ref="AF61:AK61"/>
     <mergeCell ref="D111:AK111"/>
+    <mergeCell ref="B92:I92"/>
     <mergeCell ref="Q68:S68"/>
     <mergeCell ref="C40:L40"/>
-    <mergeCell ref="D104:AK104"/>
-    <mergeCell ref="C91:AK91"/>
+    <mergeCell ref="C51:L51"/>
     <mergeCell ref="M28:P28"/>
-    <mergeCell ref="C82:AK82"/>
+    <mergeCell ref="D77:L77"/>
     <mergeCell ref="Q72:S72"/>
     <mergeCell ref="M57:P57"/>
     <mergeCell ref="M32:P32"/>
@@ -11984,12 +12222,12 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="D72:L72"/>
-    <mergeCell ref="A100:AK100"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="T63:X63"/>
     <mergeCell ref="M71:P71"/>
     <mergeCell ref="AF29:AK29"/>
     <mergeCell ref="Y38:AB38"/>
+    <mergeCell ref="A102:AK102"/>
     <mergeCell ref="T71:X71"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="Y24:AB24"/>
@@ -12001,20 +12239,23 @@
     <mergeCell ref="T66:X66"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
+    <mergeCell ref="B123:AK123"/>
     <mergeCell ref="AF67:AK67"/>
+    <mergeCell ref="C46:L46"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="AF69:AK69"/>
     <mergeCell ref="Q67:S67"/>
     <mergeCell ref="A21:AK21"/>
-    <mergeCell ref="D125:AK125"/>
     <mergeCell ref="AF62:AK62"/>
     <mergeCell ref="D112:AK112"/>
     <mergeCell ref="Q69:S69"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y76:AE76"/>
+    <mergeCell ref="D127:AK127"/>
     <mergeCell ref="AF64:AK64"/>
     <mergeCell ref="D114:AK114"/>
     <mergeCell ref="AF51:AK51"/>
+    <mergeCell ref="B103:AK103"/>
     <mergeCell ref="Y63:AE63"/>
     <mergeCell ref="M44:P44"/>
     <mergeCell ref="AF38:AK38"/>
@@ -12025,6 +12266,7 @@
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="B129:AK129"/>
     <mergeCell ref="D107:AK107"/>
     <mergeCell ref="C36:L36"/>
     <mergeCell ref="Q51:S51"/>
@@ -12033,19 +12275,17 @@
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="A47:AK47"/>
     <mergeCell ref="T32:X32"/>
     <mergeCell ref="AC35:AE35"/>
+    <mergeCell ref="C52:C78"/>
     <mergeCell ref="M63:P63"/>
     <mergeCell ref="M53:P53"/>
     <mergeCell ref="AC34:AE34"/>
     <mergeCell ref="M50:P50"/>
     <mergeCell ref="M68:P68"/>
-    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="M55:P55"/>
     <mergeCell ref="M67:P67"/>
     <mergeCell ref="AF72:AK72"/>
-    <mergeCell ref="C51:C76"/>
     <mergeCell ref="Q75:S75"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="M69:P69"/>
@@ -12054,26 +12294,26 @@
     <mergeCell ref="Y40:AB40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="T27:X27"/>
+    <mergeCell ref="C135:AK135"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="T49:X49"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="M76:P76"/>
     <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="Q65:S65"/>
-    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="AF60:AK60"/>
     <mergeCell ref="D110:AK110"/>
     <mergeCell ref="D74:L74"/>
     <mergeCell ref="D68:L68"/>
+    <mergeCell ref="A48:AK48"/>
     <mergeCell ref="AC36:AE36"/>
     <mergeCell ref="Y35:AB35"/>
     <mergeCell ref="D59:L59"/>
-    <mergeCell ref="B84:I84"/>
     <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
+    <mergeCell ref="B80:I80"/>
+    <mergeCell ref="M77:P77"/>
     <mergeCell ref="Y52:AE52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12086,7 +12326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK147"/>
+  <dimension ref="A1:AK149"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -12247,7 +12487,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/16</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -12601,7 +12841,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -14277,7 +14517,7 @@
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t>biko</t>
+          <t>haiten_flg</t>
         </is>
       </c>
       <c r="D45" s="10" t="n"/>
@@ -14291,7 +14531,7 @@
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N45" s="10" t="n"/>
@@ -14322,7 +14562,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>廃店フラグ（true:廃店, false:営業中）</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -14331,88 +14571,84 @@
       <c r="AJ45" s="10" t="n"/>
       <c r="AK45" s="11" t="n"/>
     </row>
-    <row r="46" ht="19.5" customHeight="1"/>
-    <row r="47" ht="19.5" customHeight="1">
-      <c r="A47" s="27" t="inlineStr">
+    <row r="46" ht="18" customHeight="1">
+      <c r="B46" s="31" t="n">
+        <v>23</v>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>biko</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="10" t="n"/>
+      <c r="K46" s="10" t="n"/>
+      <c r="L46" s="11" t="n"/>
+      <c r="M46" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N46" s="10" t="n"/>
+      <c r="O46" s="10" t="n"/>
+      <c r="P46" s="11" t="n"/>
+      <c r="Q46" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R46" s="10" t="n"/>
+      <c r="S46" s="11" t="n"/>
+      <c r="T46" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U46" s="10" t="n"/>
+      <c r="V46" s="10" t="n"/>
+      <c r="W46" s="10" t="n"/>
+      <c r="X46" s="11" t="n"/>
+      <c r="Y46" s="17" t="inlineStr"/>
+      <c r="Z46" s="10" t="n"/>
+      <c r="AA46" s="10" t="n"/>
+      <c r="AB46" s="11" t="n"/>
+      <c r="AC46" s="17" t="inlineStr"/>
+      <c r="AD46" s="10" t="n"/>
+      <c r="AE46" s="11" t="n"/>
+      <c r="AF46" s="19" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="AG46" s="10" t="n"/>
+      <c r="AH46" s="10" t="n"/>
+      <c r="AI46" s="10" t="n"/>
+      <c r="AJ46" s="10" t="n"/>
+      <c r="AK46" s="11" t="n"/>
+    </row>
+    <row r="47" ht="19.5" customHeight="1"/>
+    <row r="48" ht="19.5" customHeight="1">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="19.5" customHeight="1"/>
-    <row r="49" ht="19.5" customHeight="1">
-      <c r="B49" s="30" t="inlineStr">
+    <row r="49" ht="19.5" customHeight="1"/>
+    <row r="50" ht="19.5" customHeight="1">
+      <c r="B50" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="10" t="n"/>
-      <c r="G49" s="10" t="n"/>
-      <c r="H49" s="10" t="n"/>
-      <c r="I49" s="10" t="n"/>
-      <c r="J49" s="10" t="n"/>
-      <c r="K49" s="10" t="n"/>
-      <c r="L49" s="11" t="n"/>
-      <c r="M49" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N49" s="10" t="n"/>
-      <c r="O49" s="10" t="n"/>
-      <c r="P49" s="11" t="n"/>
-      <c r="Q49" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R49" s="10" t="n"/>
-      <c r="S49" s="11" t="n"/>
-      <c r="T49" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U49" s="10" t="n"/>
-      <c r="V49" s="10" t="n"/>
-      <c r="W49" s="10" t="n"/>
-      <c r="X49" s="11" t="n"/>
-      <c r="Y49" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z49" s="10" t="n"/>
-      <c r="AA49" s="10" t="n"/>
-      <c r="AB49" s="10" t="n"/>
-      <c r="AC49" s="10" t="n"/>
-      <c r="AD49" s="10" t="n"/>
-      <c r="AE49" s="11" t="n"/>
-      <c r="AF49" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG49" s="10" t="n"/>
-      <c r="AH49" s="10" t="n"/>
-      <c r="AI49" s="10" t="n"/>
-      <c r="AJ49" s="10" t="n"/>
-      <c r="AK49" s="11" t="n"/>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="B50" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
         </is>
       </c>
       <c r="D50" s="10" t="n"/>
@@ -14424,29 +14660,33 @@
       <c r="J50" s="10" t="n"/>
       <c r="K50" s="10" t="n"/>
       <c r="L50" s="11" t="n"/>
-      <c r="M50" s="17" t="inlineStr">
-        <is>
-          <t>Object</t>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N50" s="10" t="n"/>
       <c r="O50" s="10" t="n"/>
       <c r="P50" s="11" t="n"/>
-      <c r="Q50" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q50" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R50" s="10" t="n"/>
       <c r="S50" s="11" t="n"/>
-      <c r="T50" s="17" t="inlineStr"/>
+      <c r="T50" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U50" s="10" t="n"/>
       <c r="V50" s="10" t="n"/>
       <c r="W50" s="10" t="n"/>
       <c r="X50" s="11" t="n"/>
-      <c r="Y50" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y50" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z50" s="10" t="n"/>
@@ -14455,9 +14695,9 @@
       <c r="AC50" s="10" t="n"/>
       <c r="AD50" s="10" t="n"/>
       <c r="AE50" s="11" t="n"/>
-      <c r="AF50" s="19" t="inlineStr">
-        <is>
-          <t>更新された販売店データ</t>
+      <c r="AF50" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -14468,14 +14708,14 @@
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C51" s="37" t="n"/>
-      <c r="D51" s="19" t="inlineStr">
-        <is>
-          <t>hanbaiten_id</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n"/>
       <c r="E51" s="10" t="n"/>
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
@@ -14486,7 +14726,7 @@
       <c r="L51" s="11" t="n"/>
       <c r="M51" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N51" s="10" t="n"/>
@@ -14517,7 +14757,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>販売店ID</t>
+          <t>更新された販売店データ</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -14528,12 +14768,12 @@
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C52" s="38" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C52" s="37" t="n"/>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>hanbaiten_id</t>
         </is>
       </c>
       <c r="E52" s="10" t="n"/>
@@ -14577,7 +14817,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>販売店ID</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -14588,12 +14828,12 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53" s="38" t="n"/>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_code</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
@@ -14606,7 +14846,7 @@
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N53" s="10" t="n"/>
@@ -14637,7 +14877,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>販売店コード (編集不可)</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -14648,12 +14888,12 @@
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54" s="38" t="n"/>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_name</t>
+          <t>hanbaiten_code</t>
         </is>
       </c>
       <c r="E54" s="10" t="n"/>
@@ -14697,7 +14937,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>販売店名</t>
+          <t>販売店コード (編集不可)</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -14708,12 +14948,12 @@
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="38" t="n"/>
       <c r="D55" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_name_kana</t>
+          <t>hanbaiten_name</t>
         </is>
       </c>
       <c r="E55" s="10" t="n"/>
@@ -14746,7 +14986,7 @@
       <c r="X55" s="11" t="n"/>
       <c r="Y55" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z55" s="10" t="n"/>
@@ -14757,7 +14997,7 @@
       <c r="AE55" s="11" t="n"/>
       <c r="AF55" s="19" t="inlineStr">
         <is>
-          <t>販売店名（カナ）</t>
+          <t>販売店名</t>
         </is>
       </c>
       <c r="AG55" s="10" t="n"/>
@@ -14768,12 +15008,12 @@
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56" s="38" t="n"/>
       <c r="D56" s="19" t="inlineStr">
         <is>
-          <t>torihikisaki_no</t>
+          <t>hanbaiten_name_kana</t>
         </is>
       </c>
       <c r="E56" s="10" t="n"/>
@@ -14806,7 +15046,7 @@
       <c r="X56" s="11" t="n"/>
       <c r="Y56" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z56" s="10" t="n"/>
@@ -14817,7 +15057,7 @@
       <c r="AE56" s="11" t="n"/>
       <c r="AF56" s="19" t="inlineStr">
         <is>
-          <t>適格請求書発行事業者番号</t>
+          <t>販売店名（カナ）</t>
         </is>
       </c>
       <c r="AG56" s="10" t="n"/>
@@ -14828,12 +15068,12 @@
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C57" s="38" t="n"/>
       <c r="D57" s="19" t="inlineStr">
         <is>
-          <t>yubin_no</t>
+          <t>torihikisaki_no</t>
         </is>
       </c>
       <c r="E57" s="10" t="n"/>
@@ -14877,7 +15117,7 @@
       <c r="AE57" s="11" t="n"/>
       <c r="AF57" s="19" t="inlineStr">
         <is>
-          <t>郵便番号</t>
+          <t>適格請求書発行事業者番号</t>
         </is>
       </c>
       <c r="AG57" s="10" t="n"/>
@@ -14888,12 +15128,12 @@
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C58" s="38" t="n"/>
       <c r="D58" s="19" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>yubin_no</t>
         </is>
       </c>
       <c r="E58" s="10" t="n"/>
@@ -14926,7 +15166,7 @@
       <c r="X58" s="11" t="n"/>
       <c r="Y58" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z58" s="10" t="n"/>
@@ -14937,7 +15177,7 @@
       <c r="AE58" s="11" t="n"/>
       <c r="AF58" s="19" t="inlineStr">
         <is>
-          <t>住所</t>
+          <t>郵便番号</t>
         </is>
       </c>
       <c r="AG58" s="10" t="n"/>
@@ -14948,12 +15188,12 @@
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C59" s="38" t="n"/>
       <c r="D59" s="19" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>address</t>
         </is>
       </c>
       <c r="E59" s="10" t="n"/>
@@ -14986,7 +15226,7 @@
       <c r="X59" s="11" t="n"/>
       <c r="Y59" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z59" s="10" t="n"/>
@@ -14997,7 +15237,7 @@
       <c r="AE59" s="11" t="n"/>
       <c r="AF59" s="19" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>住所</t>
         </is>
       </c>
       <c r="AG59" s="10" t="n"/>
@@ -15008,12 +15248,12 @@
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C60" s="38" t="n"/>
       <c r="D60" s="19" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="E60" s="10" t="n"/>
@@ -15046,7 +15286,7 @@
       <c r="X60" s="11" t="n"/>
       <c r="Y60" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z60" s="10" t="n"/>
@@ -15057,7 +15297,7 @@
       <c r="AE60" s="11" t="n"/>
       <c r="AF60" s="19" t="inlineStr">
         <is>
-          <t>FAX番号</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="AG60" s="10" t="n"/>
@@ -15068,12 +15308,12 @@
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C61" s="38" t="n"/>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>shocho_name</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="E61" s="10" t="n"/>
@@ -15106,7 +15346,7 @@
       <c r="X61" s="11" t="n"/>
       <c r="Y61" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z61" s="10" t="n"/>
@@ -15117,7 +15357,7 @@
       <c r="AE61" s="11" t="n"/>
       <c r="AF61" s="19" t="inlineStr">
         <is>
-          <t>所長名</t>
+          <t>FAX番号</t>
         </is>
       </c>
       <c r="AG61" s="10" t="n"/>
@@ -15128,12 +15368,12 @@
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62" s="38" t="n"/>
       <c r="D62" s="19" t="inlineStr">
         <is>
-          <t>itaku_kubun</t>
+          <t>shocho_name</t>
         </is>
       </c>
       <c r="E62" s="10" t="n"/>
@@ -15146,7 +15386,7 @@
       <c r="L62" s="11" t="n"/>
       <c r="M62" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N62" s="10" t="n"/>
@@ -15177,7 +15417,7 @@
       <c r="AE62" s="11" t="n"/>
       <c r="AF62" s="19" t="inlineStr">
         <is>
-          <t>委託区分（1:振込, 2:日農委託, 9:その他）</t>
+          <t>所長名</t>
         </is>
       </c>
       <c r="AG62" s="10" t="n"/>
@@ -15188,12 +15428,12 @@
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="B63" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C63" s="38" t="n"/>
       <c r="D63" s="19" t="inlineStr">
         <is>
-          <t>haitatsuryo_tanka_id</t>
+          <t>itaku_kubun</t>
         </is>
       </c>
       <c r="E63" s="10" t="n"/>
@@ -15237,7 +15477,7 @@
       <c r="AE63" s="11" t="n"/>
       <c r="AF63" s="19" t="inlineStr">
         <is>
-          <t>配達手数料単価ID</t>
+          <t>委託区分（1:振込, 2:日農委託, 9:その他）</t>
         </is>
       </c>
       <c r="AG63" s="10" t="n"/>
@@ -15248,12 +15488,12 @@
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="B64" s="31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C64" s="38" t="n"/>
       <c r="D64" s="19" t="inlineStr">
         <is>
-          <t>haitatsuryo_shiharai_cycle</t>
+          <t>haitatsuryo_tanka_id</t>
         </is>
       </c>
       <c r="E64" s="10" t="n"/>
@@ -15297,7 +15537,7 @@
       <c r="AE64" s="11" t="n"/>
       <c r="AF64" s="19" t="inlineStr">
         <is>
-          <t>配達手数料支払サイクル（月数）</t>
+          <t>配達手数料単価ID</t>
         </is>
       </c>
       <c r="AG64" s="10" t="n"/>
@@ -15308,12 +15548,12 @@
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="B65" s="31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C65" s="38" t="n"/>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t>tesuryo_kubun</t>
+          <t>haitatsuryo_shiharai_cycle</t>
         </is>
       </c>
       <c r="E65" s="10" t="n"/>
@@ -15357,7 +15597,7 @@
       <c r="AE65" s="11" t="n"/>
       <c r="AF65" s="19" t="inlineStr">
         <is>
-          <t>手数料区分（1:JA, 2:販売店）</t>
+          <t>配達手数料支払サイクル（月数）</t>
         </is>
       </c>
       <c r="AG65" s="10" t="n"/>
@@ -15368,12 +15608,12 @@
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="B66" s="31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C66" s="38" t="n"/>
       <c r="D66" s="19" t="inlineStr">
         <is>
-          <t>tesuryo_amount</t>
+          <t>tesuryo_kubun</t>
         </is>
       </c>
       <c r="E66" s="10" t="n"/>
@@ -15399,9 +15639,7 @@
       </c>
       <c r="R66" s="10" t="n"/>
       <c r="S66" s="11" t="n"/>
-      <c r="T66" s="17" t="n">
-        <v>0</v>
-      </c>
+      <c r="T66" s="17" t="inlineStr"/>
       <c r="U66" s="10" t="n"/>
       <c r="V66" s="10" t="n"/>
       <c r="W66" s="10" t="n"/>
@@ -15419,7 +15657,7 @@
       <c r="AE66" s="11" t="n"/>
       <c r="AF66" s="19" t="inlineStr">
         <is>
-          <t>手数料金額</t>
+          <t>手数料区分（1:JA, 2:販売店）</t>
         </is>
       </c>
       <c r="AG66" s="10" t="n"/>
@@ -15430,12 +15668,12 @@
     </row>
     <row r="67" ht="18" customHeight="1">
       <c r="B67" s="31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C67" s="38" t="n"/>
       <c r="D67" s="19" t="inlineStr">
         <is>
-          <t>bank_code</t>
+          <t>tesuryo_amount</t>
         </is>
       </c>
       <c r="E67" s="10" t="n"/>
@@ -15448,7 +15686,7 @@
       <c r="L67" s="11" t="n"/>
       <c r="M67" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N67" s="10" t="n"/>
@@ -15461,7 +15699,9 @@
       </c>
       <c r="R67" s="10" t="n"/>
       <c r="S67" s="11" t="n"/>
-      <c r="T67" s="17" t="inlineStr"/>
+      <c r="T67" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="U67" s="10" t="n"/>
       <c r="V67" s="10" t="n"/>
       <c r="W67" s="10" t="n"/>
@@ -15479,7 +15719,7 @@
       <c r="AE67" s="11" t="n"/>
       <c r="AF67" s="19" t="inlineStr">
         <is>
-          <t>銀行コード</t>
+          <t>手数料金額</t>
         </is>
       </c>
       <c r="AG67" s="10" t="n"/>
@@ -15490,12 +15730,12 @@
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="B68" s="31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C68" s="38" t="n"/>
       <c r="D68" s="19" t="inlineStr">
         <is>
-          <t>bank_name</t>
+          <t>bank_code</t>
         </is>
       </c>
       <c r="E68" s="10" t="n"/>
@@ -15528,7 +15768,7 @@
       <c r="X68" s="11" t="n"/>
       <c r="Y68" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z68" s="10" t="n"/>
@@ -15539,7 +15779,7 @@
       <c r="AE68" s="11" t="n"/>
       <c r="AF68" s="19" t="inlineStr">
         <is>
-          <t>銀行名</t>
+          <t>銀行コード</t>
         </is>
       </c>
       <c r="AG68" s="10" t="n"/>
@@ -15550,12 +15790,12 @@
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="B69" s="31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C69" s="38" t="n"/>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t>bank_branch_code</t>
+          <t>bank_name</t>
         </is>
       </c>
       <c r="E69" s="10" t="n"/>
@@ -15588,7 +15828,7 @@
       <c r="X69" s="11" t="n"/>
       <c r="Y69" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z69" s="10" t="n"/>
@@ -15599,7 +15839,7 @@
       <c r="AE69" s="11" t="n"/>
       <c r="AF69" s="19" t="inlineStr">
         <is>
-          <t>支店コード</t>
+          <t>銀行名</t>
         </is>
       </c>
       <c r="AG69" s="10" t="n"/>
@@ -15610,12 +15850,12 @@
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="B70" s="31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C70" s="38" t="n"/>
       <c r="D70" s="19" t="inlineStr">
         <is>
-          <t>bank_branch_name</t>
+          <t>bank_branch_code</t>
         </is>
       </c>
       <c r="E70" s="10" t="n"/>
@@ -15659,7 +15899,7 @@
       <c r="AE70" s="11" t="n"/>
       <c r="AF70" s="19" t="inlineStr">
         <is>
-          <t>支店名</t>
+          <t>支店コード</t>
         </is>
       </c>
       <c r="AG70" s="10" t="n"/>
@@ -15670,12 +15910,12 @@
     </row>
     <row r="71" ht="18" customHeight="1">
       <c r="B71" s="31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C71" s="38" t="n"/>
       <c r="D71" s="19" t="inlineStr">
         <is>
-          <t>yokin_shubetsu</t>
+          <t>bank_branch_name</t>
         </is>
       </c>
       <c r="E71" s="10" t="n"/>
@@ -15688,7 +15928,7 @@
       <c r="L71" s="11" t="n"/>
       <c r="M71" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N71" s="10" t="n"/>
@@ -15719,7 +15959,7 @@
       <c r="AE71" s="11" t="n"/>
       <c r="AF71" s="19" t="inlineStr">
         <is>
-          <t>預金種別（1:普通, 2:当座）</t>
+          <t>支店名</t>
         </is>
       </c>
       <c r="AG71" s="10" t="n"/>
@@ -15730,12 +15970,12 @@
     </row>
     <row r="72" ht="18" customHeight="1">
       <c r="B72" s="31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C72" s="38" t="n"/>
       <c r="D72" s="19" t="inlineStr">
         <is>
-          <t>koza_no</t>
+          <t>yokin_shubetsu</t>
         </is>
       </c>
       <c r="E72" s="10" t="n"/>
@@ -15748,7 +15988,7 @@
       <c r="L72" s="11" t="n"/>
       <c r="M72" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N72" s="10" t="n"/>
@@ -15779,7 +16019,7 @@
       <c r="AE72" s="11" t="n"/>
       <c r="AF72" s="19" t="inlineStr">
         <is>
-          <t>口座番号</t>
+          <t>預金種別（1:普通, 2:当座）</t>
         </is>
       </c>
       <c r="AG72" s="10" t="n"/>
@@ -15790,12 +16030,12 @@
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="B73" s="31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C73" s="38" t="n"/>
       <c r="D73" s="19" t="inlineStr">
         <is>
-          <t>koza_meigi</t>
+          <t>koza_no</t>
         </is>
       </c>
       <c r="E73" s="10" t="n"/>
@@ -15839,7 +16079,7 @@
       <c r="AE73" s="11" t="n"/>
       <c r="AF73" s="19" t="inlineStr">
         <is>
-          <t>口座名義</t>
+          <t>口座番号</t>
         </is>
       </c>
       <c r="AG73" s="10" t="n"/>
@@ -15850,12 +16090,12 @@
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="B74" s="31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C74" s="38" t="n"/>
       <c r="D74" s="19" t="inlineStr">
         <is>
-          <t>biko</t>
+          <t>koza_meigi</t>
         </is>
       </c>
       <c r="E74" s="10" t="n"/>
@@ -15899,7 +16139,7 @@
       <c r="AE74" s="11" t="n"/>
       <c r="AF74" s="19" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>口座名義</t>
         </is>
       </c>
       <c r="AG74" s="10" t="n"/>
@@ -15910,12 +16150,12 @@
     </row>
     <row r="75" ht="18" customHeight="1">
       <c r="B75" s="31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C75" s="38" t="n"/>
       <c r="D75" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>haiten_flg</t>
         </is>
       </c>
       <c r="E75" s="10" t="n"/>
@@ -15928,7 +16168,7 @@
       <c r="L75" s="11" t="n"/>
       <c r="M75" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N75" s="10" t="n"/>
@@ -15941,11 +16181,7 @@
       </c>
       <c r="R75" s="10" t="n"/>
       <c r="S75" s="11" t="n"/>
-      <c r="T75" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T75" s="17" t="inlineStr"/>
       <c r="U75" s="10" t="n"/>
       <c r="V75" s="10" t="n"/>
       <c r="W75" s="10" t="n"/>
@@ -15963,7 +16199,7 @@
       <c r="AE75" s="11" t="n"/>
       <c r="AF75" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>廃店フラグ（true:廃店, false:営業中）</t>
         </is>
       </c>
       <c r="AG75" s="10" t="n"/>
@@ -15974,12 +16210,12 @@
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="B76" s="31" t="n">
-        <v>27</v>
-      </c>
-      <c r="C76" s="39" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="C76" s="38" t="n"/>
       <c r="D76" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>biko</t>
         </is>
       </c>
       <c r="E76" s="10" t="n"/>
@@ -16005,18 +16241,14 @@
       </c>
       <c r="R76" s="10" t="n"/>
       <c r="S76" s="11" t="n"/>
-      <c r="T76" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T76" s="17" t="inlineStr"/>
       <c r="U76" s="10" t="n"/>
       <c r="V76" s="10" t="n"/>
       <c r="W76" s="10" t="n"/>
       <c r="X76" s="11" t="n"/>
       <c r="Y76" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z76" s="10" t="n"/>
@@ -16027,7 +16259,7 @@
       <c r="AE76" s="11" t="n"/>
       <c r="AF76" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="AG76" s="10" t="n"/>
@@ -16036,16 +16268,144 @@
       <c r="AJ76" s="10" t="n"/>
       <c r="AK76" s="11" t="n"/>
     </row>
-    <row r="77" ht="19.5" customHeight="1"/>
-    <row r="78" ht="19.5" customHeight="1">
-      <c r="B78" s="40" t="inlineStr">
+    <row r="77" ht="18" customHeight="1">
+      <c r="B77" s="31" t="n">
+        <v>27</v>
+      </c>
+      <c r="C77" s="38" t="n"/>
+      <c r="D77" s="19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="10" t="n"/>
+      <c r="J77" s="10" t="n"/>
+      <c r="K77" s="10" t="n"/>
+      <c r="L77" s="11" t="n"/>
+      <c r="M77" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N77" s="10" t="n"/>
+      <c r="O77" s="10" t="n"/>
+      <c r="P77" s="11" t="n"/>
+      <c r="Q77" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R77" s="10" t="n"/>
+      <c r="S77" s="11" t="n"/>
+      <c r="T77" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U77" s="10" t="n"/>
+      <c r="V77" s="10" t="n"/>
+      <c r="W77" s="10" t="n"/>
+      <c r="X77" s="11" t="n"/>
+      <c r="Y77" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z77" s="10" t="n"/>
+      <c r="AA77" s="10" t="n"/>
+      <c r="AB77" s="10" t="n"/>
+      <c r="AC77" s="10" t="n"/>
+      <c r="AD77" s="10" t="n"/>
+      <c r="AE77" s="11" t="n"/>
+      <c r="AF77" s="19" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="AG77" s="10" t="n"/>
+      <c r="AH77" s="10" t="n"/>
+      <c r="AI77" s="10" t="n"/>
+      <c r="AJ77" s="10" t="n"/>
+      <c r="AK77" s="11" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="B78" s="31" t="n">
+        <v>28</v>
+      </c>
+      <c r="C78" s="39" t="n"/>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="10" t="n"/>
+      <c r="J78" s="10" t="n"/>
+      <c r="K78" s="10" t="n"/>
+      <c r="L78" s="11" t="n"/>
+      <c r="M78" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="11" t="n"/>
+      <c r="Q78" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="11" t="n"/>
+      <c r="T78" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U78" s="10" t="n"/>
+      <c r="V78" s="10" t="n"/>
+      <c r="W78" s="10" t="n"/>
+      <c r="X78" s="11" t="n"/>
+      <c r="Y78" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
+      <c r="AB78" s="10" t="n"/>
+      <c r="AC78" s="10" t="n"/>
+      <c r="AD78" s="10" t="n"/>
+      <c r="AE78" s="11" t="n"/>
+      <c r="AF78" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AG78" s="10" t="n"/>
+      <c r="AH78" s="10" t="n"/>
+      <c r="AI78" s="10" t="n"/>
+      <c r="AJ78" s="10" t="n"/>
+      <c r="AK78" s="11" t="n"/>
+    </row>
+    <row r="79" ht="19.5" customHeight="1"/>
+    <row r="80" ht="19.5" customHeight="1">
+      <c r="B80" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="409" customHeight="1">
-      <c r="C79" s="19" t="inlineStr">
+    <row r="81" ht="409" customHeight="1">
+      <c r="C81" s="19" t="inlineStr">
         <is>
           <t>PUT /api/v1/hanbaiten/1
 Content-Type: application/json
@@ -16070,54 +16430,55 @@
   "yokin_shubetsu": 1,
   "koza_no": "1234567",
   "koza_meigi": "販売店A代表",
+  "haiten_flg": false,
   "biko": "更新しました"
 }</t>
         </is>
       </c>
-      <c r="D79" s="10" t="n"/>
-      <c r="E79" s="10" t="n"/>
-      <c r="F79" s="10" t="n"/>
-      <c r="G79" s="10" t="n"/>
-      <c r="H79" s="10" t="n"/>
-      <c r="I79" s="10" t="n"/>
-      <c r="J79" s="10" t="n"/>
-      <c r="K79" s="10" t="n"/>
-      <c r="L79" s="10" t="n"/>
-      <c r="M79" s="10" t="n"/>
-      <c r="N79" s="10" t="n"/>
-      <c r="O79" s="10" t="n"/>
-      <c r="P79" s="10" t="n"/>
-      <c r="Q79" s="10" t="n"/>
-      <c r="R79" s="10" t="n"/>
-      <c r="S79" s="10" t="n"/>
-      <c r="T79" s="10" t="n"/>
-      <c r="U79" s="10" t="n"/>
-      <c r="V79" s="10" t="n"/>
-      <c r="W79" s="10" t="n"/>
-      <c r="X79" s="10" t="n"/>
-      <c r="Y79" s="10" t="n"/>
-      <c r="Z79" s="10" t="n"/>
-      <c r="AA79" s="10" t="n"/>
-      <c r="AB79" s="10" t="n"/>
-      <c r="AC79" s="10" t="n"/>
-      <c r="AD79" s="10" t="n"/>
-      <c r="AE79" s="10" t="n"/>
-      <c r="AF79" s="10" t="n"/>
-      <c r="AG79" s="10" t="n"/>
-      <c r="AH79" s="10" t="n"/>
-      <c r="AI79" s="10" t="n"/>
-      <c r="AJ79" s="10" t="n"/>
-      <c r="AK79" s="11" t="n"/>
-    </row>
-    <row r="81" ht="19.5" customHeight="1">
-      <c r="B81" s="40" t="inlineStr">
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="10" t="n"/>
+      <c r="K81" s="10" t="n"/>
+      <c r="L81" s="10" t="n"/>
+      <c r="M81" s="10" t="n"/>
+      <c r="N81" s="10" t="n"/>
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="10" t="n"/>
+      <c r="R81" s="10" t="n"/>
+      <c r="S81" s="10" t="n"/>
+      <c r="T81" s="10" t="n"/>
+      <c r="U81" s="10" t="n"/>
+      <c r="V81" s="10" t="n"/>
+      <c r="W81" s="10" t="n"/>
+      <c r="X81" s="10" t="n"/>
+      <c r="Y81" s="10" t="n"/>
+      <c r="Z81" s="10" t="n"/>
+      <c r="AA81" s="10" t="n"/>
+      <c r="AB81" s="10" t="n"/>
+      <c r="AC81" s="10" t="n"/>
+      <c r="AD81" s="10" t="n"/>
+      <c r="AE81" s="10" t="n"/>
+      <c r="AF81" s="10" t="n"/>
+      <c r="AG81" s="10" t="n"/>
+      <c r="AH81" s="10" t="n"/>
+      <c r="AI81" s="10" t="n"/>
+      <c r="AJ81" s="10" t="n"/>
+      <c r="AK81" s="11" t="n"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="B83" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="409" customHeight="1">
-      <c r="C82" s="19" t="inlineStr">
+    <row r="84" ht="409" customHeight="1">
+      <c r="C84" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
@@ -16144,6 +16505,7 @@
     "yokin_shubetsu": 1,
     "koza_no": "1234567",
     "koza_meigi": "販売店A代表",
+    "haiten_flg": false,
     "biko": "更新しました",
     "created_at": "2026-01-15T10:00:00Z",
     "updated_at": "2026-04-16T14:30:00Z"
@@ -16151,50 +16513,50 @@
 }</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n"/>
-      <c r="E82" s="10" t="n"/>
-      <c r="F82" s="10" t="n"/>
-      <c r="G82" s="10" t="n"/>
-      <c r="H82" s="10" t="n"/>
-      <c r="I82" s="10" t="n"/>
-      <c r="J82" s="10" t="n"/>
-      <c r="K82" s="10" t="n"/>
-      <c r="L82" s="10" t="n"/>
-      <c r="M82" s="10" t="n"/>
-      <c r="N82" s="10" t="n"/>
-      <c r="O82" s="10" t="n"/>
-      <c r="P82" s="10" t="n"/>
-      <c r="Q82" s="10" t="n"/>
-      <c r="R82" s="10" t="n"/>
-      <c r="S82" s="10" t="n"/>
-      <c r="T82" s="10" t="n"/>
-      <c r="U82" s="10" t="n"/>
-      <c r="V82" s="10" t="n"/>
-      <c r="W82" s="10" t="n"/>
-      <c r="X82" s="10" t="n"/>
-      <c r="Y82" s="10" t="n"/>
-      <c r="Z82" s="10" t="n"/>
-      <c r="AA82" s="10" t="n"/>
-      <c r="AB82" s="10" t="n"/>
-      <c r="AC82" s="10" t="n"/>
-      <c r="AD82" s="10" t="n"/>
-      <c r="AE82" s="10" t="n"/>
-      <c r="AF82" s="10" t="n"/>
-      <c r="AG82" s="10" t="n"/>
-      <c r="AH82" s="10" t="n"/>
-      <c r="AI82" s="10" t="n"/>
-      <c r="AJ82" s="10" t="n"/>
-      <c r="AK82" s="11" t="n"/>
-    </row>
-    <row r="84" ht="19.5" customHeight="1">
-      <c r="B84" s="40" t="inlineStr">
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="10" t="n"/>
+      <c r="I84" s="10" t="n"/>
+      <c r="J84" s="10" t="n"/>
+      <c r="K84" s="10" t="n"/>
+      <c r="L84" s="10" t="n"/>
+      <c r="M84" s="10" t="n"/>
+      <c r="N84" s="10" t="n"/>
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="10" t="n"/>
+      <c r="Q84" s="10" t="n"/>
+      <c r="R84" s="10" t="n"/>
+      <c r="S84" s="10" t="n"/>
+      <c r="T84" s="10" t="n"/>
+      <c r="U84" s="10" t="n"/>
+      <c r="V84" s="10" t="n"/>
+      <c r="W84" s="10" t="n"/>
+      <c r="X84" s="10" t="n"/>
+      <c r="Y84" s="10" t="n"/>
+      <c r="Z84" s="10" t="n"/>
+      <c r="AA84" s="10" t="n"/>
+      <c r="AB84" s="10" t="n"/>
+      <c r="AC84" s="10" t="n"/>
+      <c r="AD84" s="10" t="n"/>
+      <c r="AE84" s="10" t="n"/>
+      <c r="AF84" s="10" t="n"/>
+      <c r="AG84" s="10" t="n"/>
+      <c r="AH84" s="10" t="n"/>
+      <c r="AI84" s="10" t="n"/>
+      <c r="AJ84" s="10" t="n"/>
+      <c r="AK84" s="11" t="n"/>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
+      <c r="B86" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (Validation Error)）</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="144" customHeight="1">
-      <c r="C85" s="19" t="inlineStr">
+    <row r="87" ht="144" customHeight="1">
+      <c r="C87" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
@@ -16206,50 +16568,50 @@
 }</t>
         </is>
       </c>
-      <c r="D85" s="10" t="n"/>
-      <c r="E85" s="10" t="n"/>
-      <c r="F85" s="10" t="n"/>
-      <c r="G85" s="10" t="n"/>
-      <c r="H85" s="10" t="n"/>
-      <c r="I85" s="10" t="n"/>
-      <c r="J85" s="10" t="n"/>
-      <c r="K85" s="10" t="n"/>
-      <c r="L85" s="10" t="n"/>
-      <c r="M85" s="10" t="n"/>
-      <c r="N85" s="10" t="n"/>
-      <c r="O85" s="10" t="n"/>
-      <c r="P85" s="10" t="n"/>
-      <c r="Q85" s="10" t="n"/>
-      <c r="R85" s="10" t="n"/>
-      <c r="S85" s="10" t="n"/>
-      <c r="T85" s="10" t="n"/>
-      <c r="U85" s="10" t="n"/>
-      <c r="V85" s="10" t="n"/>
-      <c r="W85" s="10" t="n"/>
-      <c r="X85" s="10" t="n"/>
-      <c r="Y85" s="10" t="n"/>
-      <c r="Z85" s="10" t="n"/>
-      <c r="AA85" s="10" t="n"/>
-      <c r="AB85" s="10" t="n"/>
-      <c r="AC85" s="10" t="n"/>
-      <c r="AD85" s="10" t="n"/>
-      <c r="AE85" s="10" t="n"/>
-      <c r="AF85" s="10" t="n"/>
-      <c r="AG85" s="10" t="n"/>
-      <c r="AH85" s="10" t="n"/>
-      <c r="AI85" s="10" t="n"/>
-      <c r="AJ85" s="10" t="n"/>
-      <c r="AK85" s="11" t="n"/>
-    </row>
-    <row r="87" ht="19.5" customHeight="1">
-      <c r="B87" s="40" t="inlineStr">
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="10" t="n"/>
+      <c r="J87" s="10" t="n"/>
+      <c r="K87" s="10" t="n"/>
+      <c r="L87" s="10" t="n"/>
+      <c r="M87" s="10" t="n"/>
+      <c r="N87" s="10" t="n"/>
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="10" t="n"/>
+      <c r="R87" s="10" t="n"/>
+      <c r="S87" s="10" t="n"/>
+      <c r="T87" s="10" t="n"/>
+      <c r="U87" s="10" t="n"/>
+      <c r="V87" s="10" t="n"/>
+      <c r="W87" s="10" t="n"/>
+      <c r="X87" s="10" t="n"/>
+      <c r="Y87" s="10" t="n"/>
+      <c r="Z87" s="10" t="n"/>
+      <c r="AA87" s="10" t="n"/>
+      <c r="AB87" s="10" t="n"/>
+      <c r="AC87" s="10" t="n"/>
+      <c r="AD87" s="10" t="n"/>
+      <c r="AE87" s="10" t="n"/>
+      <c r="AF87" s="10" t="n"/>
+      <c r="AG87" s="10" t="n"/>
+      <c r="AH87" s="10" t="n"/>
+      <c r="AI87" s="10" t="n"/>
+      <c r="AJ87" s="10" t="n"/>
+      <c r="AK87" s="11" t="n"/>
+    </row>
+    <row r="89" ht="19.5" customHeight="1">
+      <c r="B89" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="72" customHeight="1">
-      <c r="C88" s="19" t="inlineStr">
+    <row r="90" ht="72" customHeight="1">
+      <c r="C90" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -16257,50 +16619,50 @@
 }</t>
         </is>
       </c>
-      <c r="D88" s="10" t="n"/>
-      <c r="E88" s="10" t="n"/>
-      <c r="F88" s="10" t="n"/>
-      <c r="G88" s="10" t="n"/>
-      <c r="H88" s="10" t="n"/>
-      <c r="I88" s="10" t="n"/>
-      <c r="J88" s="10" t="n"/>
-      <c r="K88" s="10" t="n"/>
-      <c r="L88" s="10" t="n"/>
-      <c r="M88" s="10" t="n"/>
-      <c r="N88" s="10" t="n"/>
-      <c r="O88" s="10" t="n"/>
-      <c r="P88" s="10" t="n"/>
-      <c r="Q88" s="10" t="n"/>
-      <c r="R88" s="10" t="n"/>
-      <c r="S88" s="10" t="n"/>
-      <c r="T88" s="10" t="n"/>
-      <c r="U88" s="10" t="n"/>
-      <c r="V88" s="10" t="n"/>
-      <c r="W88" s="10" t="n"/>
-      <c r="X88" s="10" t="n"/>
-      <c r="Y88" s="10" t="n"/>
-      <c r="Z88" s="10" t="n"/>
-      <c r="AA88" s="10" t="n"/>
-      <c r="AB88" s="10" t="n"/>
-      <c r="AC88" s="10" t="n"/>
-      <c r="AD88" s="10" t="n"/>
-      <c r="AE88" s="10" t="n"/>
-      <c r="AF88" s="10" t="n"/>
-      <c r="AG88" s="10" t="n"/>
-      <c r="AH88" s="10" t="n"/>
-      <c r="AI88" s="10" t="n"/>
-      <c r="AJ88" s="10" t="n"/>
-      <c r="AK88" s="11" t="n"/>
-    </row>
-    <row r="90" ht="19.5" customHeight="1">
-      <c r="B90" s="40" t="inlineStr">
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="10" t="n"/>
+      <c r="J90" s="10" t="n"/>
+      <c r="K90" s="10" t="n"/>
+      <c r="L90" s="10" t="n"/>
+      <c r="M90" s="10" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="10" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="10" t="n"/>
+      <c r="Y90" s="10" t="n"/>
+      <c r="Z90" s="10" t="n"/>
+      <c r="AA90" s="10" t="n"/>
+      <c r="AB90" s="10" t="n"/>
+      <c r="AC90" s="10" t="n"/>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="10" t="n"/>
+      <c r="AF90" s="10" t="n"/>
+      <c r="AG90" s="10" t="n"/>
+      <c r="AH90" s="10" t="n"/>
+      <c r="AI90" s="10" t="n"/>
+      <c r="AJ90" s="10" t="n"/>
+      <c r="AK90" s="11" t="n"/>
+    </row>
+    <row r="92" ht="19.5" customHeight="1">
+      <c r="B92" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="72" customHeight="1">
-      <c r="C91" s="19" t="inlineStr">
+    <row r="93" ht="72" customHeight="1">
+      <c r="C93" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -16308,50 +16670,50 @@
 }</t>
         </is>
       </c>
-      <c r="D91" s="10" t="n"/>
-      <c r="E91" s="10" t="n"/>
-      <c r="F91" s="10" t="n"/>
-      <c r="G91" s="10" t="n"/>
-      <c r="H91" s="10" t="n"/>
-      <c r="I91" s="10" t="n"/>
-      <c r="J91" s="10" t="n"/>
-      <c r="K91" s="10" t="n"/>
-      <c r="L91" s="10" t="n"/>
-      <c r="M91" s="10" t="n"/>
-      <c r="N91" s="10" t="n"/>
-      <c r="O91" s="10" t="n"/>
-      <c r="P91" s="10" t="n"/>
-      <c r="Q91" s="10" t="n"/>
-      <c r="R91" s="10" t="n"/>
-      <c r="S91" s="10" t="n"/>
-      <c r="T91" s="10" t="n"/>
-      <c r="U91" s="10" t="n"/>
-      <c r="V91" s="10" t="n"/>
-      <c r="W91" s="10" t="n"/>
-      <c r="X91" s="10" t="n"/>
-      <c r="Y91" s="10" t="n"/>
-      <c r="Z91" s="10" t="n"/>
-      <c r="AA91" s="10" t="n"/>
-      <c r="AB91" s="10" t="n"/>
-      <c r="AC91" s="10" t="n"/>
-      <c r="AD91" s="10" t="n"/>
-      <c r="AE91" s="10" t="n"/>
-      <c r="AF91" s="10" t="n"/>
-      <c r="AG91" s="10" t="n"/>
-      <c r="AH91" s="10" t="n"/>
-      <c r="AI91" s="10" t="n"/>
-      <c r="AJ91" s="10" t="n"/>
-      <c r="AK91" s="11" t="n"/>
-    </row>
-    <row r="93" ht="19.5" customHeight="1">
-      <c r="B93" s="40" t="inlineStr">
+      <c r="D93" s="10" t="n"/>
+      <c r="E93" s="10" t="n"/>
+      <c r="F93" s="10" t="n"/>
+      <c r="G93" s="10" t="n"/>
+      <c r="H93" s="10" t="n"/>
+      <c r="I93" s="10" t="n"/>
+      <c r="J93" s="10" t="n"/>
+      <c r="K93" s="10" t="n"/>
+      <c r="L93" s="10" t="n"/>
+      <c r="M93" s="10" t="n"/>
+      <c r="N93" s="10" t="n"/>
+      <c r="O93" s="10" t="n"/>
+      <c r="P93" s="10" t="n"/>
+      <c r="Q93" s="10" t="n"/>
+      <c r="R93" s="10" t="n"/>
+      <c r="S93" s="10" t="n"/>
+      <c r="T93" s="10" t="n"/>
+      <c r="U93" s="10" t="n"/>
+      <c r="V93" s="10" t="n"/>
+      <c r="W93" s="10" t="n"/>
+      <c r="X93" s="10" t="n"/>
+      <c r="Y93" s="10" t="n"/>
+      <c r="Z93" s="10" t="n"/>
+      <c r="AA93" s="10" t="n"/>
+      <c r="AB93" s="10" t="n"/>
+      <c r="AC93" s="10" t="n"/>
+      <c r="AD93" s="10" t="n"/>
+      <c r="AE93" s="10" t="n"/>
+      <c r="AF93" s="10" t="n"/>
+      <c r="AG93" s="10" t="n"/>
+      <c r="AH93" s="10" t="n"/>
+      <c r="AI93" s="10" t="n"/>
+      <c r="AJ93" s="10" t="n"/>
+      <c r="AK93" s="11" t="n"/>
+    </row>
+    <row r="95" ht="19.5" customHeight="1">
+      <c r="B95" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Data Scope Violation）</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="72" customHeight="1">
-      <c r="C94" s="19" t="inlineStr">
+    <row r="96" ht="72" customHeight="1">
+      <c r="C96" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "DATA_SCOPE_VIOLATION",
@@ -16359,101 +16721,101 @@
 }</t>
         </is>
       </c>
-      <c r="D94" s="10" t="n"/>
-      <c r="E94" s="10" t="n"/>
-      <c r="F94" s="10" t="n"/>
-      <c r="G94" s="10" t="n"/>
-      <c r="H94" s="10" t="n"/>
-      <c r="I94" s="10" t="n"/>
-      <c r="J94" s="10" t="n"/>
-      <c r="K94" s="10" t="n"/>
-      <c r="L94" s="10" t="n"/>
-      <c r="M94" s="10" t="n"/>
-      <c r="N94" s="10" t="n"/>
-      <c r="O94" s="10" t="n"/>
-      <c r="P94" s="10" t="n"/>
-      <c r="Q94" s="10" t="n"/>
-      <c r="R94" s="10" t="n"/>
-      <c r="S94" s="10" t="n"/>
-      <c r="T94" s="10" t="n"/>
-      <c r="U94" s="10" t="n"/>
-      <c r="V94" s="10" t="n"/>
-      <c r="W94" s="10" t="n"/>
-      <c r="X94" s="10" t="n"/>
-      <c r="Y94" s="10" t="n"/>
-      <c r="Z94" s="10" t="n"/>
-      <c r="AA94" s="10" t="n"/>
-      <c r="AB94" s="10" t="n"/>
-      <c r="AC94" s="10" t="n"/>
-      <c r="AD94" s="10" t="n"/>
-      <c r="AE94" s="10" t="n"/>
-      <c r="AF94" s="10" t="n"/>
-      <c r="AG94" s="10" t="n"/>
-      <c r="AH94" s="10" t="n"/>
-      <c r="AI94" s="10" t="n"/>
-      <c r="AJ94" s="10" t="n"/>
-      <c r="AK94" s="11" t="n"/>
-    </row>
-    <row r="96" ht="19.5" customHeight="1">
-      <c r="B96" s="40" t="inlineStr">
+      <c r="D96" s="10" t="n"/>
+      <c r="E96" s="10" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
+      <c r="H96" s="10" t="n"/>
+      <c r="I96" s="10" t="n"/>
+      <c r="J96" s="10" t="n"/>
+      <c r="K96" s="10" t="n"/>
+      <c r="L96" s="10" t="n"/>
+      <c r="M96" s="10" t="n"/>
+      <c r="N96" s="10" t="n"/>
+      <c r="O96" s="10" t="n"/>
+      <c r="P96" s="10" t="n"/>
+      <c r="Q96" s="10" t="n"/>
+      <c r="R96" s="10" t="n"/>
+      <c r="S96" s="10" t="n"/>
+      <c r="T96" s="10" t="n"/>
+      <c r="U96" s="10" t="n"/>
+      <c r="V96" s="10" t="n"/>
+      <c r="W96" s="10" t="n"/>
+      <c r="X96" s="10" t="n"/>
+      <c r="Y96" s="10" t="n"/>
+      <c r="Z96" s="10" t="n"/>
+      <c r="AA96" s="10" t="n"/>
+      <c r="AB96" s="10" t="n"/>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="10" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="10" t="n"/>
+      <c r="AK96" s="11" t="n"/>
+    </row>
+    <row r="98" ht="19.5" customHeight="1">
+      <c r="B98" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 404 Not Found）</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="72" customHeight="1">
-      <c r="C97" s="19" t="inlineStr">
+    <row r="99" ht="72" customHeight="1">
+      <c r="C99" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "HANBAITEN_NOT_FOUND",
+  "error_code": "NOT_FOUND",
   "message": "指定された販売店が見つかりません"
 }</t>
         </is>
       </c>
-      <c r="D97" s="10" t="n"/>
-      <c r="E97" s="10" t="n"/>
-      <c r="F97" s="10" t="n"/>
-      <c r="G97" s="10" t="n"/>
-      <c r="H97" s="10" t="n"/>
-      <c r="I97" s="10" t="n"/>
-      <c r="J97" s="10" t="n"/>
-      <c r="K97" s="10" t="n"/>
-      <c r="L97" s="10" t="n"/>
-      <c r="M97" s="10" t="n"/>
-      <c r="N97" s="10" t="n"/>
-      <c r="O97" s="10" t="n"/>
-      <c r="P97" s="10" t="n"/>
-      <c r="Q97" s="10" t="n"/>
-      <c r="R97" s="10" t="n"/>
-      <c r="S97" s="10" t="n"/>
-      <c r="T97" s="10" t="n"/>
-      <c r="U97" s="10" t="n"/>
-      <c r="V97" s="10" t="n"/>
-      <c r="W97" s="10" t="n"/>
-      <c r="X97" s="10" t="n"/>
-      <c r="Y97" s="10" t="n"/>
-      <c r="Z97" s="10" t="n"/>
-      <c r="AA97" s="10" t="n"/>
-      <c r="AB97" s="10" t="n"/>
-      <c r="AC97" s="10" t="n"/>
-      <c r="AD97" s="10" t="n"/>
-      <c r="AE97" s="10" t="n"/>
-      <c r="AF97" s="10" t="n"/>
-      <c r="AG97" s="10" t="n"/>
-      <c r="AH97" s="10" t="n"/>
-      <c r="AI97" s="10" t="n"/>
-      <c r="AJ97" s="10" t="n"/>
-      <c r="AK97" s="11" t="n"/>
-    </row>
-    <row r="99" ht="19.5" customHeight="1">
-      <c r="B99" s="40" t="inlineStr">
+      <c r="D99" s="10" t="n"/>
+      <c r="E99" s="10" t="n"/>
+      <c r="F99" s="10" t="n"/>
+      <c r="G99" s="10" t="n"/>
+      <c r="H99" s="10" t="n"/>
+      <c r="I99" s="10" t="n"/>
+      <c r="J99" s="10" t="n"/>
+      <c r="K99" s="10" t="n"/>
+      <c r="L99" s="10" t="n"/>
+      <c r="M99" s="10" t="n"/>
+      <c r="N99" s="10" t="n"/>
+      <c r="O99" s="10" t="n"/>
+      <c r="P99" s="10" t="n"/>
+      <c r="Q99" s="10" t="n"/>
+      <c r="R99" s="10" t="n"/>
+      <c r="S99" s="10" t="n"/>
+      <c r="T99" s="10" t="n"/>
+      <c r="U99" s="10" t="n"/>
+      <c r="V99" s="10" t="n"/>
+      <c r="W99" s="10" t="n"/>
+      <c r="X99" s="10" t="n"/>
+      <c r="Y99" s="10" t="n"/>
+      <c r="Z99" s="10" t="n"/>
+      <c r="AA99" s="10" t="n"/>
+      <c r="AB99" s="10" t="n"/>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="10" t="n"/>
+      <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="10" t="n"/>
+      <c r="AK99" s="11" t="n"/>
+    </row>
+    <row r="101" ht="19.5" customHeight="1">
+      <c r="B101" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="72" customHeight="1">
-      <c r="C100" s="19" t="inlineStr">
+    <row r="102" ht="72" customHeight="1">
+      <c r="C102" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -16461,240 +16823,277 @@
 }</t>
         </is>
       </c>
-      <c r="D100" s="10" t="n"/>
-      <c r="E100" s="10" t="n"/>
-      <c r="F100" s="10" t="n"/>
-      <c r="G100" s="10" t="n"/>
-      <c r="H100" s="10" t="n"/>
-      <c r="I100" s="10" t="n"/>
-      <c r="J100" s="10" t="n"/>
-      <c r="K100" s="10" t="n"/>
-      <c r="L100" s="10" t="n"/>
-      <c r="M100" s="10" t="n"/>
-      <c r="N100" s="10" t="n"/>
-      <c r="O100" s="10" t="n"/>
-      <c r="P100" s="10" t="n"/>
-      <c r="Q100" s="10" t="n"/>
-      <c r="R100" s="10" t="n"/>
-      <c r="S100" s="10" t="n"/>
-      <c r="T100" s="10" t="n"/>
-      <c r="U100" s="10" t="n"/>
-      <c r="V100" s="10" t="n"/>
-      <c r="W100" s="10" t="n"/>
-      <c r="X100" s="10" t="n"/>
-      <c r="Y100" s="10" t="n"/>
-      <c r="Z100" s="10" t="n"/>
-      <c r="AA100" s="10" t="n"/>
-      <c r="AB100" s="10" t="n"/>
-      <c r="AC100" s="10" t="n"/>
-      <c r="AD100" s="10" t="n"/>
-      <c r="AE100" s="10" t="n"/>
-      <c r="AF100" s="10" t="n"/>
-      <c r="AG100" s="10" t="n"/>
-      <c r="AH100" s="10" t="n"/>
-      <c r="AI100" s="10" t="n"/>
-      <c r="AJ100" s="10" t="n"/>
-      <c r="AK100" s="11" t="n"/>
-    </row>
-    <row r="102" ht="19.5" customHeight="1"/>
-    <row r="103" ht="19.5" customHeight="1">
-      <c r="A103" s="27" t="inlineStr">
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="10" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="10" t="n"/>
+      <c r="I102" s="10" t="n"/>
+      <c r="J102" s="10" t="n"/>
+      <c r="K102" s="10" t="n"/>
+      <c r="L102" s="10" t="n"/>
+      <c r="M102" s="10" t="n"/>
+      <c r="N102" s="10" t="n"/>
+      <c r="O102" s="10" t="n"/>
+      <c r="P102" s="10" t="n"/>
+      <c r="Q102" s="10" t="n"/>
+      <c r="R102" s="10" t="n"/>
+      <c r="S102" s="10" t="n"/>
+      <c r="T102" s="10" t="n"/>
+      <c r="U102" s="10" t="n"/>
+      <c r="V102" s="10" t="n"/>
+      <c r="W102" s="10" t="n"/>
+      <c r="X102" s="10" t="n"/>
+      <c r="Y102" s="10" t="n"/>
+      <c r="Z102" s="10" t="n"/>
+      <c r="AA102" s="10" t="n"/>
+      <c r="AB102" s="10" t="n"/>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="10" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="10" t="n"/>
+      <c r="AK102" s="11" t="n"/>
+    </row>
+    <row r="104" ht="19.5" customHeight="1"/>
+    <row r="105" ht="19.5" customHeight="1">
+      <c r="A105" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="B104" s="27" t="inlineStr">
+    <row r="106" ht="54" customHeight="1">
+      <c r="B106" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="n"/>
+      <c r="D106" s="10" t="n"/>
+      <c r="E106" s="10" t="n"/>
+      <c r="F106" s="10" t="n"/>
+      <c r="G106" s="10" t="n"/>
+      <c r="H106" s="10" t="n"/>
+      <c r="I106" s="10" t="n"/>
+      <c r="J106" s="10" t="n"/>
+      <c r="K106" s="10" t="n"/>
+      <c r="L106" s="10" t="n"/>
+      <c r="M106" s="10" t="n"/>
+      <c r="N106" s="10" t="n"/>
+      <c r="O106" s="10" t="n"/>
+      <c r="P106" s="10" t="n"/>
+      <c r="Q106" s="10" t="n"/>
+      <c r="R106" s="10" t="n"/>
+      <c r="S106" s="10" t="n"/>
+      <c r="T106" s="10" t="n"/>
+      <c r="U106" s="10" t="n"/>
+      <c r="V106" s="10" t="n"/>
+      <c r="W106" s="10" t="n"/>
+      <c r="X106" s="10" t="n"/>
+      <c r="Y106" s="10" t="n"/>
+      <c r="Z106" s="10" t="n"/>
+      <c r="AA106" s="10" t="n"/>
+      <c r="AB106" s="10" t="n"/>
+      <c r="AC106" s="10" t="n"/>
+      <c r="AD106" s="10" t="n"/>
+      <c r="AE106" s="10" t="n"/>
+      <c r="AF106" s="10" t="n"/>
+      <c r="AG106" s="10" t="n"/>
+      <c r="AH106" s="10" t="n"/>
+      <c r="AI106" s="10" t="n"/>
+      <c r="AJ106" s="10" t="n"/>
+      <c r="AK106" s="11" t="n"/>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="B107" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="C105" s="41" t="inlineStr">
+    <row r="108" ht="18" customHeight="1">
+      <c r="C108" s="41" t="inlineStr">
         <is>
           <t>パスパラメータ：hanbaiten_id 数値型チェック、必須</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="C106" s="41" t="inlineStr">
+    <row r="109" ht="18" customHeight="1">
+      <c r="C109" s="41" t="inlineStr">
         <is>
           <t>リクエストボディ：</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="D107" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_name：必須、最大100桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="D108" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_name_kana：最大100桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="D109" s="41" t="inlineStr">
-        <is>
-          <t>torihikisaki_no：最大20桁</t>
         </is>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="D110" s="41" t="inlineStr">
         <is>
-          <t>yubin_no：最大7桁（郵便番号形式チェック）</t>
+          <t>hanbaiten_name：必須、最大100桁</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="D111" s="41" t="inlineStr">
         <is>
-          <t>address：最大200桁</t>
+          <t>hanbaiten_name_kana：最大100桁</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="D112" s="41" t="inlineStr">
         <is>
-          <t>tel：最大15桁</t>
+          <t>torihikisaki_no：最大20桁</t>
         </is>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="D113" s="41" t="inlineStr">
         <is>
-          <t>fax：最大15桁</t>
+          <t>yubin_no：最大7桁（郵便番号形式チェック）</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
       <c r="D114" s="41" t="inlineStr">
         <is>
-          <t>shocho_name：最大50桁</t>
+          <t>address：最大200桁</t>
         </is>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1">
       <c r="D115" s="41" t="inlineStr">
         <is>
-          <t>itaku_kubun：1, 2, 9 のいずれか</t>
+          <t>tel：最大15桁</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="D116" s="41" t="inlineStr">
         <is>
-          <t>haitatsuryo_tanka_id：数値型チェック</t>
+          <t>shocho_name：最大50桁</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="D117" s="41" t="inlineStr">
         <is>
-          <t>haitatsuryo_shiharai_cycle：数値型チェック、≧ 0</t>
+          <t>itaku_kubun：1, 2, 9 のいずれか</t>
         </is>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="D118" s="41" t="inlineStr">
         <is>
-          <t>tesuryo_kubun：1, 2 のいずれか</t>
+          <t>haitatsuryo_tanka_id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="D119" s="41" t="inlineStr">
         <is>
-          <t>tesuryo_amount：数値型チェック、≧ 0</t>
+          <t>tesuryo_kubun：1, 2 のいずれか</t>
         </is>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1">
       <c r="D120" s="41" t="inlineStr">
         <is>
-          <t>itaku_kubun = 1（振込）の場合：</t>
+          <t>tesuryo_amount：数値型チェック、≧ 0</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="D121" s="41" t="inlineStr">
         <is>
-          <t>koza_meigi：最大50桁</t>
+          <t>itaku_kubun = 1（振込）の場合：</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="D122" s="41" t="inlineStr">
         <is>
+          <t>koza_meigi：最大50桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="D123" s="41" t="inlineStr">
+        <is>
+          <t>haiten_flg：Boolean型チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="D124" s="41" t="inlineStr">
+        <is>
           <t>biko：テキスト型</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="C123" s="41" t="inlineStr">
-        <is>
-          <t>バリデーションエラーの場合：HTTP 400 (`VALIDATION_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="18" customHeight="1">
-      <c r="B124" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1">
       <c r="C125" s="41" t="inlineStr">
         <is>
+          <t>バリデーションエラーの場合：HTTP 400 (`VALIDATION_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="B126" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="C127" s="41" t="inlineStr">
+        <is>
           <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="18" customHeight="1">
-      <c r="C126" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：`hanbaiten.update` を保持しているか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="36" customHeight="1">
-      <c r="D127" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="C128" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="B129" s="27" t="inlineStr">
-        <is>
-          <t>4.3 対象レコードの存在確認</t>
+          <t>権限チェック：`hanbaiten.update` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="36" customHeight="1">
+      <c r="D129" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="C130" s="41" t="inlineStr">
         <is>
+          <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="B131" s="27" t="inlineStr">
+        <is>
+          <t>4.3 対象レコードの存在確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="C132" s="41" t="inlineStr">
+        <is>
           <t>ログインユーザーのスコープを取得する（ja_id）。</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="72" customHeight="1">
-      <c r="C131" s="42" t="inlineStr">
+    <row r="133" ht="72" customHeight="1">
+      <c r="C133" s="42" t="inlineStr">
         <is>
           <t>SELECT * FROM m_hanbaiten
 WHERE hanbaiten_id = :hanbaiten_id
@@ -16702,64 +17101,64 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D131" s="10" t="n"/>
-      <c r="E131" s="10" t="n"/>
-      <c r="F131" s="10" t="n"/>
-      <c r="G131" s="10" t="n"/>
-      <c r="H131" s="10" t="n"/>
-      <c r="I131" s="10" t="n"/>
-      <c r="J131" s="10" t="n"/>
-      <c r="K131" s="10" t="n"/>
-      <c r="L131" s="10" t="n"/>
-      <c r="M131" s="10" t="n"/>
-      <c r="N131" s="10" t="n"/>
-      <c r="O131" s="10" t="n"/>
-      <c r="P131" s="10" t="n"/>
-      <c r="Q131" s="10" t="n"/>
-      <c r="R131" s="10" t="n"/>
-      <c r="S131" s="10" t="n"/>
-      <c r="T131" s="10" t="n"/>
-      <c r="U131" s="10" t="n"/>
-      <c r="V131" s="10" t="n"/>
-      <c r="W131" s="10" t="n"/>
-      <c r="X131" s="10" t="n"/>
-      <c r="Y131" s="10" t="n"/>
-      <c r="Z131" s="10" t="n"/>
-      <c r="AA131" s="10" t="n"/>
-      <c r="AB131" s="10" t="n"/>
-      <c r="AC131" s="10" t="n"/>
-      <c r="AD131" s="10" t="n"/>
-      <c r="AE131" s="10" t="n"/>
-      <c r="AF131" s="10" t="n"/>
-      <c r="AG131" s="10" t="n"/>
-      <c r="AH131" s="10" t="n"/>
-      <c r="AI131" s="10" t="n"/>
-      <c r="AJ131" s="10" t="n"/>
-      <c r="AK131" s="11" t="n"/>
-    </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="C132" s="41" t="inlineStr">
-        <is>
-          <t>レコードが存在しない場合：HTTP 404 (`HANBAITEN_NOT_FOUND`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="C133" s="41" t="inlineStr">
+      <c r="D133" s="10" t="n"/>
+      <c r="E133" s="10" t="n"/>
+      <c r="F133" s="10" t="n"/>
+      <c r="G133" s="10" t="n"/>
+      <c r="H133" s="10" t="n"/>
+      <c r="I133" s="10" t="n"/>
+      <c r="J133" s="10" t="n"/>
+      <c r="K133" s="10" t="n"/>
+      <c r="L133" s="10" t="n"/>
+      <c r="M133" s="10" t="n"/>
+      <c r="N133" s="10" t="n"/>
+      <c r="O133" s="10" t="n"/>
+      <c r="P133" s="10" t="n"/>
+      <c r="Q133" s="10" t="n"/>
+      <c r="R133" s="10" t="n"/>
+      <c r="S133" s="10" t="n"/>
+      <c r="T133" s="10" t="n"/>
+      <c r="U133" s="10" t="n"/>
+      <c r="V133" s="10" t="n"/>
+      <c r="W133" s="10" t="n"/>
+      <c r="X133" s="10" t="n"/>
+      <c r="Y133" s="10" t="n"/>
+      <c r="Z133" s="10" t="n"/>
+      <c r="AA133" s="10" t="n"/>
+      <c r="AB133" s="10" t="n"/>
+      <c r="AC133" s="10" t="n"/>
+      <c r="AD133" s="10" t="n"/>
+      <c r="AE133" s="10" t="n"/>
+      <c r="AF133" s="10" t="n"/>
+      <c r="AG133" s="10" t="n"/>
+      <c r="AH133" s="10" t="n"/>
+      <c r="AI133" s="10" t="n"/>
+      <c r="AJ133" s="10" t="n"/>
+      <c r="AK133" s="11" t="n"/>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="C134" s="41" t="inlineStr">
+        <is>
+          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="C135" s="41" t="inlineStr">
         <is>
           <t>ja_id が一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="18" customHeight="1">
-      <c r="B134" s="27" t="inlineStr">
+    <row r="136" ht="18" customHeight="1">
+      <c r="B136" s="27" t="inlineStr">
         <is>
           <t>4.4 データ更新</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="409" customHeight="1">
-      <c r="C135" s="42" t="inlineStr">
+    <row r="137" ht="409" customHeight="1">
+      <c r="C137" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_hanbaiten
 SET hanbaiten_name = :hanbaiten_name,
@@ -16782,6 +17181,7 @@
     yokin_shubetsu = :yokin_shubetsu,
     koza_no = :koza_no,
     koza_meigi = :koza_meigi,
+    haiten_flg = :haiten_flg,
     biko = :biko,
     updated_at = NOW(),
     updated_by = :user_account_id
@@ -16791,64 +17191,64 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D135" s="10" t="n"/>
-      <c r="E135" s="10" t="n"/>
-      <c r="F135" s="10" t="n"/>
-      <c r="G135" s="10" t="n"/>
-      <c r="H135" s="10" t="n"/>
-      <c r="I135" s="10" t="n"/>
-      <c r="J135" s="10" t="n"/>
-      <c r="K135" s="10" t="n"/>
-      <c r="L135" s="10" t="n"/>
-      <c r="M135" s="10" t="n"/>
-      <c r="N135" s="10" t="n"/>
-      <c r="O135" s="10" t="n"/>
-      <c r="P135" s="10" t="n"/>
-      <c r="Q135" s="10" t="n"/>
-      <c r="R135" s="10" t="n"/>
-      <c r="S135" s="10" t="n"/>
-      <c r="T135" s="10" t="n"/>
-      <c r="U135" s="10" t="n"/>
-      <c r="V135" s="10" t="n"/>
-      <c r="W135" s="10" t="n"/>
-      <c r="X135" s="10" t="n"/>
-      <c r="Y135" s="10" t="n"/>
-      <c r="Z135" s="10" t="n"/>
-      <c r="AA135" s="10" t="n"/>
-      <c r="AB135" s="10" t="n"/>
-      <c r="AC135" s="10" t="n"/>
-      <c r="AD135" s="10" t="n"/>
-      <c r="AE135" s="10" t="n"/>
-      <c r="AF135" s="10" t="n"/>
-      <c r="AG135" s="10" t="n"/>
-      <c r="AH135" s="10" t="n"/>
-      <c r="AI135" s="10" t="n"/>
-      <c r="AJ135" s="10" t="n"/>
-      <c r="AK135" s="11" t="n"/>
-    </row>
-    <row r="136" ht="18" customHeight="1">
-      <c r="B136" s="27" t="inlineStr">
+      <c r="D137" s="10" t="n"/>
+      <c r="E137" s="10" t="n"/>
+      <c r="F137" s="10" t="n"/>
+      <c r="G137" s="10" t="n"/>
+      <c r="H137" s="10" t="n"/>
+      <c r="I137" s="10" t="n"/>
+      <c r="J137" s="10" t="n"/>
+      <c r="K137" s="10" t="n"/>
+      <c r="L137" s="10" t="n"/>
+      <c r="M137" s="10" t="n"/>
+      <c r="N137" s="10" t="n"/>
+      <c r="O137" s="10" t="n"/>
+      <c r="P137" s="10" t="n"/>
+      <c r="Q137" s="10" t="n"/>
+      <c r="R137" s="10" t="n"/>
+      <c r="S137" s="10" t="n"/>
+      <c r="T137" s="10" t="n"/>
+      <c r="U137" s="10" t="n"/>
+      <c r="V137" s="10" t="n"/>
+      <c r="W137" s="10" t="n"/>
+      <c r="X137" s="10" t="n"/>
+      <c r="Y137" s="10" t="n"/>
+      <c r="Z137" s="10" t="n"/>
+      <c r="AA137" s="10" t="n"/>
+      <c r="AB137" s="10" t="n"/>
+      <c r="AC137" s="10" t="n"/>
+      <c r="AD137" s="10" t="n"/>
+      <c r="AE137" s="10" t="n"/>
+      <c r="AF137" s="10" t="n"/>
+      <c r="AG137" s="10" t="n"/>
+      <c r="AH137" s="10" t="n"/>
+      <c r="AI137" s="10" t="n"/>
+      <c r="AJ137" s="10" t="n"/>
+      <c r="AK137" s="11" t="n"/>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="B138" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="18" customHeight="1">
-      <c r="C137" s="41" t="inlineStr">
+    <row r="139" ht="18" customHeight="1">
+      <c r="C139" s="41" t="inlineStr">
         <is>
           <t>更新前データを取得（4.3 のSELECT結果）し、`before_value` に格納する。</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="C138" s="41" t="inlineStr">
+    <row r="140" ht="18" customHeight="1">
+      <c r="C140" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="216" customHeight="1">
-      <c r="C139" s="42" t="inlineStr">
+    <row r="141" ht="216" customHeight="1">
+      <c r="C141" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -16862,140 +17262,6 @@
         :before_value_json, :after_value_json,
         '', '',
         :ip_address, :user_agent)</t>
-        </is>
-      </c>
-      <c r="D139" s="10" t="n"/>
-      <c r="E139" s="10" t="n"/>
-      <c r="F139" s="10" t="n"/>
-      <c r="G139" s="10" t="n"/>
-      <c r="H139" s="10" t="n"/>
-      <c r="I139" s="10" t="n"/>
-      <c r="J139" s="10" t="n"/>
-      <c r="K139" s="10" t="n"/>
-      <c r="L139" s="10" t="n"/>
-      <c r="M139" s="10" t="n"/>
-      <c r="N139" s="10" t="n"/>
-      <c r="O139" s="10" t="n"/>
-      <c r="P139" s="10" t="n"/>
-      <c r="Q139" s="10" t="n"/>
-      <c r="R139" s="10" t="n"/>
-      <c r="S139" s="10" t="n"/>
-      <c r="T139" s="10" t="n"/>
-      <c r="U139" s="10" t="n"/>
-      <c r="V139" s="10" t="n"/>
-      <c r="W139" s="10" t="n"/>
-      <c r="X139" s="10" t="n"/>
-      <c r="Y139" s="10" t="n"/>
-      <c r="Z139" s="10" t="n"/>
-      <c r="AA139" s="10" t="n"/>
-      <c r="AB139" s="10" t="n"/>
-      <c r="AC139" s="10" t="n"/>
-      <c r="AD139" s="10" t="n"/>
-      <c r="AE139" s="10" t="n"/>
-      <c r="AF139" s="10" t="n"/>
-      <c r="AG139" s="10" t="n"/>
-      <c r="AH139" s="10" t="n"/>
-      <c r="AI139" s="10" t="n"/>
-      <c r="AJ139" s="10" t="n"/>
-      <c r="AK139" s="11" t="n"/>
-    </row>
-    <row r="140" ht="409" customHeight="1">
-      <c r="C140" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：更新前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-{
-  "hanbaiten_id": 1,
-  "ja_id": 1,
-  "hanbaiten_code": "H001",
-  "hanbaiten_name": "販売店A",
-  "hanbaiten_name_kana": "ハンバイテンA",
-  "torihikisaki_no": "1234567890123",
-  "yubin_no": "1000001",
-  "address": "東京都千代田区1-1-1",
-  "tel": "03-1234-5678",
-  "fax": "03-1234-5679",
-  "shocho_name": "山田太郎",
-  "itaku_kubun": 1,
-  "haitatsuryo_tanka_id": 10,
-  "haitatsuryo_shiharai_cycle": 1,
-  "tesuryo_kubun": 1,
-  "tesuryo_amount": 500.00,
-  "bank_code": "0001",
-  "bank_name": "○○銀行",
-  "bank_branch_code": "001",
-  "bank_branch_name": "東京支店",
-  "yokin_shubetsu": 1,
-  "koza_no": "1234567",
-  "koza_meigi": "販売店A代表",
-  "biko": "特別な対応なし"
-}</t>
-        </is>
-      </c>
-      <c r="D140" s="10" t="n"/>
-      <c r="E140" s="10" t="n"/>
-      <c r="F140" s="10" t="n"/>
-      <c r="G140" s="10" t="n"/>
-      <c r="H140" s="10" t="n"/>
-      <c r="I140" s="10" t="n"/>
-      <c r="J140" s="10" t="n"/>
-      <c r="K140" s="10" t="n"/>
-      <c r="L140" s="10" t="n"/>
-      <c r="M140" s="10" t="n"/>
-      <c r="N140" s="10" t="n"/>
-      <c r="O140" s="10" t="n"/>
-      <c r="P140" s="10" t="n"/>
-      <c r="Q140" s="10" t="n"/>
-      <c r="R140" s="10" t="n"/>
-      <c r="S140" s="10" t="n"/>
-      <c r="T140" s="10" t="n"/>
-      <c r="U140" s="10" t="n"/>
-      <c r="V140" s="10" t="n"/>
-      <c r="W140" s="10" t="n"/>
-      <c r="X140" s="10" t="n"/>
-      <c r="Y140" s="10" t="n"/>
-      <c r="Z140" s="10" t="n"/>
-      <c r="AA140" s="10" t="n"/>
-      <c r="AB140" s="10" t="n"/>
-      <c r="AC140" s="10" t="n"/>
-      <c r="AD140" s="10" t="n"/>
-      <c r="AE140" s="10" t="n"/>
-      <c r="AF140" s="10" t="n"/>
-      <c r="AG140" s="10" t="n"/>
-      <c r="AH140" s="10" t="n"/>
-      <c r="AI140" s="10" t="n"/>
-      <c r="AJ140" s="10" t="n"/>
-      <c r="AK140" s="11" t="n"/>
-    </row>
-    <row r="141" ht="409" customHeight="1">
-      <c r="C141" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> `after_value`：更新後のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-{
-  "hanbaiten_id": 1,
-  "ja_id": 1,
-  "hanbaiten_code": "H001",
-  "hanbaiten_name": "販売店A改定",
-  "hanbaiten_name_kana": "ハンバイテンA",
-  "torihikisaki_no": "1234567890123",
-  "yubin_no": "1000001",
-  "address": "東京都千代田区1-1-1",
-  "tel": "03-1234-5678",
-  "fax": "03-1234-5679",
-  "shocho_name": "山田太郎",
-  "itaku_kubun": 1,
-  "haitatsuryo_tanka_id": 10,
-  "haitatsuryo_shiharai_cycle": 1,
-  "tesuryo_kubun": 1,
-  "tesuryo_amount": 600.00,
-  "bank_code": "0001",
-  "bank_name": "○○銀行",
-  "bank_branch_code": "001",
-  "bank_branch_name": "東京支店",
-  "yokin_shubetsu": 1,
-  "koza_no": "1234567",
-  "koza_meigi": "販売店A代表",
-  "biko": "更新しました"
-}</t>
         </is>
       </c>
       <c r="D141" s="10" t="n"/>
@@ -17033,43 +17299,179 @@
       <c r="AJ141" s="10" t="n"/>
       <c r="AK141" s="11" t="n"/>
     </row>
-    <row r="142" ht="18" customHeight="1">
-      <c r="B142" s="27" t="inlineStr">
-        <is>
-          <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="C143" s="41" t="inlineStr">
-        <is>
-          <t>更新されたデータをdata オブジェクトとして返却する。HTTP 200。</t>
-        </is>
-      </c>
+    <row r="142" ht="409" customHeight="1">
+      <c r="C142" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：更新前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+{
+  "hanbaiten_id": 1,
+  "ja_id": 1,
+  "hanbaiten_code": "H001",
+  "hanbaiten_name": "販売店A",
+  "hanbaiten_name_kana": "ハンバイテンA",
+  "torihikisaki_no": "1234567890123",
+  "yubin_no": "1000001",
+  "address": "東京都千代田区1-1-1",
+  "tel": "03-1234-5678",
+  "fax": "03-1234-5679",
+  "shocho_name": "山田太郎",
+  "itaku_kubun": 1,
+  "haitatsuryo_tanka_id": 10,
+  "haitatsuryo_shiharai_cycle": 1,
+  "tesuryo_kubun": 1,
+  "tesuryo_amount": 500.00,
+  "bank_code": "0001",
+  "bank_name": "○○銀行",
+  "bank_branch_code": "001",
+  "bank_branch_name": "東京支店",
+  "yokin_shubetsu": 1,
+  "koza_no": "1234567",
+  "koza_meigi": "販売店A代表",
+  "haiten_flg": false,
+  "biko": "特別な対応なし"
+}</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="n"/>
+      <c r="E142" s="10" t="n"/>
+      <c r="F142" s="10" t="n"/>
+      <c r="G142" s="10" t="n"/>
+      <c r="H142" s="10" t="n"/>
+      <c r="I142" s="10" t="n"/>
+      <c r="J142" s="10" t="n"/>
+      <c r="K142" s="10" t="n"/>
+      <c r="L142" s="10" t="n"/>
+      <c r="M142" s="10" t="n"/>
+      <c r="N142" s="10" t="n"/>
+      <c r="O142" s="10" t="n"/>
+      <c r="P142" s="10" t="n"/>
+      <c r="Q142" s="10" t="n"/>
+      <c r="R142" s="10" t="n"/>
+      <c r="S142" s="10" t="n"/>
+      <c r="T142" s="10" t="n"/>
+      <c r="U142" s="10" t="n"/>
+      <c r="V142" s="10" t="n"/>
+      <c r="W142" s="10" t="n"/>
+      <c r="X142" s="10" t="n"/>
+      <c r="Y142" s="10" t="n"/>
+      <c r="Z142" s="10" t="n"/>
+      <c r="AA142" s="10" t="n"/>
+      <c r="AB142" s="10" t="n"/>
+      <c r="AC142" s="10" t="n"/>
+      <c r="AD142" s="10" t="n"/>
+      <c r="AE142" s="10" t="n"/>
+      <c r="AF142" s="10" t="n"/>
+      <c r="AG142" s="10" t="n"/>
+      <c r="AH142" s="10" t="n"/>
+      <c r="AI142" s="10" t="n"/>
+      <c r="AJ142" s="10" t="n"/>
+      <c r="AK142" s="11" t="n"/>
+    </row>
+    <row r="143" ht="409" customHeight="1">
+      <c r="C143" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> `after_value`：更新後のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+{
+  "hanbaiten_id": 1,
+  "ja_id": 1,
+  "hanbaiten_code": "H001",
+  "hanbaiten_name": "販売店A改定",
+  "hanbaiten_name_kana": "ハンバイテンA",
+  "torihikisaki_no": "1234567890123",
+  "yubin_no": "1000001",
+  "address": "東京都千代田区1-1-1",
+  "tel": "03-1234-5678",
+  "fax": "03-1234-5679",
+  "shocho_name": "山田太郎",
+  "itaku_kubun": 1,
+  "haitatsuryo_tanka_id": 10,
+  "haitatsuryo_shiharai_cycle": 1,
+  "tesuryo_kubun": 1,
+  "tesuryo_amount": 600.00,
+  "bank_code": "0001",
+  "bank_name": "○○銀行",
+  "bank_branch_code": "001",
+  "bank_branch_name": "東京支店",
+  "yokin_shubetsu": 1,
+  "koza_no": "1234567",
+  "koza_meigi": "販売店A代表",
+  "haiten_flg": false,
+  "biko": "更新しました"
+}</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="n"/>
+      <c r="E143" s="10" t="n"/>
+      <c r="F143" s="10" t="n"/>
+      <c r="G143" s="10" t="n"/>
+      <c r="H143" s="10" t="n"/>
+      <c r="I143" s="10" t="n"/>
+      <c r="J143" s="10" t="n"/>
+      <c r="K143" s="10" t="n"/>
+      <c r="L143" s="10" t="n"/>
+      <c r="M143" s="10" t="n"/>
+      <c r="N143" s="10" t="n"/>
+      <c r="O143" s="10" t="n"/>
+      <c r="P143" s="10" t="n"/>
+      <c r="Q143" s="10" t="n"/>
+      <c r="R143" s="10" t="n"/>
+      <c r="S143" s="10" t="n"/>
+      <c r="T143" s="10" t="n"/>
+      <c r="U143" s="10" t="n"/>
+      <c r="V143" s="10" t="n"/>
+      <c r="W143" s="10" t="n"/>
+      <c r="X143" s="10" t="n"/>
+      <c r="Y143" s="10" t="n"/>
+      <c r="Z143" s="10" t="n"/>
+      <c r="AA143" s="10" t="n"/>
+      <c r="AB143" s="10" t="n"/>
+      <c r="AC143" s="10" t="n"/>
+      <c r="AD143" s="10" t="n"/>
+      <c r="AE143" s="10" t="n"/>
+      <c r="AF143" s="10" t="n"/>
+      <c r="AG143" s="10" t="n"/>
+      <c r="AH143" s="10" t="n"/>
+      <c r="AI143" s="10" t="n"/>
+      <c r="AJ143" s="10" t="n"/>
+      <c r="AK143" s="11" t="n"/>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="B144" s="27" t="inlineStr">
         <is>
-          <t>4.7 例外処理</t>
+          <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
       <c r="C145" s="41" t="inlineStr">
         <is>
+          <t>更新されたデータをdata オブジェクトとして返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="B146" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="C147" s="41" t="inlineStr">
+        <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="18" customHeight="1">
-      <c r="C146" s="41" t="inlineStr">
+    <row r="148" ht="18" customHeight="1">
+      <c r="C148" s="41" t="inlineStr">
         <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="216" customHeight="1">
-      <c r="C147" s="42" t="inlineStr">
+    <row r="149" ht="216" customHeight="1">
+      <c r="C149" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -17085,46 +17487,48 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D147" s="10" t="n"/>
-      <c r="E147" s="10" t="n"/>
-      <c r="F147" s="10" t="n"/>
-      <c r="G147" s="10" t="n"/>
-      <c r="H147" s="10" t="n"/>
-      <c r="I147" s="10" t="n"/>
-      <c r="J147" s="10" t="n"/>
-      <c r="K147" s="10" t="n"/>
-      <c r="L147" s="10" t="n"/>
-      <c r="M147" s="10" t="n"/>
-      <c r="N147" s="10" t="n"/>
-      <c r="O147" s="10" t="n"/>
-      <c r="P147" s="10" t="n"/>
-      <c r="Q147" s="10" t="n"/>
-      <c r="R147" s="10" t="n"/>
-      <c r="S147" s="10" t="n"/>
-      <c r="T147" s="10" t="n"/>
-      <c r="U147" s="10" t="n"/>
-      <c r="V147" s="10" t="n"/>
-      <c r="W147" s="10" t="n"/>
-      <c r="X147" s="10" t="n"/>
-      <c r="Y147" s="10" t="n"/>
-      <c r="Z147" s="10" t="n"/>
-      <c r="AA147" s="10" t="n"/>
-      <c r="AB147" s="10" t="n"/>
-      <c r="AC147" s="10" t="n"/>
-      <c r="AD147" s="10" t="n"/>
-      <c r="AE147" s="10" t="n"/>
-      <c r="AF147" s="10" t="n"/>
-      <c r="AG147" s="10" t="n"/>
-      <c r="AH147" s="10" t="n"/>
-      <c r="AI147" s="10" t="n"/>
-      <c r="AJ147" s="10" t="n"/>
-      <c r="AK147" s="11" t="n"/>
+      <c r="D149" s="10" t="n"/>
+      <c r="E149" s="10" t="n"/>
+      <c r="F149" s="10" t="n"/>
+      <c r="G149" s="10" t="n"/>
+      <c r="H149" s="10" t="n"/>
+      <c r="I149" s="10" t="n"/>
+      <c r="J149" s="10" t="n"/>
+      <c r="K149" s="10" t="n"/>
+      <c r="L149" s="10" t="n"/>
+      <c r="M149" s="10" t="n"/>
+      <c r="N149" s="10" t="n"/>
+      <c r="O149" s="10" t="n"/>
+      <c r="P149" s="10" t="n"/>
+      <c r="Q149" s="10" t="n"/>
+      <c r="R149" s="10" t="n"/>
+      <c r="S149" s="10" t="n"/>
+      <c r="T149" s="10" t="n"/>
+      <c r="U149" s="10" t="n"/>
+      <c r="V149" s="10" t="n"/>
+      <c r="W149" s="10" t="n"/>
+      <c r="X149" s="10" t="n"/>
+      <c r="Y149" s="10" t="n"/>
+      <c r="Z149" s="10" t="n"/>
+      <c r="AA149" s="10" t="n"/>
+      <c r="AB149" s="10" t="n"/>
+      <c r="AC149" s="10" t="n"/>
+      <c r="AD149" s="10" t="n"/>
+      <c r="AE149" s="10" t="n"/>
+      <c r="AF149" s="10" t="n"/>
+      <c r="AG149" s="10" t="n"/>
+      <c r="AH149" s="10" t="n"/>
+      <c r="AI149" s="10" t="n"/>
+      <c r="AJ149" s="10" t="n"/>
+      <c r="AK149" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="435">
+  <mergeCells count="448">
+    <mergeCell ref="Y46:AB46"/>
     <mergeCell ref="AF65:AK65"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="D61:L61"/>
+    <mergeCell ref="Q78:S78"/>
     <mergeCell ref="M72:P72"/>
     <mergeCell ref="T53:X53"/>
     <mergeCell ref="Y41:AB41"/>
@@ -17136,31 +17540,31 @@
     <mergeCell ref="M59:P59"/>
     <mergeCell ref="Y43:AB43"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="D64:L64"/>
-    <mergeCell ref="C94:AK94"/>
-    <mergeCell ref="D51:L51"/>
+    <mergeCell ref="C142:AK142"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
+    <mergeCell ref="Q77:S77"/>
+    <mergeCell ref="D124:AK124"/>
     <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="B138:AK138"/>
     <mergeCell ref="Y34:AB34"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="Y36:AB36"/>
-    <mergeCell ref="C131:AK131"/>
     <mergeCell ref="AC39:AE39"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="D75:L75"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="C38:L38"/>
     <mergeCell ref="Q59:S59"/>
+    <mergeCell ref="Q46:S46"/>
     <mergeCell ref="Y66:AE66"/>
-    <mergeCell ref="C88:AK88"/>
     <mergeCell ref="Y53:AE53"/>
-    <mergeCell ref="C126:AK126"/>
+    <mergeCell ref="D129:AK129"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="Q61:S61"/>
     <mergeCell ref="AF35:AK35"/>
@@ -17168,13 +17572,13 @@
     <mergeCell ref="Y68:AE68"/>
     <mergeCell ref="T74:X74"/>
     <mergeCell ref="Y55:AE55"/>
-    <mergeCell ref="B87:I87"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C35:L35"/>
     <mergeCell ref="T76:X76"/>
     <mergeCell ref="T69:X69"/>
     <mergeCell ref="D65:L65"/>
     <mergeCell ref="M27:P27"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="C145:AK145"/>
@@ -17186,13 +17590,13 @@
     <mergeCell ref="C28:L28"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
-    <mergeCell ref="Q49:S49"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="Y56:AE56"/>
     <mergeCell ref="T59:X59"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="C134:AK134"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="Y39:AB39"/>
@@ -17205,16 +17609,17 @@
     <mergeCell ref="M75:P75"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="Q62:S62"/>
+    <mergeCell ref="B95:I95"/>
+    <mergeCell ref="B89:I89"/>
     <mergeCell ref="Y69:AE69"/>
     <mergeCell ref="D120:AK120"/>
     <mergeCell ref="C43:L43"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
-    <mergeCell ref="B134:AK134"/>
     <mergeCell ref="Q64:S64"/>
+    <mergeCell ref="T77:X77"/>
     <mergeCell ref="M41:P41"/>
-    <mergeCell ref="B90:I90"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
@@ -17227,25 +17632,26 @@
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="T61:X61"/>
     <mergeCell ref="Y51:AE51"/>
-    <mergeCell ref="B124:AK124"/>
+    <mergeCell ref="C148:AK148"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="C44:L44"/>
     <mergeCell ref="AF70:AK70"/>
-    <mergeCell ref="D108:AK108"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="AC28:AE28"/>
+    <mergeCell ref="B126:AK126"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="M46:P46"/>
     <mergeCell ref="M37:P37"/>
     <mergeCell ref="AC30:AE30"/>
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="C102:AK102"/>
+    <mergeCell ref="Y77:AE77"/>
     <mergeCell ref="J18:M18"/>
-    <mergeCell ref="B96:I96"/>
     <mergeCell ref="D121:AK121"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="C49:L49"/>
     <mergeCell ref="M56:P56"/>
     <mergeCell ref="C141:AK141"/>
     <mergeCell ref="D113:AK113"/>
@@ -17253,6 +17659,7 @@
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="AF50:AK50"/>
     <mergeCell ref="Q70:S70"/>
+    <mergeCell ref="B98:I98"/>
     <mergeCell ref="Y72:AE72"/>
     <mergeCell ref="C42:L42"/>
     <mergeCell ref="J19:M19"/>
@@ -17262,9 +17669,9 @@
     <mergeCell ref="AF34:AK34"/>
     <mergeCell ref="T75:X75"/>
     <mergeCell ref="M25:P25"/>
-    <mergeCell ref="AF49:AK49"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="Q58:S58"/>
+    <mergeCell ref="AF78:AK78"/>
     <mergeCell ref="Y65:AE65"/>
     <mergeCell ref="D76:L76"/>
     <mergeCell ref="C39:L39"/>
@@ -17276,6 +17683,7 @@
     <mergeCell ref="D118:AK118"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="B86:I86"/>
     <mergeCell ref="AC44:AE44"/>
     <mergeCell ref="AC31:AE31"/>
     <mergeCell ref="M64:P64"/>
@@ -17288,19 +17696,24 @@
     <mergeCell ref="AF73:AK73"/>
     <mergeCell ref="Q71:S71"/>
     <mergeCell ref="M65:P65"/>
+    <mergeCell ref="Y78:AE78"/>
+    <mergeCell ref="T46:X46"/>
     <mergeCell ref="AF66:AK66"/>
     <mergeCell ref="D116:AK116"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q73:S73"/>
     <mergeCell ref="AF68:AK68"/>
+    <mergeCell ref="C96:AK96"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="M34:P34"/>
-    <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
+    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="D119:AK119"/>
     <mergeCell ref="D54:L54"/>
     <mergeCell ref="T41:X41"/>
+    <mergeCell ref="M78:P78"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="J9:AK9"/>
@@ -17322,15 +17735,16 @@
     <mergeCell ref="AF76:AK76"/>
     <mergeCell ref="Q74:S74"/>
     <mergeCell ref="T62:X62"/>
+    <mergeCell ref="B146:AK146"/>
     <mergeCell ref="Q76:S76"/>
     <mergeCell ref="AC27:AE27"/>
     <mergeCell ref="C137:AK137"/>
     <mergeCell ref="T64:X64"/>
     <mergeCell ref="Y44:AB44"/>
+    <mergeCell ref="C90:AK90"/>
+    <mergeCell ref="D60:L60"/>
     <mergeCell ref="C139:AK139"/>
-    <mergeCell ref="D60:L60"/>
     <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="C138:AK138"/>
     <mergeCell ref="C132:AK132"/>
     <mergeCell ref="Y59:AE59"/>
     <mergeCell ref="M42:P42"/>
@@ -17338,7 +17752,6 @@
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
     <mergeCell ref="T33:X33"/>
@@ -17348,20 +17761,27 @@
     <mergeCell ref="AC38:AE38"/>
     <mergeCell ref="B136:AK136"/>
     <mergeCell ref="Y32:AB32"/>
+    <mergeCell ref="C108:AK108"/>
+    <mergeCell ref="D78:L78"/>
     <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="AC46:AE46"/>
     <mergeCell ref="AC40:AE40"/>
     <mergeCell ref="D71:L71"/>
     <mergeCell ref="C34:L34"/>
-    <mergeCell ref="C85:AK85"/>
+    <mergeCell ref="C109:AK109"/>
     <mergeCell ref="Y62:AE62"/>
     <mergeCell ref="D73:L73"/>
+    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="C133:AK133"/>
     <mergeCell ref="M70:P70"/>
+    <mergeCell ref="C127:AK127"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AC41:AE41"/>
     <mergeCell ref="Y64:AE64"/>
     <mergeCell ref="J2:P3"/>
+    <mergeCell ref="AF77:AK77"/>
+    <mergeCell ref="B83:I83"/>
     <mergeCell ref="M74:P74"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
@@ -17389,14 +17809,14 @@
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="B78:I78"/>
+    <mergeCell ref="C99:AK99"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="B104:AK104"/>
     <mergeCell ref="T60:X60"/>
     <mergeCell ref="C130:AK130"/>
+    <mergeCell ref="B106:AK106"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="C125:AK125"/>
@@ -17406,42 +17826,41 @@
     <mergeCell ref="Y57:AE57"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="B93:I93"/>
     <mergeCell ref="C37:L37"/>
+    <mergeCell ref="T78:X78"/>
     <mergeCell ref="T65:X65"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="T50:X50"/>
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="J8:AK8"/>
+    <mergeCell ref="B101:I101"/>
     <mergeCell ref="D55:L55"/>
     <mergeCell ref="AF40:AK40"/>
-    <mergeCell ref="C146:AK146"/>
     <mergeCell ref="D67:L67"/>
     <mergeCell ref="T73:X73"/>
     <mergeCell ref="J10:AK10"/>
-    <mergeCell ref="C105:AK105"/>
     <mergeCell ref="D69:L69"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="Y60:AE60"/>
     <mergeCell ref="N16:AK16"/>
+    <mergeCell ref="C149:AK149"/>
     <mergeCell ref="Q55:S55"/>
     <mergeCell ref="Y37:AB37"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="M26:P26"/>
-    <mergeCell ref="B81:I81"/>
     <mergeCell ref="Q40:S40"/>
     <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="B107:AK107"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="Y71:AE71"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="C45:L45"/>
     <mergeCell ref="Y58:AE58"/>
-    <mergeCell ref="D109:AK109"/>
+    <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="Q66:S66"/>
-    <mergeCell ref="B99:I99"/>
     <mergeCell ref="Q53:S53"/>
     <mergeCell ref="Y73:AE73"/>
     <mergeCell ref="J15:M15"/>
@@ -17449,11 +17868,13 @@
     <mergeCell ref="T70:X70"/>
     <mergeCell ref="AF61:AK61"/>
     <mergeCell ref="D111:AK111"/>
+    <mergeCell ref="B92:I92"/>
     <mergeCell ref="Q68:S68"/>
     <mergeCell ref="C40:L40"/>
-    <mergeCell ref="C91:AK91"/>
+    <mergeCell ref="C51:L51"/>
     <mergeCell ref="M28:P28"/>
-    <mergeCell ref="C82:AK82"/>
+    <mergeCell ref="D77:L77"/>
+    <mergeCell ref="A105:AK105"/>
     <mergeCell ref="Q72:S72"/>
     <mergeCell ref="M57:P57"/>
     <mergeCell ref="M32:P32"/>
@@ -17473,13 +17894,12 @@
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q56:S56"/>
-    <mergeCell ref="A103:AK103"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="T66:X66"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
     <mergeCell ref="AF67:AK67"/>
-    <mergeCell ref="C106:AK106"/>
+    <mergeCell ref="C46:L46"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="AF69:AK69"/>
     <mergeCell ref="Q67:S67"/>
@@ -17489,7 +17909,6 @@
     <mergeCell ref="Q69:S69"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y76:AE76"/>
-    <mergeCell ref="D127:AK127"/>
     <mergeCell ref="AF64:AK64"/>
     <mergeCell ref="D114:AK114"/>
     <mergeCell ref="AF51:AK51"/>
@@ -17503,33 +17922,29 @@
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="B129:AK129"/>
-    <mergeCell ref="D107:AK107"/>
     <mergeCell ref="C36:L36"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="D52:L52"/>
     <mergeCell ref="AC33:AE33"/>
     <mergeCell ref="T39:X39"/>
+    <mergeCell ref="B131:AK131"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="A47:AK47"/>
     <mergeCell ref="T32:X32"/>
     <mergeCell ref="AC35:AE35"/>
+    <mergeCell ref="C52:C78"/>
     <mergeCell ref="M63:P63"/>
     <mergeCell ref="M53:P53"/>
     <mergeCell ref="AC34:AE34"/>
     <mergeCell ref="M50:P50"/>
     <mergeCell ref="M68:P68"/>
-    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="M55:P55"/>
     <mergeCell ref="M67:P67"/>
     <mergeCell ref="AF72:AK72"/>
-    <mergeCell ref="C51:C76"/>
     <mergeCell ref="Q75:S75"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="M69:P69"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="B142:AK142"/>
     <mergeCell ref="T52:X52"/>
     <mergeCell ref="B144:AK144"/>
     <mergeCell ref="Y40:AB40"/>
@@ -17539,23 +17954,23 @@
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="T49:X49"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="M76:P76"/>
     <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="Q65:S65"/>
-    <mergeCell ref="C97:AK97"/>
+    <mergeCell ref="D123:AK123"/>
     <mergeCell ref="AF60:AK60"/>
     <mergeCell ref="D110:AK110"/>
     <mergeCell ref="D74:L74"/>
     <mergeCell ref="D68:L68"/>
+    <mergeCell ref="A48:AK48"/>
     <mergeCell ref="AC36:AE36"/>
     <mergeCell ref="Y35:AB35"/>
     <mergeCell ref="D59:L59"/>
-    <mergeCell ref="B84:I84"/>
     <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
+    <mergeCell ref="B80:I80"/>
+    <mergeCell ref="M77:P77"/>
     <mergeCell ref="Y52:AE52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
